--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7755"/>
+    <workbookView windowWidth="20490" windowHeight="7635" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -969,7 +969,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="189">
   <si>
     <t>Atributos</t>
   </si>
@@ -1263,6 +1263,9 @@
   </si>
   <si>
     <t>Controlar Madeira</t>
+  </si>
+  <si>
+    <t>disc</t>
   </si>
   <si>
     <t>Enxame de Pesteste</t>
@@ -1618,10 +1621,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1673,83 +1676,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1766,12 +1692,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
@@ -1786,8 +1721,76 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1803,10 +1806,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1828,7 +1831,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1849,7 +1852,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1861,13 +1906,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1879,7 +1930,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1891,7 +1948,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1903,55 +2014,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1963,73 +2038,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2552,35 +2561,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2600,6 +2591,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2607,30 +2613,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2649,155 +2631,182 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="44" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3003,6 +3012,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3079,54 +3089,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
+    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
+    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
+    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
+    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
+    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
+    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
+    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
+    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
+    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
+    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
+    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
+    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
+    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
+    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
+    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
+    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
+    <cellStyle name="Saída" xfId="25" builtinId="21"/>
+    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
+    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bom" xfId="29" builtinId="26"/>
+    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
+    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
+    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
+    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
+    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
+    <cellStyle name="Título" xfId="36" builtinId="15"/>
+    <cellStyle name="Observação" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
+    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
+    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
+    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
+    <cellStyle name="Comma" xfId="43" builtinId="3"/>
+    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
+    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
+    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
+    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
@@ -4396,19 +4406,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.4266666666667" customWidth="1"/>
-    <col min="3" max="3" width="6.14222222222222" customWidth="1"/>
-    <col min="4" max="4" width="13.2844444444444" customWidth="1"/>
-    <col min="6" max="6" width="14.5688888888889" customWidth="1"/>
-    <col min="7" max="8" width="7.85333333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.425" customWidth="1"/>
+    <col min="3" max="3" width="6.14166666666667" customWidth="1"/>
+    <col min="4" max="4" width="13.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="14.5666666666667" customWidth="1"/>
+    <col min="7" max="8" width="7.85" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="14" max="14" width="36.4266666666667" customWidth="1"/>
+    <col min="14" max="14" width="36.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
+    <row r="1" ht="15.75"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -4449,7 +4459,7 @@
       </c>
       <c r="G3" s="27">
         <f>H3-L25-SUM(L4:L22)</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H3" s="39">
         <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
@@ -4494,7 +4504,9 @@
       <c r="K4" s="41">
         <v>1</v>
       </c>
-      <c r="L4" s="29"/>
+      <c r="L4" s="29">
+        <v>12</v>
+      </c>
       <c r="M4" s="29"/>
       <c r="N4" s="42"/>
     </row>
@@ -4517,11 +4529,13 @@
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="89"/>
+      <c r="H5" s="90"/>
       <c r="K5" s="38">
         <v>2</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="27">
+        <v>-6</v>
+      </c>
       <c r="M5" s="27"/>
       <c r="N5" s="39"/>
     </row>
@@ -4544,7 +4558,7 @@
         <f>G5+Perícias!J12</f>
         <v>27</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="91"/>
       <c r="K6" s="41">
         <v>3</v>
       </c>
@@ -4571,7 +4585,7 @@
         <f>Perícias!J27+Perícias!J21</f>
         <v>17</v>
       </c>
-      <c r="H7" s="89"/>
+      <c r="H7" s="90"/>
       <c r="K7" s="38">
         <v>4</v>
       </c>
@@ -4579,7 +4593,7 @@
       <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" ht="17.25" spans="2:14">
+    <row r="8" ht="15.75" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4594,10 +4608,10 @@
       <c r="F8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="92">
         <v>0.5</v>
       </c>
-      <c r="H8" s="92"/>
+      <c r="H8" s="93"/>
       <c r="K8" s="41">
         <v>5</v>
       </c>
@@ -4605,12 +4619,12 @@
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" spans="6:14">
+    <row r="9" ht="15.75" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="27">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="H9" s="39"/>
       <c r="K9" s="38">
@@ -4620,7 +4634,7 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" ht="17.25" spans="6:14">
+    <row r="10" ht="15.75" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
@@ -4635,7 +4649,7 @@
       <c r="M10" s="29"/>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" ht="18" spans="11:14">
+    <row r="11" ht="16.5" spans="11:14">
       <c r="K11" s="38">
         <v>8</v>
       </c>
@@ -4643,17 +4657,17 @@
       <c r="M11" s="27"/>
       <c r="N11" s="39"/>
     </row>
-    <row r="12" ht="18" spans="2:14">
-      <c r="B12" s="71" t="s">
+    <row r="12" ht="16.5" spans="2:14">
+      <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
       <c r="K12" s="41">
         <v>9</v>
       </c>
@@ -4661,8 +4675,8 @@
       <c r="M12" s="29"/>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" ht="18" spans="2:14">
-      <c r="B13" s="88"/>
+    <row r="13" ht="16.5" spans="2:14">
+      <c r="B13" s="89"/>
       <c r="K13" s="38">
         <v>10</v>
       </c>
@@ -4670,7 +4684,7 @@
       <c r="M13" s="27"/>
       <c r="N13" s="39"/>
     </row>
-    <row r="14" ht="17.25" spans="2:14">
+    <row r="14" ht="15.75" spans="2:14">
       <c r="B14" s="35" t="s">
         <v>21</v>
       </c>
@@ -4718,7 +4732,7 @@
       <c r="M15" s="27"/>
       <c r="N15" s="39"/>
     </row>
-    <row r="16" ht="17.25" spans="2:14">
+    <row r="16" ht="30.75" spans="2:14">
       <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
@@ -4752,7 +4766,7 @@
       <c r="M16" s="29"/>
       <c r="N16" s="42"/>
     </row>
-    <row r="17" ht="17.25" spans="11:14">
+    <row r="17" ht="15.75" spans="11:14">
       <c r="K17" s="38">
         <v>14</v>
       </c>
@@ -4800,8 +4814,8 @@
       <c r="M22" s="53"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" ht="18"/>
-    <row r="24" ht="17.25" spans="11:12">
+    <row r="23" ht="16.5"/>
+    <row r="24" ht="15.75" spans="11:12">
       <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
@@ -4813,13 +4827,13 @@
       </c>
       <c r="L25" s="39"/>
     </row>
-    <row r="26" ht="17.25" spans="11:12">
+    <row r="26" ht="15.75" spans="11:12">
       <c r="K26" s="45" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" ht="17.25"/>
+    <row r="27" ht="15.75"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4854,35 +4868,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="12" max="12" width="19.7111111111111" customWidth="1"/>
-    <col min="13" max="13" width="12.2844444444444" customWidth="1"/>
-    <col min="14" max="14" width="12.1422222222222" customWidth="1"/>
+    <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
+    <col min="13" max="13" width="12.2833333333333" customWidth="1"/>
+    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:15">
-      <c r="A1" s="71" t="s">
+    <row r="1" ht="16.5" spans="1:15">
+      <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73"/>
-      <c r="I1" s="71" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="74"/>
+      <c r="I1" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="73"/>
-    </row>
-    <row r="2" ht="18"/>
-    <row r="3" ht="17.25" spans="2:13">
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74"/>
+    </row>
+    <row r="2" ht="16.5"/>
+    <row r="3" ht="15.75" spans="2:13">
       <c r="B3" s="35" t="s">
         <v>34</v>
       </c>
@@ -4892,17 +4906,17 @@
       </c>
       <c r="E3" s="48"/>
       <c r="F3" s="36"/>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="84" t="s">
+      <c r="M3" s="85" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="2:13">
+    <row r="4" customHeight="1" spans="2:13">
       <c r="B4" s="38" t="s">
         <v>38</v>
       </c>
@@ -4914,15 +4928,15 @@
       <c r="F4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="77" t="s">
+      <c r="K4" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="78" t="s">
+      <c r="L4" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="85"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="2:13">
+      <c r="M4" s="86"/>
+    </row>
+    <row r="5" customHeight="1" spans="2:13">
       <c r="B5" s="41" t="s">
         <v>43</v>
       </c>
@@ -4934,15 +4948,15 @@
       <c r="F5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="79" t="s">
+      <c r="K5" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="80" t="s">
+      <c r="L5" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="86"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="2:13">
+      <c r="M5" s="87"/>
+    </row>
+    <row r="6" customHeight="1" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>46</v>
       </c>
@@ -4954,13 +4968,13 @@
       <c r="F6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="77" t="s">
+      <c r="K6" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="78" t="s">
+      <c r="L6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="85"/>
+      <c r="M6" s="86"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="41" t="s">
@@ -4974,13 +4988,13 @@
       <c r="F7" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="79" t="s">
+      <c r="K7" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="80" t="s">
+      <c r="L7" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="86"/>
+      <c r="M7" s="87"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
@@ -4994,13 +5008,13 @@
       <c r="F8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="77" t="s">
+      <c r="K8" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="81" t="s">
+      <c r="L8" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="85"/>
+      <c r="M8" s="86"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="41" t="s">
@@ -5014,11 +5028,11 @@
       <c r="F9" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="86"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="2:13">
+      <c r="K9" s="80"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="87"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>59</v>
       </c>
@@ -5030,9 +5044,9 @@
       <c r="F10" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="77"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="85"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="86"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="41" t="s">
@@ -5046,9 +5060,9 @@
       <c r="F11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="79"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="86"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="87"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
@@ -5062,9 +5076,9 @@
       <c r="F12" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="85"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="86"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="41" t="s">
@@ -5078,10 +5092,10 @@
       <c r="F13" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="74"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="86"/>
+      <c r="G13" s="75"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="87"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
@@ -5091,9 +5105,9 @@
       <c r="D14" s="27"/>
       <c r="E14" s="27"/>
       <c r="F14" s="39"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="85"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="86"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
@@ -5103,9 +5117,9 @@
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="42"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="86"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="87"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="38" t="s">
@@ -5115,9 +5129,9 @@
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="39"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="85"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="86"/>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="41" t="s">
@@ -5127,9 +5141,9 @@
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="42"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="86"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="87"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="38" t="s">
@@ -5139,9 +5153,9 @@
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
       <c r="F18" s="39"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="85"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="86"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="41" t="s">
@@ -5151,9 +5165,9 @@
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="42"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="86"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="87"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="38" t="s">
@@ -5163,9 +5177,9 @@
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
       <c r="F20" s="39"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="85"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="86"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="41" t="s">
@@ -5175,11 +5189,11 @@
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
       <c r="F21" s="42"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="86"/>
-    </row>
-    <row r="22" ht="17.25" spans="2:13">
+      <c r="K21" s="80"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="87"/>
+    </row>
+    <row r="22" ht="15.75" spans="2:13">
       <c r="B22" s="43" t="s">
         <v>76</v>
       </c>
@@ -5187,11 +5201,11 @@
       <c r="D22" s="50"/>
       <c r="E22" s="50"/>
       <c r="F22" s="44"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="87"/>
-    </row>
-    <row r="23" ht="17.25"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="88"/>
+    </row>
+    <row r="23" ht="15.75"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5247,14 +5261,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.8533333333333" customWidth="1"/>
-    <col min="7" max="7" width="8.42666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.85" customWidth="1"/>
+    <col min="7" max="7" width="8.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="17.25" spans="2:8">
+    <row r="1" ht="15.75"/>
+    <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
@@ -5272,7 +5286,7 @@
       </c>
       <c r="H2" s="65"/>
     </row>
-    <row r="3" ht="17.25" spans="2:8">
+    <row r="3" ht="15.75" spans="2:8">
       <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5283,21 +5297,21 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="17.25" spans="2:5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="2:5">
       <c r="B4" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5308,11 +5322,11 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -5326,11 +5340,11 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -5344,11 +5358,11 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -5362,11 +5376,11 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -5380,11 +5394,11 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -5398,11 +5412,11 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -5416,11 +5430,11 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -5434,11 +5448,11 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -5452,11 +5466,11 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -5470,11 +5484,11 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -5488,11 +5502,11 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -5506,11 +5520,11 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:5">
@@ -5524,11 +5538,11 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -5542,11 +5556,11 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -5578,11 +5592,11 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -5596,11 +5610,11 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -5614,11 +5628,11 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -5632,11 +5646,11 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -5657,7 +5671,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" ht="30" spans="2:5">
       <c r="B24" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Alquimista)</v>
@@ -5668,11 +5682,11 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -5686,14 +5700,14 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="2:5">
       <c r="B26" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Engenhoqueiro)</v>
@@ -5704,11 +5718,11 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -5722,11 +5736,11 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -5758,11 +5772,11 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -5776,14 +5790,14 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" ht="17.25" spans="2:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" spans="2:5">
       <c r="B31" s="43" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
@@ -5794,14 +5808,14 @@
       </c>
       <c r="D31" s="50">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" ht="17.25"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5819,17 +5833,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="23.2844444444444" customWidth="1"/>
-    <col min="3" max="3" width="15.4266666666667" customWidth="1"/>
-    <col min="4" max="4" width="11.8533333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.5688888888889" customWidth="1"/>
+    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.425" customWidth="1"/>
+    <col min="4" max="4" width="11.85" customWidth="1"/>
+    <col min="5" max="5" width="10.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="17.25" spans="2:8">
+    <row r="1" ht="15.75"/>
+    <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="24" t="s">
         <v>81</v>
       </c>
@@ -5839,7 +5853,7 @@
       <c r="D2" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="71" t="s">
         <v>83</v>
       </c>
       <c r="G2" s="35" t="s">
@@ -5861,9 +5875,6 @@
         <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="G3" s="38">
         <v>1</v>
       </c>
@@ -5885,9 +5896,6 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="G4" s="41">
         <v>2</v>
       </c>
@@ -5937,7 +5945,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="2:8">
+    <row r="7" ht="15.75" spans="1:8">
+      <c r="A7" s="69"/>
       <c r="B7" s="68" t="s">
         <v>91</v>
       </c>
@@ -5951,6 +5960,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F7" s="69"/>
       <c r="G7" s="43">
         <v>5</v>
       </c>
@@ -5958,7 +5968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="2:5">
+    <row r="8" ht="15.75" spans="2:5">
       <c r="B8" s="30" t="s">
         <v>92</v>
       </c>
@@ -6033,7 +6043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:7">
       <c r="B13" s="68" t="s">
         <v>97</v>
       </c>
@@ -6047,10 +6057,13 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
+      <c r="G13" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>86</v>
@@ -6065,10 +6078,10 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" s="27">
         <v>2</v>
@@ -6080,7 +6093,7 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>89</v>
@@ -6256,7 +6269,7 @@
       </c>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="69"/>
+      <c r="B35" s="70"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
       <c r="E35" s="47" t="str">
@@ -6281,17 +6294,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.1422222222222" customWidth="1"/>
-    <col min="4" max="4" width="17.7111111111111" customWidth="1"/>
+    <col min="2" max="2" width="21.1416666666667" customWidth="1"/>
+    <col min="4" max="4" width="17.7083333333333" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="17.25" spans="2:6">
+    <row r="1" ht="15.75"/>
+    <row r="2" ht="15.75" spans="2:6">
       <c r="B2" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -6309,15 +6322,15 @@
         <v>25</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" s="29">
         <v>10</v>
@@ -6332,17 +6345,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="2:6">
+    <row r="5" ht="15.75" spans="2:6">
       <c r="B5" s="43"/>
       <c r="C5" s="50"/>
       <c r="D5" s="50"/>
       <c r="E5" s="64"/>
       <c r="F5" s="44"/>
     </row>
-    <row r="6" ht="18"/>
-    <row r="7" ht="17.25" spans="2:8">
+    <row r="6" ht="16.5"/>
+    <row r="7" ht="15.75" spans="2:8">
       <c r="B7" s="51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
@@ -6359,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>36</v>
@@ -6379,37 +6392,37 @@
         <v>30</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="37">
         <v>2</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -6430,7 +6443,7 @@
       <c r="G12" s="37"/>
       <c r="H12" s="39"/>
     </row>
-    <row r="13" ht="17.25" spans="2:8">
+    <row r="13" ht="15.75" spans="2:8">
       <c r="B13" s="45"/>
       <c r="C13" s="53"/>
       <c r="D13" s="53"/>
@@ -6439,10 +6452,10 @@
       <c r="G13" s="66"/>
       <c r="H13" s="46"/>
     </row>
-    <row r="14" ht="18"/>
-    <row r="15" ht="17.25" spans="2:9">
+    <row r="14" ht="16.5"/>
+    <row r="15" ht="15.75" spans="2:9">
       <c r="B15" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -6461,27 +6474,27 @@
       </c>
       <c r="D16" s="55"/>
       <c r="E16" s="55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="67" t="s">
         <v>104</v>
-      </c>
-      <c r="H16" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="93" t="s">
         <v>119</v>
+      </c>
+      <c r="C17" s="94" t="s">
+        <v>120</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="29">
@@ -6504,10 +6517,10 @@
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="55">
@@ -6528,10 +6541,10 @@
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="29">
@@ -6552,7 +6565,7 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="54" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="55"/>
@@ -6574,7 +6587,7 @@
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -6660,7 +6673,7 @@
       <c r="H28" s="55"/>
       <c r="I28" s="67"/>
     </row>
-    <row r="29" ht="17.25" spans="2:9">
+    <row r="29" ht="15.75" spans="2:9">
       <c r="B29" s="7"/>
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
@@ -6670,11 +6683,11 @@
       <c r="H29" s="53"/>
       <c r="I29" s="46"/>
     </row>
-    <row r="30" ht="17.25"/>
-    <row r="31" ht="17.25"/>
-    <row r="32" ht="17.25" spans="2:4">
+    <row r="30" ht="15.75"/>
+    <row r="31" ht="15.75"/>
+    <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C32" s="57">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
@@ -6685,9 +6698,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="2:4">
+    <row r="33" customHeight="1" spans="2:4">
       <c r="B33" s="58" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C33" s="59">
         <f>Clebina!C3*10</f>
@@ -6697,7 +6710,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C34" s="61" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
@@ -6705,7 +6718,7 @@
       </c>
       <c r="D34" s="62"/>
     </row>
-    <row r="35" ht="17.25"/>
+    <row r="35" ht="15.75"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6737,39 +6750,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56888888888889" customWidth="1"/>
-    <col min="4" max="4" width="10.5688888888889" customWidth="1"/>
-    <col min="5" max="5" width="13.2844444444444" customWidth="1"/>
-    <col min="6" max="7" width="11.4266666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.1422222222222" customWidth="1"/>
-    <col min="9" max="9" width="21.4266666666667" customWidth="1"/>
-    <col min="10" max="10" width="10.1422222222222" customWidth="1"/>
-    <col min="11" max="11" width="13.8533333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.4266666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.7111111111111" customWidth="1"/>
-    <col min="14" max="14" width="9.85333333333333" customWidth="1"/>
-    <col min="15" max="15" width="12.5688888888889" customWidth="1"/>
+    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
+    <col min="6" max="7" width="11.425" customWidth="1"/>
+    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
+    <col min="9" max="9" width="21.425" customWidth="1"/>
+    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="13.85" customWidth="1"/>
+    <col min="12" max="12" width="21.425" customWidth="1"/>
+    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
+    <col min="14" max="14" width="9.85" customWidth="1"/>
+    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="15" customHeight="1" spans="2:16">
+    <row r="1" ht="15.75"/>
+    <row r="2" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6778,31 +6791,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>79</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6824,13 +6837,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6841,10 +6854,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6866,13 +6879,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>140</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6881,12 +6894,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="2:16">
+    <row r="5" ht="15.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6908,13 +6921,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>71</v>
@@ -6923,12 +6936,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="2:13">
+    <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6950,21 +6963,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6986,25 +6999,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P7" s="36"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
+    <row r="8" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7026,13 +7039,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>140</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -7044,10 +7057,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7069,13 +7082,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -7087,10 +7100,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7112,13 +7125,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7130,10 +7143,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7155,13 +7168,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7173,10 +7186,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7198,13 +7211,13 @@
         <v>5</v>
       </c>
       <c r="K12" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="M12" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7214,12 +7227,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="17.25" spans="2:16">
+    <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7241,13 +7254,13 @@
         <v>2</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7257,12 +7270,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="17.25" spans="2:13">
+    <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7284,21 +7297,21 @@
         <v>10</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7320,21 +7333,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7356,21 +7369,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7392,13 +7405,13 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
@@ -7407,10 +7420,10 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7432,21 +7445,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7468,21 +7481,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7504,13 +7517,13 @@
         <v>2</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -7518,7 +7531,7 @@
         <v>80</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7540,21 +7553,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7578,21 +7591,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7614,21 +7627,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7650,21 +7663,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7686,21 +7699,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7722,21 +7735,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7760,21 +7773,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7796,21 +7809,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7832,21 +7845,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7868,21 +7881,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7904,21 +7917,21 @@
         <v>6</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L31" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7940,21 +7953,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7976,13 +7989,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>140</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8003,39 +8016,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56888888888889" customWidth="1"/>
-    <col min="4" max="4" width="10.5688888888889" customWidth="1"/>
-    <col min="5" max="5" width="13.2844444444444" customWidth="1"/>
-    <col min="6" max="7" width="11.4266666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.1422222222222" customWidth="1"/>
-    <col min="9" max="9" width="21.4266666666667" customWidth="1"/>
-    <col min="10" max="10" width="10.1422222222222" customWidth="1"/>
-    <col min="11" max="11" width="13.8533333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.4266666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.7111111111111" customWidth="1"/>
-    <col min="14" max="14" width="9.85333333333333" customWidth="1"/>
-    <col min="15" max="15" width="12.5688888888889" customWidth="1"/>
+    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
+    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
+    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
+    <col min="6" max="7" width="11.425" customWidth="1"/>
+    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
+    <col min="9" max="9" width="21.425" customWidth="1"/>
+    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="11" max="11" width="13.85" customWidth="1"/>
+    <col min="12" max="12" width="21.425" customWidth="1"/>
+    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
+    <col min="14" max="14" width="9.85" customWidth="1"/>
+    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="15" customHeight="1" spans="2:16">
+    <row r="1" ht="15.75"/>
+    <row r="2" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -8044,31 +8057,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>79</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8090,13 +8103,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8107,10 +8120,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8132,13 +8145,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>140</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8147,12 +8160,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="2:16">
+    <row r="5" ht="15.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8174,13 +8187,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>71</v>
@@ -8189,12 +8202,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="2:13">
+    <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8216,21 +8229,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8252,25 +8265,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P7" s="36"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
+    <row r="8" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8292,13 +8305,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>140</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8310,10 +8323,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8335,13 +8348,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8353,10 +8366,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8378,13 +8391,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8396,10 +8409,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8421,13 +8434,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8439,10 +8452,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8464,13 +8477,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8480,12 +8493,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="17.25" spans="2:16">
+    <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8507,13 +8520,13 @@
         <v>4</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8523,12 +8536,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="17.25" spans="2:13">
+    <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8552,21 +8565,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8588,21 +8601,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8624,21 +8637,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8660,21 +8673,21 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8696,21 +8709,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8732,21 +8745,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8768,13 +8781,13 @@
         <v>4</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -8782,7 +8795,7 @@
         <v>80</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8804,21 +8817,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8842,21 +8855,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8878,21 +8891,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8914,21 +8927,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8950,21 +8963,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8986,21 +8999,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9024,21 +9037,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>140</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9060,21 +9073,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>141</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9096,21 +9109,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9132,21 +9145,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>140</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9168,21 +9181,21 @@
         <v>8</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9204,21 +9217,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9240,13 +9253,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>140</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -9267,19 +9280,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="10.2844444444444" customWidth="1"/>
-    <col min="4" max="4" width="12.2844444444444" customWidth="1"/>
-    <col min="8" max="8" width="20.2844444444444" customWidth="1"/>
-    <col min="9" max="9" width="19.8533333333333" customWidth="1"/>
+    <col min="2" max="3" width="10.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
+    <col min="8" max="8" width="20.2833333333333" customWidth="1"/>
+    <col min="9" max="9" width="19.85" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25"/>
-    <row r="2" ht="17.25" spans="2:13">
+    <row r="1" ht="15.75"/>
+    <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9289,16 +9302,16 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
@@ -9329,13 +9342,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="17.25" spans="2:13">
+    <row r="4" ht="15.75" spans="2:13">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9359,13 +9372,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="2:10">
+    <row r="5" ht="15.75" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9419,7 +9432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="2:10">
+    <row r="8" ht="15.75" spans="2:10">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9437,7 +9450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="8:10">
+    <row r="9" ht="15.75" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9461,7 +9474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="8:10">
+    <row r="11" ht="15.75" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9473,9 +9486,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="17.25" spans="2:10">
+    <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9494,7 +9507,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9511,7 +9524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="17.25" spans="2:10">
+    <row r="14" ht="15.75" spans="2:10">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
@@ -9525,7 +9538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="18" spans="8:10">
+    <row r="15" ht="16.5" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9537,15 +9550,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="17.25" spans="2:10">
+    <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>79</v>
@@ -9678,7 +9691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="17.25" spans="2:10">
+    <row r="22" ht="15.75" spans="2:10">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9701,7 +9714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="17.25"/>
+    <row r="23" ht="15.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -969,7 +969,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="188">
   <si>
     <t>Atributos</t>
   </si>
@@ -1289,58 +1289,6 @@
     <t>Peso</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="DejaVu Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Armadura</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="Palatino Linotype"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="DejaVu Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>de</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="Palatino Linotype"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="DejaVu Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Gelo Eterno</t>
-    </r>
-  </si>
-  <si>
     <t>Armas</t>
   </si>
   <si>
@@ -1389,36 +1337,7 @@
     <t>2d8+2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="DejaVu Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>poçao</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="Palatino Linotype"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF231F20"/>
-        <rFont val="DejaVu Sans"/>
-        <charset val="134"/>
-      </rPr>
-      <t>vida</t>
-    </r>
+    <t>poçao vida</t>
   </si>
   <si>
     <t>Curar ferimentos</t>
@@ -1621,12 +1540,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1656,21 +1575,15 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF231F20"/>
-      <name val="DejaVu Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF231F20"/>
       <name val="Palatino Linotype"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1683,30 +1596,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
@@ -1715,14 +1634,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1737,7 +1649,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1745,45 +1657,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1797,9 +1678,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1858,30 +1770,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1894,13 +1782,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1918,19 +1824,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1948,13 +1842,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1966,31 +1860,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2008,7 +1890,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2020,25 +1944,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2576,6 +2488,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2591,21 +2521,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2613,6 +2528,15 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2632,181 +2556,169 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2952,9 +2864,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2967,10 +2876,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3006,7 +2915,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4406,7 +4315,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.425" customWidth="1"/>
     <col min="3" max="3" width="6.14166666666667" customWidth="1"/>
@@ -4418,7 +4327,7 @@
     <col min="14" max="14" width="36.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -4442,7 +4351,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="36"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" ht="14.25" spans="2:14">
       <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4478,7 +4387,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" ht="15" spans="2:14">
       <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
@@ -4495,7 +4404,7 @@
       </c>
       <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
@@ -4510,7 +4419,7 @@
       <c r="M4" s="29"/>
       <c r="N4" s="42"/>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" ht="14.25" spans="2:14">
       <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
@@ -4529,7 +4438,7 @@
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="90"/>
+      <c r="H5" s="89"/>
       <c r="K5" s="38">
         <v>2</v>
       </c>
@@ -4539,7 +4448,7 @@
       <c r="M5" s="27"/>
       <c r="N5" s="39"/>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" ht="15" spans="2:14">
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
@@ -4558,15 +4467,17 @@
         <f>G5+Perícias!J12</f>
         <v>27</v>
       </c>
-      <c r="H6" s="91"/>
+      <c r="H6" s="90"/>
       <c r="K6" s="41">
         <v>3</v>
       </c>
-      <c r="L6" s="29"/>
+      <c r="L6" s="29">
+        <v>8</v>
+      </c>
       <c r="M6" s="29"/>
       <c r="N6" s="42"/>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" ht="14.25" spans="2:14">
       <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
@@ -4585,19 +4496,21 @@
         <f>Perícias!J27+Perícias!J21</f>
         <v>17</v>
       </c>
-      <c r="H7" s="90"/>
+      <c r="H7" s="89"/>
       <c r="K7" s="38">
         <v>4</v>
       </c>
       <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
+      <c r="M7" s="27">
+        <v>3</v>
+      </c>
       <c r="N7" s="39"/>
     </row>
     <row r="8" ht="15.75" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="52">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
@@ -4608,23 +4521,25 @@
       <c r="F8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="91">
         <v>0.5</v>
       </c>
-      <c r="H8" s="93"/>
+      <c r="H8" s="92"/>
       <c r="K8" s="41">
         <v>5</v>
       </c>
-      <c r="L8" s="29"/>
+      <c r="L8" s="29">
+        <v>-8</v>
+      </c>
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" ht="15.75" spans="6:14">
+    <row r="9" ht="15" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="27">
-        <v>18</v>
+        <v>1018</v>
       </c>
       <c r="H9" s="39"/>
       <c r="K9" s="38">
@@ -4638,7 +4553,7 @@
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="52">
         <v>6600</v>
       </c>
       <c r="H10" s="46"/>
@@ -4649,7 +4564,7 @@
       <c r="M10" s="29"/>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" ht="16.5" spans="11:14">
+    <row r="11" ht="15.75" spans="11:14">
       <c r="K11" s="38">
         <v>8</v>
       </c>
@@ -4658,16 +4573,16 @@
       <c r="N11" s="39"/>
     </row>
     <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="73"/>
       <c r="K12" s="41">
         <v>9</v>
       </c>
@@ -4675,8 +4590,8 @@
       <c r="M12" s="29"/>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" ht="16.5" spans="2:14">
-      <c r="B13" s="89"/>
+    <row r="13" ht="15.75" spans="2:14">
+      <c r="B13" s="88"/>
       <c r="K13" s="38">
         <v>10</v>
       </c>
@@ -4703,7 +4618,7 @@
       <c r="M14" s="29"/>
       <c r="N14" s="42"/>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" ht="14.25" spans="2:14">
       <c r="B15" s="38" t="s">
         <v>23</v>
       </c>
@@ -4736,7 +4651,7 @@
       <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="52">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,2,FALSE),"")</f>
         <v>10</v>
       </c>
@@ -4747,11 +4662,11 @@
       <c r="F16" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="52" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
         <v>1d4</v>
       </c>
-      <c r="H16" s="53">
+      <c r="H16" s="52">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,3,FALSE),"")</f>
         <v>0</v>
       </c>
@@ -4766,7 +4681,7 @@
       <c r="M16" s="29"/>
       <c r="N16" s="42"/>
     </row>
-    <row r="17" ht="15.75" spans="11:14">
+    <row r="17" ht="15" spans="11:14">
       <c r="K17" s="38">
         <v>14</v>
       </c>
@@ -4782,7 +4697,7 @@
       <c r="M18" s="29"/>
       <c r="N18" s="42"/>
     </row>
-    <row r="19" spans="11:14">
+    <row r="19" ht="14.25" spans="11:14">
       <c r="K19" s="38">
         <v>16</v>
       </c>
@@ -4790,7 +4705,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="39"/>
     </row>
-    <row r="20" spans="11:14">
+    <row r="20" ht="15" spans="11:14">
       <c r="K20" s="41">
         <v>17</v>
       </c>
@@ -4798,7 +4713,7 @@
       <c r="M20" s="29"/>
       <c r="N20" s="42"/>
     </row>
-    <row r="21" spans="11:14">
+    <row r="21" ht="14.25" spans="11:14">
       <c r="K21" s="38">
         <v>18</v>
       </c>
@@ -4810,18 +4725,18 @@
       <c r="K22" s="45">
         <v>20</v>
       </c>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" ht="16.5"/>
+    <row r="23" ht="15"/>
     <row r="24" ht="15.75" spans="11:12">
       <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="36"/>
     </row>
-    <row r="25" spans="11:12">
+    <row r="25" ht="14.25" spans="11:12">
       <c r="K25" s="38" t="s">
         <v>5</v>
       </c>
@@ -4833,7 +4748,7 @@
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" ht="15.75"/>
+    <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4868,7 +4783,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
     <col min="13" max="13" width="12.2833333333333" customWidth="1"/>
@@ -4876,26 +4791,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
-      <c r="I1" s="72" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73"/>
+      <c r="I1" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74"/>
-    </row>
-    <row r="2" ht="16.5"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="73"/>
+    </row>
+    <row r="2" ht="15"/>
     <row r="3" ht="15.75" spans="2:13">
       <c r="B3" s="35" t="s">
         <v>34</v>
@@ -4906,17 +4821,17 @@
       </c>
       <c r="E3" s="48"/>
       <c r="F3" s="36"/>
-      <c r="K3" s="76" t="s">
+      <c r="K3" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="77" t="s">
+      <c r="L3" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="85" t="s">
+      <c r="M3" s="84" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:13">
+    <row r="4" ht="15" customHeight="1" spans="2:13">
       <c r="B4" s="38" t="s">
         <v>38</v>
       </c>
@@ -4928,15 +4843,15 @@
       <c r="F4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="86"/>
-    </row>
-    <row r="5" customHeight="1" spans="2:13">
+      <c r="M4" s="85"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="2:13">
       <c r="B5" s="41" t="s">
         <v>43</v>
       </c>
@@ -4948,15 +4863,15 @@
       <c r="F5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="80" t="s">
+      <c r="K5" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="87"/>
-    </row>
-    <row r="6" customHeight="1" spans="2:13">
+      <c r="M5" s="86"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>46</v>
       </c>
@@ -4968,15 +4883,15 @@
       <c r="F6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="86"/>
-    </row>
-    <row r="7" spans="2:13">
+      <c r="M6" s="85"/>
+    </row>
+    <row r="7" ht="15" spans="2:13">
       <c r="B7" s="41" t="s">
         <v>49</v>
       </c>
@@ -4988,15 +4903,15 @@
       <c r="F7" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="80" t="s">
+      <c r="K7" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="81" t="s">
+      <c r="L7" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="87"/>
-    </row>
-    <row r="8" spans="2:13">
+      <c r="M7" s="86"/>
+    </row>
+    <row r="8" ht="14.25" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>53</v>
       </c>
@@ -5008,15 +4923,15 @@
       <c r="F8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="82" t="s">
+      <c r="L8" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="86"/>
-    </row>
-    <row r="9" spans="2:13">
+      <c r="M8" s="85"/>
+    </row>
+    <row r="9" ht="15" spans="2:13">
       <c r="B9" s="41" t="s">
         <v>57</v>
       </c>
@@ -5028,11 +4943,11 @@
       <c r="F9" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="87"/>
-    </row>
-    <row r="10" customHeight="1" spans="2:13">
+      <c r="K9" s="79"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="86"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>59</v>
       </c>
@@ -5044,11 +4959,11 @@
       <c r="F10" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="78"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="86"/>
-    </row>
-    <row r="11" spans="2:13">
+      <c r="K10" s="77"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="85"/>
+    </row>
+    <row r="11" ht="15" spans="2:13">
       <c r="B11" s="41" t="s">
         <v>61</v>
       </c>
@@ -5060,11 +4975,11 @@
       <c r="F11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="87"/>
-    </row>
-    <row r="12" spans="2:13">
+      <c r="K11" s="79"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="86"/>
+    </row>
+    <row r="12" ht="14.25" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>63</v>
       </c>
@@ -5076,11 +4991,11 @@
       <c r="F12" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="78"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="86"/>
-    </row>
-    <row r="13" spans="2:13">
+      <c r="K12" s="77"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="85"/>
+    </row>
+    <row r="13" ht="15" spans="2:13">
       <c r="B13" s="41" t="s">
         <v>65</v>
       </c>
@@ -5092,12 +5007,12 @@
       <c r="F13" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="87"/>
-    </row>
-    <row r="14" spans="2:13">
+      <c r="G13" s="74"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="86"/>
+    </row>
+    <row r="14" ht="14.25" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>68</v>
       </c>
@@ -5105,11 +5020,11 @@
       <c r="D14" s="27"/>
       <c r="E14" s="27"/>
       <c r="F14" s="39"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="86"/>
-    </row>
-    <row r="15" spans="2:13">
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="85"/>
+    </row>
+    <row r="15" ht="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>69</v>
       </c>
@@ -5117,11 +5032,11 @@
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="42"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="87"/>
-    </row>
-    <row r="16" spans="2:13">
+      <c r="K15" s="79"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="86"/>
+    </row>
+    <row r="16" ht="14.25" spans="2:13">
       <c r="B16" s="38" t="s">
         <v>70</v>
       </c>
@@ -5129,11 +5044,11 @@
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="39"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="86"/>
-    </row>
-    <row r="17" spans="2:13">
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="85"/>
+    </row>
+    <row r="17" ht="15" spans="2:13">
       <c r="B17" s="41" t="s">
         <v>71</v>
       </c>
@@ -5141,11 +5056,11 @@
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="42"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="87"/>
-    </row>
-    <row r="18" spans="2:13">
+      <c r="K17" s="79"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="86"/>
+    </row>
+    <row r="18" ht="14.25" spans="2:13">
       <c r="B18" s="38" t="s">
         <v>72</v>
       </c>
@@ -5153,11 +5068,11 @@
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
       <c r="F18" s="39"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="86"/>
-    </row>
-    <row r="19" spans="2:13">
+      <c r="K18" s="77"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="85"/>
+    </row>
+    <row r="19" ht="15" spans="2:13">
       <c r="B19" s="41" t="s">
         <v>73</v>
       </c>
@@ -5165,11 +5080,11 @@
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="42"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="87"/>
-    </row>
-    <row r="20" spans="2:13">
+      <c r="K19" s="79"/>
+      <c r="L19" s="80"/>
+      <c r="M19" s="86"/>
+    </row>
+    <row r="20" ht="14.25" spans="2:13">
       <c r="B20" s="38" t="s">
         <v>74</v>
       </c>
@@ -5177,11 +5092,11 @@
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
       <c r="F20" s="39"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="86"/>
-    </row>
-    <row r="21" spans="2:13">
+      <c r="K20" s="77"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="85"/>
+    </row>
+    <row r="21" ht="15" spans="2:13">
       <c r="B21" s="41" t="s">
         <v>75</v>
       </c>
@@ -5189,23 +5104,23 @@
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
       <c r="F21" s="42"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="87"/>
-    </row>
-    <row r="22" ht="15.75" spans="2:13">
+      <c r="K21" s="79"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="86"/>
+    </row>
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="44"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="88"/>
-    </row>
-    <row r="23" ht="15.75"/>
+      <c r="K22" s="82"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="87"/>
+    </row>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5261,13 +5176,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.85" customWidth="1"/>
     <col min="7" max="7" width="8.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -5281,12 +5196,12 @@
       <c r="E2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="65"/>
-    </row>
-    <row r="3" ht="15.75" spans="2:8">
+      <c r="H2" s="64"/>
+    </row>
+    <row r="3" ht="15" spans="2:8">
       <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5297,18 +5212,18 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>80</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="2:5">
@@ -5322,14 +5237,14 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="2:5">
       <c r="B5" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5340,14 +5255,14 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:5">
       <c r="B6" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5358,14 +5273,14 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="2:5">
       <c r="B7" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5376,14 +5291,14 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="2:5">
       <c r="B8" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
@@ -5394,14 +5309,14 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="2:5">
       <c r="B9" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
@@ -5412,14 +5327,14 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:5">
       <c r="B10" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5430,14 +5345,14 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
       <c r="B11" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5448,14 +5363,14 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="2:5">
       <c r="B12" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5466,14 +5381,14 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="2:5">
       <c r="B13" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
@@ -5484,14 +5399,14 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="2:5">
       <c r="B14" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
@@ -5502,14 +5417,14 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:5">
       <c r="B15" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5520,14 +5435,14 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:5">
       <c r="B16" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5538,14 +5453,14 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:5">
       <c r="B17" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5556,14 +5471,14 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:5">
       <c r="B18" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
@@ -5574,14 +5489,14 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:5">
       <c r="B19" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5592,14 +5507,14 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:5">
       <c r="B20" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
@@ -5610,14 +5525,14 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:5">
       <c r="B21" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
@@ -5628,14 +5543,14 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:5">
       <c r="B22" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
@@ -5646,14 +5561,14 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:5">
       <c r="B23" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
@@ -5664,11 +5579,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5682,14 +5597,14 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:5">
       <c r="B25" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
@@ -5700,11 +5615,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5718,14 +5633,14 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:5">
       <c r="B27" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
@@ -5736,14 +5651,14 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:5">
       <c r="B28" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5754,14 +5669,14 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:5">
       <c r="B29" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
@@ -5772,14 +5687,14 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:5">
       <c r="B30" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
@@ -5790,32 +5705,32 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" spans="2:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="2:5">
       <c r="B31" s="43" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
       </c>
-      <c r="C31" s="50">
+      <c r="C31" s="49">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>6</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5834,7 +5749,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.425" customWidth="1"/>
@@ -5842,7 +5757,7 @@
     <col min="5" max="5" width="10.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="24" t="s">
         <v>81</v>
@@ -5853,7 +5768,7 @@
       <c r="D2" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="70" t="s">
         <v>83</v>
       </c>
       <c r="G2" s="35" t="s">
@@ -5861,11 +5776,11 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="68" t="s">
+    <row r="3" ht="14.25" spans="2:8">
+      <c r="B3" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="67" t="s">
         <v>86</v>
       </c>
       <c r="D3" s="27">
@@ -5882,7 +5797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" ht="15" spans="2:8">
       <c r="B4" s="30" t="s">
         <v>87</v>
       </c>
@@ -5903,8 +5818,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="68" t="s">
+    <row r="5" ht="14.25" spans="2:8">
+      <c r="B5" s="67" t="s">
         <v>88</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -5924,7 +5839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" ht="15" spans="2:8">
       <c r="B6" s="30" t="s">
         <v>90</v>
       </c>
@@ -5945,9 +5860,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15.75" spans="1:8">
-      <c r="A7" s="69"/>
-      <c r="B7" s="68" t="s">
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7" s="68"/>
+      <c r="B7" s="67" t="s">
         <v>91</v>
       </c>
       <c r="C7" s="26" t="s">
@@ -5960,7 +5875,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F7" s="69"/>
+      <c r="F7" s="68"/>
       <c r="G7" s="43">
         <v>5</v>
       </c>
@@ -5983,8 +5898,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="68" t="s">
+    <row r="9" ht="14.25" spans="2:5">
+      <c r="B9" s="67" t="s">
         <v>93</v>
       </c>
       <c r="C9" s="26" t="s">
@@ -5998,7 +5913,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
+    <row r="10" ht="15" spans="2:5">
       <c r="B10" s="30" t="s">
         <v>94</v>
       </c>
@@ -6013,8 +5928,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="68" t="s">
+    <row r="11" ht="14.25" spans="2:5">
+      <c r="B11" s="67" t="s">
         <v>95</v>
       </c>
       <c r="C11" s="26" t="s">
@@ -6028,7 +5943,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" ht="15" spans="2:5">
       <c r="B12" s="30" t="s">
         <v>96</v>
       </c>
@@ -6043,8 +5958,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="68" t="s">
+    <row r="13" ht="14.25" spans="2:7">
+      <c r="B13" s="67" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="26" t="s">
@@ -6061,7 +5976,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" ht="15" spans="2:5">
       <c r="B14" s="30" t="s">
         <v>99</v>
       </c>
@@ -6076,8 +5991,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="68" t="s">
+    <row r="15" ht="14.25" spans="2:5">
+      <c r="B15" s="67" t="s">
         <v>100</v>
       </c>
       <c r="C15" s="26" t="s">
@@ -6091,7 +6006,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="15" spans="2:5">
       <c r="B16" s="30" t="s">
         <v>102</v>
       </c>
@@ -6106,8 +6021,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="68"/>
+    <row r="17" ht="14.25" spans="2:5">
+      <c r="B17" s="67"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
       <c r="E17" s="37" t="str">
@@ -6115,7 +6030,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" ht="15" spans="2:5">
       <c r="B18" s="30"/>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -6124,8 +6039,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="68"/>
+    <row r="19" ht="14.25" spans="2:5">
+      <c r="B19" s="67"/>
       <c r="C19" s="26"/>
       <c r="D19" s="27"/>
       <c r="E19" s="37" t="str">
@@ -6133,7 +6048,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" ht="15" spans="2:5">
       <c r="B20" s="30"/>
       <c r="C20" s="28"/>
       <c r="D20" s="29"/>
@@ -6142,8 +6057,8 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="68"/>
+    <row r="21" ht="14.25" spans="2:5">
+      <c r="B21" s="67"/>
       <c r="C21" s="26"/>
       <c r="D21" s="27"/>
       <c r="E21" s="37" t="str">
@@ -6151,7 +6066,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" ht="15" spans="2:5">
       <c r="B22" s="30"/>
       <c r="C22" s="28"/>
       <c r="D22" s="29"/>
@@ -6160,8 +6075,8 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="68"/>
+    <row r="23" ht="14.25" spans="2:5">
+      <c r="B23" s="67"/>
       <c r="C23" s="26"/>
       <c r="D23" s="27"/>
       <c r="E23" s="37" t="str">
@@ -6169,7 +6084,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" ht="15" spans="2:5">
       <c r="B24" s="30"/>
       <c r="C24" s="28"/>
       <c r="D24" s="29"/>
@@ -6178,8 +6093,8 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="68"/>
+    <row r="25" ht="14.25" spans="2:5">
+      <c r="B25" s="67"/>
       <c r="C25" s="26"/>
       <c r="D25" s="27"/>
       <c r="E25" s="37" t="str">
@@ -6187,7 +6102,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" ht="15" spans="2:5">
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29"/>
@@ -6196,8 +6111,8 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="68"/>
+    <row r="27" ht="14.25" spans="2:5">
+      <c r="B27" s="67"/>
       <c r="C27" s="26"/>
       <c r="D27" s="27"/>
       <c r="E27" s="37" t="str">
@@ -6205,7 +6120,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="15" spans="2:5">
       <c r="B28" s="30"/>
       <c r="C28" s="28"/>
       <c r="D28" s="29"/>
@@ -6214,8 +6129,8 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="68"/>
+    <row r="29" ht="14.25" spans="2:5">
+      <c r="B29" s="67"/>
       <c r="C29" s="26"/>
       <c r="D29" s="27"/>
       <c r="E29" s="37" t="str">
@@ -6223,7 +6138,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="15" spans="2:5">
       <c r="B30" s="30"/>
       <c r="C30" s="28"/>
       <c r="D30" s="29"/>
@@ -6232,8 +6147,8 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="68"/>
+    <row r="31" ht="14.25" spans="2:5">
+      <c r="B31" s="67"/>
       <c r="C31" s="26"/>
       <c r="D31" s="27"/>
       <c r="E31" s="37" t="str">
@@ -6241,7 +6156,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" ht="15" spans="2:5">
       <c r="B32" s="30"/>
       <c r="C32" s="28"/>
       <c r="D32" s="29"/>
@@ -6250,8 +6165,8 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="68"/>
+    <row r="33" ht="14.25" spans="2:5">
+      <c r="B33" s="67"/>
       <c r="C33" s="26"/>
       <c r="D33" s="27"/>
       <c r="E33" s="37" t="str">
@@ -6259,7 +6174,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" ht="15" spans="2:5">
       <c r="B34" s="30"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
@@ -6268,8 +6183,8 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="70"/>
+    <row r="35" ht="14.25" spans="2:5">
+      <c r="B35" s="69"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
       <c r="E35" s="47" t="str">
@@ -6294,24 +6209,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.1416666666667" customWidth="1"/>
     <col min="4" max="4" width="17.7083333333333" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:6">
       <c r="B2" s="35" t="s">
         <v>103</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
-      <c r="E2" s="63"/>
+      <c r="E2" s="62"/>
       <c r="F2" s="36"/>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" ht="14.25" spans="2:6">
       <c r="B3" s="38" t="s">
         <v>23</v>
       </c>
@@ -6328,9 +6243,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="49" t="s">
-        <v>106</v>
+    <row r="4" ht="15" spans="2:6">
+      <c r="B4" s="41" t="s">
+        <v>29</v>
       </c>
       <c r="C4" s="29">
         <v>10</v>
@@ -6345,26 +6260,26 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:6">
+    <row r="5" ht="15" spans="2:6">
       <c r="B5" s="43"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="64"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="63"/>
       <c r="F5" s="44"/>
     </row>
-    <row r="6" ht="16.5"/>
+    <row r="6" ht="15"/>
     <row r="7" ht="15.75" spans="2:8">
-      <c r="B7" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="65"/>
-    </row>
-    <row r="8" spans="2:8">
+      <c r="B7" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="64"/>
+    </row>
+    <row r="8" ht="14.25" spans="2:8">
       <c r="B8" s="38" t="s">
         <v>23</v>
       </c>
@@ -6372,7 +6287,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>27</v>
@@ -6387,45 +6302,45 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" ht="15" spans="2:8">
       <c r="B9" s="41" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="H9" s="42" t="s">
+    </row>
+    <row r="10" ht="14.25" spans="2:8">
+      <c r="B10" s="38" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="38" t="s">
+      <c r="C10" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>113</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>114</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="37">
         <v>2</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
+    </row>
+    <row r="11" ht="15" spans="2:8">
       <c r="B11" s="41"/>
       <c r="C11" s="29"/>
       <c r="D11" s="29"/>
@@ -6434,7 +6349,7 @@
       <c r="G11" s="40"/>
       <c r="H11" s="42"/>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" ht="14.25" spans="2:8">
       <c r="B12" s="38"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -6445,17 +6360,17 @@
     </row>
     <row r="13" ht="15.75" spans="2:8">
       <c r="B13" s="45"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
       <c r="H13" s="46"/>
     </row>
-    <row r="14" ht="16.5"/>
+    <row r="14" ht="15"/>
     <row r="15" ht="15.75" spans="2:9">
       <c r="B15" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -6465,36 +6380,36 @@
       <c r="H15" s="48"/>
       <c r="I15" s="36"/>
     </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="54" t="s">
+    <row r="16" ht="14.25" spans="2:9">
+      <c r="B16" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55" t="s">
+      <c r="D16" s="54"/>
+      <c r="E16" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="F16" s="55" t="s">
+      <c r="G16" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="55" t="s">
+      <c r="I16" s="66" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="2:9">
+      <c r="B17" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I16" s="67" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="93" t="s">
         <v>119</v>
-      </c>
-      <c r="C17" s="94" t="s">
-        <v>120</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="29">
@@ -6515,36 +6430,36 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="54" t="s">
+    <row r="18" ht="14.25" spans="2:9">
+      <c r="B18" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="D18" s="54"/>
+      <c r="E18" s="54">
+        <v>1</v>
+      </c>
+      <c r="F18" s="54">
+        <v>2</v>
+      </c>
+      <c r="G18" s="54">
+        <f>PRODUCT(E18:F18)</f>
+        <v>2</v>
+      </c>
+      <c r="H18" s="54"/>
+      <c r="I18" s="66">
+        <f>PRODUCT(H18,E18)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="2:9">
+      <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55">
-        <v>2</v>
-      </c>
-      <c r="F18" s="55">
-        <v>2</v>
-      </c>
-      <c r="G18" s="55">
-        <f>PRODUCT(E18:F18)</f>
-        <v>4</v>
-      </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="67">
-        <f>PRODUCT(H18,E18)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="29">
@@ -6563,31 +6478,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55">
+    <row r="20" ht="14.25" spans="2:9">
+      <c r="B20" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54">
         <v>1</v>
       </c>
-      <c r="F20" s="55">
-        <v>2</v>
-      </c>
-      <c r="G20" s="55">
+      <c r="F20" s="54">
+        <v>2</v>
+      </c>
+      <c r="G20" s="54">
         <f>PRODUCT(E20:F20)</f>
         <v>2</v>
       </c>
-      <c r="H20" s="55"/>
-      <c r="I20" s="67">
+      <c r="H20" s="54"/>
+      <c r="I20" s="66">
         <f>PRODUCT(H20,E20)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -6603,17 +6518,17 @@
       <c r="H21" s="29"/>
       <c r="I21" s="42"/>
     </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="67"/>
-    </row>
-    <row r="23" spans="2:9">
+    <row r="22" ht="14.25" spans="2:9">
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="66"/>
+    </row>
+    <row r="23" ht="15" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -6623,17 +6538,17 @@
       <c r="H23" s="29"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="54"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="67"/>
-    </row>
-    <row r="25" spans="2:9">
+    <row r="24" ht="14.25" spans="2:9">
+      <c r="B24" s="53"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="66"/>
+    </row>
+    <row r="25" ht="15" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -6643,17 +6558,17 @@
       <c r="H25" s="29"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="67"/>
-    </row>
-    <row r="27" spans="2:9">
+    <row r="26" ht="14.25" spans="2:9">
+      <c r="B26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="66"/>
+    </row>
+    <row r="27" ht="15" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -6663,62 +6578,62 @@
       <c r="H27" s="29"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="67"/>
+    <row r="28" ht="14.25" spans="2:9">
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="66"/>
     </row>
     <row r="29" ht="15.75" spans="2:9">
       <c r="B29" s="7"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
       <c r="I29" s="46"/>
     </row>
-    <row r="30" ht="15.75"/>
-    <row r="31" ht="15.75"/>
+    <row r="30" ht="14.25"/>
+    <row r="31" ht="14.25"/>
     <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="57">
+        <v>125</v>
+      </c>
+      <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D32" s="2">
         <f>Clebina!C3*3</f>
         <v>48</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="2:4">
-      <c r="B33" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="59">
+    <row r="33" ht="15" customHeight="1" spans="2:4">
+      <c r="B33" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="58">
         <f>Clebina!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D33" s="60"/>
+      <c r="D33" s="59"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="61" t="str">
+        <v>127</v>
+      </c>
+      <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D34" s="62"/>
-    </row>
-    <row r="35" ht="15.75"/>
+      <c r="D34" s="61"/>
+    </row>
+    <row r="35" ht="14.25"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6750,7 +6665,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
@@ -6767,22 +6682,22 @@
     <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
-    <row r="2" customHeight="1" spans="2:16">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>129</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>130</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>131</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>132</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6791,31 +6706,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>79</v>
       </c>
       <c r="K2" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="O2" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="36"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>138</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>139</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6837,13 +6752,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="M3" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6852,12 +6767,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>144</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6879,13 +6794,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>140</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6894,12 +6809,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:16">
+    <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>146</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6921,13 +6836,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L5" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M5" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>71</v>
@@ -6938,10 +6853,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6963,21 +6878,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M6" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6999,25 +6914,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L7" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M7" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O7" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="P7" s="36"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>150</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>151</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7039,13 +6954,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -7055,12 +6970,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>152</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>153</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7082,13 +6997,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -7098,12 +7013,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7125,13 +7040,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L10" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M10" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7141,12 +7056,12 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7168,13 +7083,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M11" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7184,12 +7099,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>156</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>157</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7211,13 +7126,13 @@
         <v>5</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7229,10 +7144,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7254,13 +7169,13 @@
         <v>2</v>
       </c>
       <c r="K13" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="M13" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7272,10 +7187,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7297,21 +7212,21 @@
         <v>10</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7333,21 +7248,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L15" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M15" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7369,21 +7284,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L16" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M16" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7405,25 +7320,25 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L17" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M17" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7445,21 +7360,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7481,21 +7396,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13">
+    </row>
+    <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7517,21 +7432,21 @@
         <v>2</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>80</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7553,21 +7468,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7591,21 +7506,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7627,21 +7542,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13">
+    </row>
+    <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7663,21 +7578,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7699,21 +7614,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7735,21 +7650,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7773,21 +7688,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7809,21 +7724,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="L28" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
+    </row>
+    <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7845,21 +7760,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L29" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M29" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7881,21 +7796,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7917,21 +7832,21 @@
         <v>6</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L31" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13">
+    </row>
+    <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7953,21 +7868,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L32" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L32" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M32" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7989,13 +7904,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -8016,7 +7931,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
@@ -8033,22 +7948,22 @@
     <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
-    <row r="2" customHeight="1" spans="2:16">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>129</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>130</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>131</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>132</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -8057,31 +7972,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>79</v>
       </c>
       <c r="K2" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="O2" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="36"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>138</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>139</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8103,13 +8018,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="M3" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8118,12 +8033,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>144</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8145,13 +8060,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>140</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8160,12 +8075,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:16">
+    <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>146</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8187,13 +8102,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L5" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M5" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>71</v>
@@ -8204,10 +8119,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8229,21 +8144,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M6" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8265,25 +8180,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L7" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M7" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O7" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="P7" s="36"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>150</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>151</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8305,13 +8220,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8321,12 +8236,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>152</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>153</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8348,13 +8263,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8364,12 +8279,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8391,13 +8306,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L10" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L10" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M10" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8407,12 +8322,12 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8434,13 +8349,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M11" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8450,12 +8365,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>156</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>157</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8477,13 +8392,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M12" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8495,10 +8410,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8520,13 +8435,13 @@
         <v>4</v>
       </c>
       <c r="K13" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="M13" s="37" t="s">
         <v>141</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>142</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8538,10 +8453,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8565,21 +8480,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8601,21 +8516,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L15" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M15" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8637,21 +8552,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L16" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L16" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M16" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8673,21 +8588,21 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L17" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M17" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8709,21 +8624,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8745,21 +8660,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13">
+    </row>
+    <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8781,21 +8696,21 @@
         <v>4</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>80</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8817,21 +8732,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8855,21 +8770,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8891,21 +8806,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13">
+    </row>
+    <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8927,21 +8842,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8963,21 +8878,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8999,21 +8914,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9037,21 +8952,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9073,21 +8988,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="L28" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
+    </row>
+    <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9109,21 +9024,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="L29" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M29" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9145,21 +9060,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9181,21 +9096,21 @@
         <v>8</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L31" s="27" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9217,21 +9132,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="L32" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="L32" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M32" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9253,13 +9168,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -9280,7 +9195,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.2833333333333" customWidth="1"/>
     <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
@@ -9289,10 +9204,10 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9302,23 +9217,23 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="J2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" ht="14.25" spans="2:13">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9342,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
@@ -9372,13 +9287,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="2:10">
+    <row r="5" ht="15" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9396,7 +9311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" ht="15" spans="2:10">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9414,7 +9329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" ht="14.25" spans="2:10">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9450,7 +9365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="8:10">
+    <row r="9" ht="15" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9462,7 +9377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" ht="15" spans="8:10">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
@@ -9474,7 +9389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="8:10">
+    <row r="11" ht="15" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9488,7 +9403,7 @@
     </row>
     <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9505,9 +9420,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" ht="14.25" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9538,7 +9453,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="8:10">
+    <row r="15" ht="15.75" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9552,13 +9467,13 @@
     </row>
     <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>79</v>
@@ -9574,7 +9489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" ht="15" spans="2:10">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9597,7 +9512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" ht="15" spans="2:10">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9620,7 +9535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" ht="15" spans="2:10">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9643,7 +9558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" ht="15" spans="2:10">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9666,7 +9581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" ht="15" spans="2:10">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9714,7 +9629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="15.75"/>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7635" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12315" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -152,22 +152,14 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="9"/>
             <rFont val="Segoe UI"/>
             <charset val="134"/>
           </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Invenção Potente - Quando usa um item fabricado por você mesmo, você pode pagar 1 PM para
-aumentar em +2 a CD para resistir a ele.</t>
+          <t>Você recebe proficiência com armas
+marciais corpo a corpo. Quando usa uma arma corpo a corpo, pode usar seu modificador de Inteligência em
+vez de Força nos testes de ataque e rolagens de dano.
+Pré-requisitos: treinado em Luta e Ofício (armeiro).</t>
         </r>
       </text>
     </comment>
@@ -275,10 +267,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-Aumento de Atributo. Você recebe +2 em um
-atributo a sua escolha. Você pode escolher este poder
-várias vezes. A partir da segunda vez que escolhê-lo
-para o mesmo atributo, o aumento diminui para +1.</t>
+Invenção Potente - Quando usa um item fabricado por você mesmo, você pode pagar 1 PM para
+aumentar em +2 a CD para resistir a ele.</t>
         </r>
       </text>
     </comment>
@@ -969,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="186">
   <si>
     <t>Atributos</t>
   </si>
@@ -1121,39 +1111,36 @@
     <t>Nível 5</t>
   </si>
   <si>
+    <t>Armeiro</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Venefício</t>
+  </si>
+  <si>
+    <t>Nível 6</t>
+  </si>
+  <si>
+    <t>Alquimista de Batalha</t>
+  </si>
+  <si>
+    <t>Divindade</t>
+  </si>
+  <si>
+    <t>Voz da Civilização</t>
+  </si>
+  <si>
+    <t>Nível 7</t>
+  </si>
+  <si>
     <t>Invenção Potente</t>
   </si>
   <si>
-    <t>Origem</t>
-  </si>
-  <si>
-    <t>Venefício</t>
-  </si>
-  <si>
-    <t>Nível 6</t>
-  </si>
-  <si>
-    <t>Alquimista de Batalha</t>
-  </si>
-  <si>
-    <t>Divindade</t>
-  </si>
-  <si>
-    <t>Voz da Civilização</t>
-  </si>
-  <si>
-    <t>Nível 7</t>
-  </si>
-  <si>
-    <t>Aumento de Atributo</t>
-  </si>
-  <si>
     <t>Nível 8</t>
   </si>
   <si>
-    <t>Armeiro</t>
-  </si>
-  <si>
     <t>Nível 9</t>
   </si>
   <si>
@@ -1263,9 +1250,6 @@
   </si>
   <si>
     <t>Controlar Madeira</t>
-  </si>
-  <si>
-    <t>disc</t>
   </si>
   <si>
     <t>Enxame de Pesteste</t>
@@ -1540,9 +1524,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="27">
@@ -1581,31 +1565,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1627,6 +1588,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
@@ -1634,7 +1611,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1647,9 +1624,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1678,19 +1663,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1709,16 +1693,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1770,7 +1754,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1782,7 +1784,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1794,13 +1796,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1812,7 +1820,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1824,31 +1832,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1860,61 +1892,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1926,31 +1922,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2473,6 +2457,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2488,35 +2496,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2541,17 +2531,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2573,152 +2557,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2921,6 +2905,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4341,7 +4326,7 @@
       </c>
       <c r="G2" s="48">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="36"/>
       <c r="K2" s="35" t="s">
@@ -4368,11 +4353,11 @@
       </c>
       <c r="G3" s="27">
         <f>H3-L25-SUM(L4:L22)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H3" s="39">
         <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K3" s="38" t="s">
         <v>6</v>
@@ -4404,11 +4389,11 @@
       </c>
       <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K4" s="41">
         <v>1</v>
@@ -4438,7 +4423,7 @@
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="89"/>
+      <c r="H5" s="90"/>
       <c r="K5" s="38">
         <v>2</v>
       </c>
@@ -4467,7 +4452,7 @@
         <f>G5+Perícias!J12</f>
         <v>27</v>
       </c>
-      <c r="H6" s="90"/>
+      <c r="H6" s="91"/>
       <c r="K6" s="41">
         <v>3</v>
       </c>
@@ -4496,7 +4481,7 @@
         <f>Perícias!J27+Perícias!J21</f>
         <v>17</v>
       </c>
-      <c r="H7" s="89"/>
+      <c r="H7" s="90"/>
       <c r="K7" s="38">
         <v>4</v>
       </c>
@@ -4521,10 +4506,10 @@
       <c r="F8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="92">
         <v>0.5</v>
       </c>
-      <c r="H8" s="92"/>
+      <c r="H8" s="93"/>
       <c r="K8" s="41">
         <v>5</v>
       </c>
@@ -4554,7 +4539,7 @@
         <v>19</v>
       </c>
       <c r="G10" s="52">
-        <v>6600</v>
+        <v>10700</v>
       </c>
       <c r="H10" s="46"/>
       <c r="K10" s="41">
@@ -4573,16 +4558,16 @@
       <c r="N11" s="39"/>
     </row>
     <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
       <c r="K12" s="41">
         <v>9</v>
       </c>
@@ -4591,7 +4576,7 @@
       <c r="N12" s="42"/>
     </row>
     <row r="13" ht="15.75" spans="2:14">
-      <c r="B13" s="88"/>
+      <c r="B13" s="89"/>
       <c r="K13" s="38">
         <v>10</v>
       </c>
@@ -4782,7 +4767,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
@@ -4791,24 +4776,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73"/>
-      <c r="I1" s="71" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="74"/>
+      <c r="I1" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74"/>
     </row>
     <row r="2" ht="15"/>
     <row r="3" ht="15.75" spans="2:13">
@@ -4821,13 +4806,13 @@
       </c>
       <c r="E3" s="48"/>
       <c r="F3" s="36"/>
-      <c r="K3" s="75" t="s">
+      <c r="K3" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="84" t="s">
+      <c r="M3" s="85" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4843,13 +4828,13 @@
       <c r="F4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="77" t="s">
+      <c r="K4" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="78" t="s">
+      <c r="L4" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="85"/>
+      <c r="M4" s="86"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:13">
       <c r="B5" s="41" t="s">
@@ -4863,13 +4848,13 @@
       <c r="F5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="79" t="s">
+      <c r="K5" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="80" t="s">
+      <c r="L5" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="86"/>
+      <c r="M5" s="87"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="2:13">
       <c r="B6" s="38" t="s">
@@ -4883,13 +4868,13 @@
       <c r="F6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="77" t="s">
+      <c r="K6" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="78" t="s">
+      <c r="L6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="85"/>
+      <c r="M6" s="86"/>
     </row>
     <row r="7" ht="15" spans="2:13">
       <c r="B7" s="41" t="s">
@@ -4903,13 +4888,13 @@
       <c r="F7" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="79" t="s">
+      <c r="K7" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="80" t="s">
+      <c r="L7" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="86"/>
+      <c r="M7" s="87"/>
     </row>
     <row r="8" ht="14.25" spans="2:13">
       <c r="B8" s="38" t="s">
@@ -4923,13 +4908,13 @@
       <c r="F8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="77" t="s">
+      <c r="K8" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="81" t="s">
+      <c r="L8" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="85"/>
+      <c r="M8" s="86"/>
     </row>
     <row r="9" ht="15" spans="2:13">
       <c r="B9" s="41" t="s">
@@ -4943,9 +4928,9 @@
       <c r="F9" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="79"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="86"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="87"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:13">
       <c r="B10" s="38" t="s">
@@ -4953,174 +4938,173 @@
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="27" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="77"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="85"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="86"/>
     </row>
     <row r="11" ht="15" spans="2:13">
       <c r="B11" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="79"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="86"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="87"/>
     </row>
     <row r="12" ht="14.25" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="27"/>
       <c r="D12" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="85"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="86"/>
     </row>
     <row r="13" ht="15" spans="2:13">
       <c r="B13" s="41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" s="29"/>
       <c r="F13" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="74"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="86"/>
+        <v>66</v>
+      </c>
+      <c r="G13" s="75"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="87"/>
     </row>
     <row r="14" ht="14.25" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="27"/>
       <c r="E14" s="27"/>
       <c r="F14" s="39"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="85"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="86"/>
     </row>
     <row r="15" ht="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="42"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="86"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="87"/>
     </row>
     <row r="16" ht="14.25" spans="2:13">
       <c r="B16" s="38" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
       <c r="E16" s="27"/>
       <c r="F16" s="39"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="85"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="86"/>
     </row>
     <row r="17" ht="15" spans="2:13">
       <c r="B17" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="29"/>
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="42"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="86"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="87"/>
     </row>
     <row r="18" ht="14.25" spans="2:13">
       <c r="B18" s="38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="27"/>
       <c r="E18" s="27"/>
       <c r="F18" s="39"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="85"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="86"/>
     </row>
     <row r="19" ht="15" spans="2:13">
       <c r="B19" s="41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="42"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="86"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="87"/>
     </row>
     <row r="20" ht="14.25" spans="2:13">
       <c r="B20" s="38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="27"/>
       <c r="E20" s="27"/>
       <c r="F20" s="39"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="85"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="86"/>
     </row>
     <row r="21" ht="15" spans="2:13">
       <c r="B21" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
       <c r="F21" s="42"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="86"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="87"/>
     </row>
     <row r="22" ht="15" spans="2:13">
       <c r="B22" s="43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="49"/>
       <c r="E22" s="49"/>
       <c r="F22" s="44"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="87"/>
-    </row>
-    <row r="23" ht="14.25"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="88"/>
+    </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5188,16 +5172,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>79</v>
-      </c>
       <c r="G2" s="50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="64"/>
     </row>
@@ -5212,18 +5196,18 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="2:5">
@@ -5237,11 +5221,11 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="2:5">
@@ -5255,11 +5239,11 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:5">
@@ -5273,11 +5257,11 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="2:5">
@@ -5291,11 +5275,11 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="15" spans="2:5">
@@ -5309,11 +5293,11 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="2:5">
@@ -5327,11 +5311,11 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:5">
@@ -5345,11 +5329,11 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="2:5">
@@ -5363,11 +5347,11 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:5">
@@ -5381,11 +5365,11 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="2:5">
@@ -5399,11 +5383,11 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="15" spans="2:5">
@@ -5417,11 +5401,11 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:5">
@@ -5435,11 +5419,11 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:5">
@@ -5453,11 +5437,11 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:5">
@@ -5471,11 +5455,11 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:5">
@@ -5489,11 +5473,11 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:5">
@@ -5507,11 +5491,11 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:5">
@@ -5525,11 +5509,11 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:5">
@@ -5543,11 +5527,11 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:5">
@@ -5561,11 +5545,11 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:5">
@@ -5579,11 +5563,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5597,11 +5581,11 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:5">
@@ -5615,11 +5599,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5633,11 +5617,11 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:5">
@@ -5651,11 +5635,11 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:5">
@@ -5669,11 +5653,11 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:5">
@@ -5687,11 +5671,11 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:5">
@@ -5705,11 +5689,11 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" ht="15" spans="2:5">
@@ -5723,11 +5707,11 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" ht="14.25"/>
@@ -5760,28 +5744,28 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="G2" s="35" t="s">
         <v>83</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>84</v>
       </c>
       <c r="H2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:8">
       <c r="B3" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="67" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>86</v>
       </c>
       <c r="D3" s="27">
         <v>1</v>
@@ -5799,10 +5783,10 @@
     </row>
     <row r="4" ht="15" spans="2:8">
       <c r="B4" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" s="29">
         <v>1</v>
@@ -5820,10 +5804,10 @@
     </row>
     <row r="5" ht="14.25" spans="2:8">
       <c r="B5" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>89</v>
       </c>
       <c r="D5" s="27">
         <v>1</v>
@@ -5841,10 +5825,10 @@
     </row>
     <row r="6" ht="15" spans="2:8">
       <c r="B6" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6" s="29">
         <v>1</v>
@@ -5863,10 +5847,10 @@
     <row r="7" ht="15" spans="1:8">
       <c r="A7" s="68"/>
       <c r="B7" s="67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="27">
         <v>1</v>
@@ -5885,10 +5869,10 @@
     </row>
     <row r="8" ht="15.75" spans="2:5">
       <c r="B8" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="29">
         <v>1</v>
@@ -5898,12 +5882,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="2:5">
+    <row r="9" ht="14.25" spans="1:6">
+      <c r="A9" s="69"/>
       <c r="B9" s="67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="27">
         <v>1</v>
@@ -5912,13 +5897,14 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F9" s="69"/>
     </row>
     <row r="10" ht="15" spans="2:5">
       <c r="B10" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="29">
         <v>1</v>
@@ -5930,10 +5916,10 @@
     </row>
     <row r="11" ht="14.25" spans="2:5">
       <c r="B11" s="67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" s="27">
         <v>2</v>
@@ -5945,10 +5931,10 @@
     </row>
     <row r="12" ht="15" spans="2:5">
       <c r="B12" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="29">
         <v>1</v>
@@ -5958,12 +5944,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:7">
+    <row r="13" ht="14.25" spans="2:5">
       <c r="B13" s="67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" s="27">
         <v>2</v>
@@ -5972,16 +5958,13 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="G13" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="14" ht="15" spans="2:5">
       <c r="B14" s="30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="29">
         <v>2</v>
@@ -5993,10 +5976,10 @@
     </row>
     <row r="15" ht="14.25" spans="2:5">
       <c r="B15" s="67" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D15" s="27">
         <v>2</v>
@@ -6008,10 +5991,10 @@
     </row>
     <row r="16" ht="15" spans="2:5">
       <c r="B16" s="30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="29">
         <v>3</v>
@@ -6184,7 +6167,7 @@
       </c>
     </row>
     <row r="35" ht="14.25" spans="2:5">
-      <c r="B35" s="69"/>
+      <c r="B35" s="70"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
       <c r="E35" s="47" t="str">
@@ -6219,7 +6202,7 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:6">
       <c r="B2" s="35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -6237,10 +6220,10 @@
         <v>25</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:6">
@@ -6270,7 +6253,7 @@
     <row r="6" ht="15"/>
     <row r="7" ht="15.75" spans="2:8">
       <c r="B7" s="50" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
@@ -6287,13 +6270,13 @@
         <v>26</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>36</v>
@@ -6307,37 +6290,37 @@
         <v>30</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="2:8">
       <c r="B10" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>111</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>113</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="37">
         <v>2</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:8">
@@ -6370,7 +6353,7 @@
     <row r="14" ht="15"/>
     <row r="15" ht="15.75" spans="2:9">
       <c r="B15" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -6389,27 +6372,27 @@
       </c>
       <c r="D16" s="54"/>
       <c r="E16" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="54" t="s">
-        <v>117</v>
-      </c>
       <c r="I16" s="66" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="15" spans="2:9">
       <c r="B17" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="93" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="C17" s="94" t="s">
+        <v>117</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="29">
@@ -6432,10 +6415,10 @@
     </row>
     <row r="18" ht="14.25" spans="2:9">
       <c r="B18" s="53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D18" s="54"/>
       <c r="E18" s="54">
@@ -6456,10 +6439,10 @@
     </row>
     <row r="19" ht="15" spans="2:9">
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="29">
@@ -6480,7 +6463,7 @@
     </row>
     <row r="20" ht="14.25" spans="2:9">
       <c r="B20" s="53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
@@ -6502,7 +6485,7 @@
     </row>
     <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -6602,7 +6585,7 @@
     <row r="31" ht="14.25"/>
     <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
@@ -6615,7 +6598,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
       <c r="B33" s="57" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C33" s="58">
         <f>Clebina!C3*10</f>
@@ -6625,7 +6608,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
@@ -6685,19 +6668,19 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6706,31 +6689,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="M2" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="O2" s="35" t="s">
         <v>134</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="O2" s="35" t="s">
-        <v>136</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6752,13 +6735,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="M3" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6769,10 +6752,10 @@
     </row>
     <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6794,13 +6777,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M4" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6811,10 +6794,10 @@
     </row>
     <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6836,16 +6819,16 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O5" s="43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" s="44">
         <v>6</v>
@@ -6853,10 +6836,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6878,21 +6861,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6914,25 +6897,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6954,13 +6937,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -6972,10 +6955,10 @@
     </row>
     <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6997,13 +6980,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -7015,10 +6998,10 @@
     </row>
     <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7040,13 +7023,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7058,10 +7041,10 @@
     </row>
     <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7083,13 +7066,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7101,10 +7084,10 @@
     </row>
     <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7126,13 +7109,13 @@
         <v>5</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7144,10 +7127,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7169,13 +7152,13 @@
         <v>2</v>
       </c>
       <c r="K13" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="M13" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7187,10 +7170,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7212,21 +7195,21 @@
         <v>10</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7248,21 +7231,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7284,21 +7267,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7320,13 +7303,13 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
@@ -7335,10 +7318,10 @@
     </row>
     <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7360,21 +7343,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7396,21 +7379,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M19" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7432,21 +7415,21 @@
         <v>2</v>
       </c>
       <c r="K20" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L20" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L20" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M20" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7468,21 +7451,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7506,21 +7489,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7542,21 +7525,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L23" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M23" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7578,21 +7561,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7614,21 +7597,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7650,21 +7633,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7688,21 +7671,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7724,21 +7707,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L28" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L28" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M28" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7760,21 +7743,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7796,21 +7779,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7832,21 +7815,21 @@
         <v>6</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L31" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L31" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M31" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7868,21 +7851,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7904,13 +7887,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -7951,19 +7934,19 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -7972,31 +7955,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="M2" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="O2" s="35" t="s">
         <v>134</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="O2" s="35" t="s">
-        <v>136</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8018,13 +8001,13 @@
         <v>2</v>
       </c>
       <c r="K3" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="M3" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8035,10 +8018,10 @@
     </row>
     <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8060,13 +8043,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L4" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M4" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8077,10 +8060,10 @@
     </row>
     <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8102,16 +8085,16 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O5" s="43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" s="44">
         <v>6</v>
@@ -8119,10 +8102,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8144,21 +8127,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8180,25 +8163,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8220,13 +8203,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8238,10 +8221,10 @@
     </row>
     <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8263,13 +8246,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8281,10 +8264,10 @@
     </row>
     <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8306,13 +8289,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8324,10 +8307,10 @@
     </row>
     <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8349,13 +8332,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8367,10 +8350,10 @@
     </row>
     <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8392,13 +8375,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8410,10 +8393,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8435,13 +8418,13 @@
         <v>4</v>
       </c>
       <c r="K13" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="M13" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8453,10 +8436,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8480,21 +8463,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8516,21 +8499,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8552,21 +8535,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8588,21 +8571,21 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8624,21 +8607,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8660,21 +8643,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M19" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8696,21 +8679,21 @@
         <v>4</v>
       </c>
       <c r="K20" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L20" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L20" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M20" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8732,21 +8715,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8770,21 +8753,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8806,21 +8789,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="L23" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M23" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8842,21 +8825,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8878,21 +8861,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8914,21 +8897,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8952,21 +8935,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8988,21 +8971,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="L28" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L28" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M28" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9024,21 +9007,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9060,21 +9043,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9096,21 +9079,21 @@
         <v>8</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L31" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9132,21 +9115,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9168,13 +9151,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -9207,7 +9190,7 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9217,16 +9200,16 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="L2" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
@@ -9257,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
@@ -9287,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
@@ -9403,7 +9386,7 @@
     </row>
     <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9422,7 +9405,7 @@
     </row>
     <row r="13" ht="14.25" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9467,16 +9450,16 @@
     </row>
     <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H16" s="16">
         <v>91000</v>
@@ -9644,8 +9627,8 @@
   <commentList sheetStid="9">
     <comment s:ref="D5" rgbClr="217AA0"/>
     <comment s:ref="D6" rgbClr="E3E4E0"/>
-    <comment s:ref="D7" rgbClr="BDBBC0"/>
-    <comment s:ref="D9" rgbClr="77DE00"/>
+    <comment s:ref="D7" rgbClr="77DE00"/>
+    <comment s:ref="D9" rgbClr="BDBBC0"/>
   </commentList>
   <commentList sheetStid="6"/>
 </comments>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12315" activeTab="3"/>
+    <workbookView windowWidth="20490" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="190">
   <si>
     <t>Atributos</t>
   </si>
@@ -1051,234 +1051,237 @@
     <t>Armadura de Gelo Eterno</t>
   </si>
   <si>
+    <t>Alabarda</t>
+  </si>
+  <si>
+    <t>Status Anteriores</t>
+  </si>
+  <si>
+    <t>Poderes</t>
+  </si>
+  <si>
+    <t>Outros Poderes</t>
+  </si>
+  <si>
+    <t>Nível 1</t>
+  </si>
+  <si>
+    <t>Engenhosidade, protótipo</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Poder</t>
+  </si>
+  <si>
+    <t>Nível 2</t>
+  </si>
+  <si>
+    <t>Alquimista iniciado</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>Raça</t>
+  </si>
+  <si>
+    <t>Graça de Glorien</t>
+  </si>
+  <si>
+    <t>Nível 3</t>
+  </si>
+  <si>
+    <t>Engenhoqueiro</t>
+  </si>
+  <si>
+    <t>Sentidos Elficos</t>
+  </si>
+  <si>
+    <t>Nível 4</t>
+  </si>
+  <si>
+    <t>Síntese Rápida</t>
+  </si>
+  <si>
+    <t>Herança Férica</t>
+  </si>
+  <si>
+    <t>Nível 5</t>
+  </si>
+  <si>
+    <t>Armeiro</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Venefício</t>
+  </si>
+  <si>
+    <t>Nível 6</t>
+  </si>
+  <si>
+    <t>Alquimista de Batalha</t>
+  </si>
+  <si>
+    <t>Divindade</t>
+  </si>
+  <si>
+    <t>Voz da Civilização</t>
+  </si>
+  <si>
+    <t>Nível 7</t>
+  </si>
+  <si>
+    <t>Invenção Potente</t>
+  </si>
+  <si>
+    <t>Nível 8</t>
+  </si>
+  <si>
+    <t>Nível 9</t>
+  </si>
+  <si>
+    <t>Granadeiro</t>
+  </si>
+  <si>
+    <t>Nível 10</t>
+  </si>
+  <si>
+    <t>Mestre Alquimista</t>
+  </si>
+  <si>
+    <t>Nível 11</t>
+  </si>
+  <si>
+    <t>Magia Ilimitada</t>
+  </si>
+  <si>
+    <t>PNA</t>
+  </si>
+  <si>
+    <t>Nível 12</t>
+  </si>
+  <si>
+    <t>Nível 13</t>
+  </si>
+  <si>
+    <t>Nível 14</t>
+  </si>
+  <si>
+    <t>Nível 15</t>
+  </si>
+  <si>
+    <t>Nível 16</t>
+  </si>
+  <si>
+    <t>Nível 17</t>
+  </si>
+  <si>
+    <t>Nível 18</t>
+  </si>
+  <si>
+    <t>Nível 19</t>
+  </si>
+  <si>
+    <t>Nível 20</t>
+  </si>
+  <si>
+    <t>Teste</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Luta</t>
+  </si>
+  <si>
+    <t>Magia</t>
+  </si>
+  <si>
+    <t>Círculo</t>
+  </si>
+  <si>
+    <t>Custo</t>
+  </si>
+  <si>
+    <t>Custo Círculo</t>
+  </si>
+  <si>
+    <t>Curar Ferimentos</t>
+  </si>
+  <si>
+    <t>Divina</t>
+  </si>
+  <si>
+    <t>Consagrar</t>
+  </si>
+  <si>
+    <t>Imagem Espelhada</t>
+  </si>
+  <si>
+    <t>Arcana</t>
+  </si>
+  <si>
+    <t>Sono</t>
+  </si>
+  <si>
+    <t>Teia</t>
+  </si>
+  <si>
+    <t>Transmutar Objetos</t>
+  </si>
+  <si>
+    <t>Toque Chocante</t>
+  </si>
+  <si>
+    <t>Tranquilidade</t>
+  </si>
+  <si>
+    <t>Crânio voador de Vladislav</t>
+  </si>
+  <si>
+    <t>Concentração</t>
+  </si>
+  <si>
+    <t>Controlar Madeira</t>
+  </si>
+  <si>
+    <t>Enxame de Pesteste</t>
+  </si>
+  <si>
+    <t>Velocidade</t>
+  </si>
+  <si>
+    <t>Aracana</t>
+  </si>
+  <si>
+    <t>Transformação de Guerra</t>
+  </si>
+  <si>
+    <t>Armaduras</t>
+  </si>
+  <si>
+    <t>Preço</t>
+  </si>
+  <si>
+    <t>Peso</t>
+  </si>
+  <si>
+    <t>Armas</t>
+  </si>
+  <si>
+    <t>Modificação</t>
+  </si>
+  <si>
     <t>Ataque Desarmado</t>
   </si>
   <si>
-    <t>Status Anteriores</t>
-  </si>
-  <si>
-    <t>Poderes</t>
-  </si>
-  <si>
-    <t>Outros Poderes</t>
-  </si>
-  <si>
-    <t>Nível 1</t>
-  </si>
-  <si>
-    <t>Engenhosidade, protótipo</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Poder</t>
-  </si>
-  <si>
-    <t>Nível 2</t>
-  </si>
-  <si>
-    <t>Alquimista iniciado</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>Raça</t>
-  </si>
-  <si>
-    <t>Graça de Glorien</t>
-  </si>
-  <si>
-    <t>Nível 3</t>
-  </si>
-  <si>
-    <t>Engenhoqueiro</t>
-  </si>
-  <si>
-    <t>Sentidos Elficos</t>
-  </si>
-  <si>
-    <t>Nível 4</t>
-  </si>
-  <si>
-    <t>Síntese Rápida</t>
-  </si>
-  <si>
-    <t>Herança Férica</t>
-  </si>
-  <si>
-    <t>Nível 5</t>
-  </si>
-  <si>
-    <t>Armeiro</t>
-  </si>
-  <si>
-    <t>Origem</t>
-  </si>
-  <si>
-    <t>Venefício</t>
-  </si>
-  <si>
-    <t>Nível 6</t>
-  </si>
-  <si>
-    <t>Alquimista de Batalha</t>
-  </si>
-  <si>
-    <t>Divindade</t>
-  </si>
-  <si>
-    <t>Voz da Civilização</t>
-  </si>
-  <si>
-    <t>Nível 7</t>
-  </si>
-  <si>
-    <t>Invenção Potente</t>
-  </si>
-  <si>
-    <t>Nível 8</t>
-  </si>
-  <si>
-    <t>Nível 9</t>
-  </si>
-  <si>
-    <t>Granadeiro</t>
-  </si>
-  <si>
-    <t>Nível 10</t>
-  </si>
-  <si>
-    <t>Mestre Alquimista</t>
-  </si>
-  <si>
-    <t>Nível 11</t>
-  </si>
-  <si>
-    <t>Magia Ilimitada</t>
-  </si>
-  <si>
-    <t>PNA</t>
-  </si>
-  <si>
-    <t>Nível 12</t>
-  </si>
-  <si>
-    <t>Nível 13</t>
-  </si>
-  <si>
-    <t>Nível 14</t>
-  </si>
-  <si>
-    <t>Nível 15</t>
-  </si>
-  <si>
-    <t>Nível 16</t>
-  </si>
-  <si>
-    <t>Nível 17</t>
-  </si>
-  <si>
-    <t>Nível 18</t>
-  </si>
-  <si>
-    <t>Nível 19</t>
-  </si>
-  <si>
-    <t>Nível 20</t>
-  </si>
-  <si>
-    <t>Teste</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Luta</t>
-  </si>
-  <si>
-    <t>Magia</t>
-  </si>
-  <si>
-    <t>Círculo</t>
-  </si>
-  <si>
-    <t>Custo</t>
-  </si>
-  <si>
-    <t>Custo Círculo</t>
-  </si>
-  <si>
-    <t>Curar Ferimentos</t>
-  </si>
-  <si>
-    <t>Divina</t>
-  </si>
-  <si>
-    <t>Consagrar</t>
-  </si>
-  <si>
-    <t>Imagem Espelhada</t>
-  </si>
-  <si>
-    <t>Arcana</t>
-  </si>
-  <si>
-    <t>Sono</t>
-  </si>
-  <si>
-    <t>Teia</t>
-  </si>
-  <si>
-    <t>Transmutar Objetos</t>
-  </si>
-  <si>
-    <t>Toque Chocante</t>
-  </si>
-  <si>
-    <t>Tranquilidade</t>
-  </si>
-  <si>
-    <t>Crânio voador de Vladislav</t>
-  </si>
-  <si>
-    <t>Concentração</t>
-  </si>
-  <si>
-    <t>Controlar Madeira</t>
-  </si>
-  <si>
-    <t>Enxame de Pesteste</t>
-  </si>
-  <si>
-    <t>Velocidade</t>
-  </si>
-  <si>
-    <t>Aracana</t>
-  </si>
-  <si>
-    <t>Transformação de Guerra</t>
-  </si>
-  <si>
-    <t>Armaduras</t>
-  </si>
-  <si>
-    <t>Preço</t>
-  </si>
-  <si>
-    <t>Peso</t>
-  </si>
-  <si>
-    <t>Armas</t>
-  </si>
-  <si>
-    <t>Modificação</t>
-  </si>
-  <si>
     <t>1d4</t>
   </si>
   <si>
@@ -1297,6 +1300,18 @@
     <t>Equilibrada</t>
   </si>
   <si>
+    <t>1d12</t>
+  </si>
+  <si>
+    <t>Material Especial (adamante)</t>
+  </si>
+  <si>
+    <t>Cortante/Perfurante</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
     <t>Itens</t>
   </si>
   <si>
@@ -1315,13 +1330,10 @@
     <t>+10 em teste de alquimia</t>
   </si>
   <si>
-    <t>Poçao mana</t>
+    <t>poçao vida</t>
   </si>
   <si>
     <t>2d8+2</t>
-  </si>
-  <si>
-    <t>poçao vida</t>
   </si>
   <si>
     <t>Curar ferimentos</t>
@@ -1524,10 +1536,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1565,6 +1577,29 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1572,15 +1607,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1594,11 +1622,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1611,30 +1638,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1655,8 +1659,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1671,15 +1697,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1687,15 +1707,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1754,7 +1766,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1766,13 +1850,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1784,19 +1886,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1808,25 +1898,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1838,31 +1916,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1874,7 +1934,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1886,55 +1946,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2457,15 +2469,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2477,6 +2480,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2496,28 +2525,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2534,22 +2546,22 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -2557,148 +2569,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="41" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2983,54 +2995,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
-    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
-    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
-    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
-    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
-    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
-    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
-    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
-    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
-    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
-    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
-    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
-    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
-    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
-    <cellStyle name="Saída" xfId="25" builtinId="21"/>
-    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
-    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bom" xfId="29" builtinId="26"/>
-    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
-    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
-    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
-    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
-    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
-    <cellStyle name="Título" xfId="36" builtinId="15"/>
-    <cellStyle name="Observação" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
-    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
-    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
-    <cellStyle name="Comma" xfId="43" builtinId="3"/>
-    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
-    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
-    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
-    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
@@ -4300,7 +4312,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.425" customWidth="1"/>
     <col min="3" max="3" width="6.14166666666667" customWidth="1"/>
@@ -4312,7 +4324,7 @@
     <col min="14" max="14" width="36.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -4336,7 +4348,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:14">
+    <row r="3" spans="2:14">
       <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4353,7 +4365,7 @@
       </c>
       <c r="G3" s="27">
         <f>H3-L25-SUM(L4:L22)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H3" s="39">
         <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
@@ -4372,7 +4384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:14">
+    <row r="4" spans="2:14">
       <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
@@ -4389,7 +4401,7 @@
       </c>
       <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
@@ -4398,13 +4410,11 @@
       <c r="K4" s="41">
         <v>1</v>
       </c>
-      <c r="L4" s="29">
-        <v>12</v>
-      </c>
+      <c r="L4" s="29"/>
       <c r="M4" s="29"/>
       <c r="N4" s="42"/>
     </row>
-    <row r="5" ht="14.25" spans="2:14">
+    <row r="5" spans="2:14">
       <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
@@ -4427,13 +4437,11 @@
       <c r="K5" s="38">
         <v>2</v>
       </c>
-      <c r="L5" s="27">
-        <v>-6</v>
-      </c>
+      <c r="L5" s="27"/>
       <c r="M5" s="27"/>
       <c r="N5" s="39"/>
     </row>
-    <row r="6" ht="15" spans="2:14">
+    <row r="6" spans="2:14">
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
@@ -4456,13 +4464,11 @@
       <c r="K6" s="41">
         <v>3</v>
       </c>
-      <c r="L6" s="29">
-        <v>8</v>
-      </c>
+      <c r="L6" s="29"/>
       <c r="M6" s="29"/>
       <c r="N6" s="42"/>
     </row>
-    <row r="7" ht="14.25" spans="2:14">
+    <row r="7" spans="2:14">
       <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
@@ -4486,12 +4492,10 @@
         <v>4</v>
       </c>
       <c r="L7" s="27"/>
-      <c r="M7" s="27">
-        <v>3</v>
-      </c>
+      <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" ht="15.75" spans="2:14">
+    <row r="8" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4513,18 +4517,16 @@
       <c r="K8" s="41">
         <v>5</v>
       </c>
-      <c r="L8" s="29">
-        <v>-8</v>
-      </c>
+      <c r="L8" s="29"/>
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" ht="15" spans="6:14">
+    <row r="9" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="27">
-        <v>1018</v>
+        <v>682</v>
       </c>
       <c r="H9" s="39"/>
       <c r="K9" s="38">
@@ -4534,7 +4536,7 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" ht="15.75" spans="6:14">
+    <row r="10" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
@@ -4549,7 +4551,7 @@
       <c r="M10" s="29"/>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" ht="15.75" spans="11:14">
+    <row r="11" ht="19.5" spans="11:14">
       <c r="K11" s="38">
         <v>8</v>
       </c>
@@ -4557,7 +4559,7 @@
       <c r="M11" s="27"/>
       <c r="N11" s="39"/>
     </row>
-    <row r="12" ht="16.5" spans="2:14">
+    <row r="12" ht="19.5" spans="2:14">
       <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
@@ -4575,7 +4577,7 @@
       <c r="M12" s="29"/>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" ht="15.75" spans="2:14">
+    <row r="13" ht="19.5" spans="2:14">
       <c r="B13" s="89"/>
       <c r="K13" s="38">
         <v>10</v>
@@ -4584,7 +4586,7 @@
       <c r="M13" s="27"/>
       <c r="N13" s="39"/>
     </row>
-    <row r="14" ht="15.75" spans="2:14">
+    <row r="14" ht="18.75" spans="2:14">
       <c r="B14" s="35" t="s">
         <v>21</v>
       </c>
@@ -4603,7 +4605,7 @@
       <c r="M14" s="29"/>
       <c r="N14" s="42"/>
     </row>
-    <row r="15" ht="14.25" spans="2:14">
+    <row r="15" spans="2:14">
       <c r="B15" s="38" t="s">
         <v>23</v>
       </c>
@@ -4642,22 +4644,22 @@
       </c>
       <c r="D16" s="46">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,3,FALSE),"")</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="45" t="s">
         <v>30</v>
       </c>
       <c r="G16" s="52" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
-        <v>1d4</v>
+        <v>1d12</v>
       </c>
       <c r="H16" s="52">
-        <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,3,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="46">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,4,FALSE),"")</f>
         <v>0</v>
+      </c>
+      <c r="I16" s="46" t="str">
+        <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
+        <v>x3</v>
       </c>
       <c r="K16" s="41">
         <v>13</v>
@@ -4666,7 +4668,7 @@
       <c r="M16" s="29"/>
       <c r="N16" s="42"/>
     </row>
-    <row r="17" ht="15" spans="11:14">
+    <row r="17" ht="18.75" spans="11:14">
       <c r="K17" s="38">
         <v>14</v>
       </c>
@@ -4682,7 +4684,7 @@
       <c r="M18" s="29"/>
       <c r="N18" s="42"/>
     </row>
-    <row r="19" ht="14.25" spans="11:14">
+    <row r="19" spans="11:14">
       <c r="K19" s="38">
         <v>16</v>
       </c>
@@ -4690,7 +4692,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="39"/>
     </row>
-    <row r="20" ht="15" spans="11:14">
+    <row r="20" spans="11:14">
       <c r="K20" s="41">
         <v>17</v>
       </c>
@@ -4698,7 +4700,7 @@
       <c r="M20" s="29"/>
       <c r="N20" s="42"/>
     </row>
-    <row r="21" ht="14.25" spans="11:14">
+    <row r="21" spans="11:14">
       <c r="K21" s="38">
         <v>18</v>
       </c>
@@ -4714,26 +4716,26 @@
       <c r="M22" s="52"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15.75" spans="11:12">
+    <row r="23" ht="19.5"/>
+    <row r="24" ht="18.75" spans="11:12">
       <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="36"/>
     </row>
-    <row r="25" ht="14.25" spans="11:12">
+    <row r="25" spans="11:12">
       <c r="K25" s="38" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="39"/>
     </row>
-    <row r="26" ht="15.75" spans="11:12">
+    <row r="26" ht="18.75" spans="11:12">
       <c r="K26" s="45" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" ht="14.25"/>
+    <row r="27" ht="18.75"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4767,15 +4769,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
     <col min="13" max="13" width="12.2833333333333" customWidth="1"/>
     <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
+    <row r="1" ht="19.5" spans="1:15">
       <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
@@ -4795,8 +4797,8 @@
       <c r="N1" s="73"/>
       <c r="O1" s="74"/>
     </row>
-    <row r="2" ht="15"/>
-    <row r="3" ht="15.75" spans="2:13">
+    <row r="2" ht="19.5"/>
+    <row r="3" ht="18.75" spans="2:13">
       <c r="B3" s="35" t="s">
         <v>34</v>
       </c>
@@ -4876,7 +4878,7 @@
       </c>
       <c r="M6" s="86"/>
     </row>
-    <row r="7" ht="15" spans="2:13">
+    <row r="7" spans="2:13">
       <c r="B7" s="41" t="s">
         <v>49</v>
       </c>
@@ -4896,7 +4898,7 @@
       </c>
       <c r="M7" s="87"/>
     </row>
-    <row r="8" ht="14.25" spans="2:13">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>53</v>
       </c>
@@ -4916,7 +4918,7 @@
       </c>
       <c r="M8" s="86"/>
     </row>
-    <row r="9" ht="15" spans="2:13">
+    <row r="9" spans="2:13">
       <c r="B9" s="41" t="s">
         <v>57</v>
       </c>
@@ -4948,7 +4950,7 @@
       <c r="L10" s="79"/>
       <c r="M10" s="86"/>
     </row>
-    <row r="11" ht="15" spans="2:13">
+    <row r="11" spans="2:13">
       <c r="B11" s="41" t="s">
         <v>60</v>
       </c>
@@ -4964,7 +4966,7 @@
       <c r="L11" s="81"/>
       <c r="M11" s="87"/>
     </row>
-    <row r="12" ht="14.25" spans="2:13">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>62</v>
       </c>
@@ -4980,7 +4982,7 @@
       <c r="L12" s="79"/>
       <c r="M12" s="86"/>
     </row>
-    <row r="13" ht="15" spans="2:13">
+    <row r="13" spans="2:13">
       <c r="B13" s="41" t="s">
         <v>64</v>
       </c>
@@ -4997,7 +4999,7 @@
       <c r="L13" s="81"/>
       <c r="M13" s="87"/>
     </row>
-    <row r="14" ht="14.25" spans="2:13">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>67</v>
       </c>
@@ -5009,7 +5011,7 @@
       <c r="L14" s="79"/>
       <c r="M14" s="86"/>
     </row>
-    <row r="15" ht="15" spans="2:13">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>68</v>
       </c>
@@ -5021,7 +5023,7 @@
       <c r="L15" s="81"/>
       <c r="M15" s="87"/>
     </row>
-    <row r="16" ht="14.25" spans="2:13">
+    <row r="16" spans="2:13">
       <c r="B16" s="38" t="s">
         <v>69</v>
       </c>
@@ -5033,7 +5035,7 @@
       <c r="L16" s="79"/>
       <c r="M16" s="86"/>
     </row>
-    <row r="17" ht="15" spans="2:13">
+    <row r="17" spans="2:13">
       <c r="B17" s="41" t="s">
         <v>70</v>
       </c>
@@ -5045,7 +5047,7 @@
       <c r="L17" s="81"/>
       <c r="M17" s="87"/>
     </row>
-    <row r="18" ht="14.25" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="38" t="s">
         <v>71</v>
       </c>
@@ -5057,7 +5059,7 @@
       <c r="L18" s="79"/>
       <c r="M18" s="86"/>
     </row>
-    <row r="19" ht="15" spans="2:13">
+    <row r="19" spans="2:13">
       <c r="B19" s="41" t="s">
         <v>72</v>
       </c>
@@ -5069,7 +5071,7 @@
       <c r="L19" s="81"/>
       <c r="M19" s="87"/>
     </row>
-    <row r="20" ht="14.25" spans="2:13">
+    <row r="20" spans="2:13">
       <c r="B20" s="38" t="s">
         <v>73</v>
       </c>
@@ -5081,7 +5083,7 @@
       <c r="L20" s="79"/>
       <c r="M20" s="86"/>
     </row>
-    <row r="21" ht="15" spans="2:13">
+    <row r="21" spans="2:13">
       <c r="B21" s="41" t="s">
         <v>74</v>
       </c>
@@ -5093,7 +5095,7 @@
       <c r="L21" s="81"/>
       <c r="M21" s="87"/>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="43" t="s">
         <v>75</v>
       </c>
@@ -5105,6 +5107,7 @@
       <c r="L22" s="84"/>
       <c r="M22" s="88"/>
     </row>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5160,14 +5163,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.85" customWidth="1"/>
     <col min="7" max="7" width="8.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
       <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
@@ -5185,32 +5188,32 @@
       </c>
       <c r="H2" s="64"/>
     </row>
-    <row r="3" ht="15" spans="2:8">
+    <row r="3" ht="18.75" spans="2:8">
       <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
       </c>
       <c r="C3" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>79</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="2:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" spans="2:5">
       <c r="B4" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5221,14 +5224,14 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
       <c r="B5" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5239,14 +5242,14 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="2:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5257,14 +5260,14 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
       <c r="B7" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5275,14 +5278,14 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="2:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
       <c r="B8" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
@@ -5293,14 +5296,14 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
       <c r="B9" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
@@ -5311,14 +5314,14 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="2:5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
       <c r="B10" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5329,14 +5332,14 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5347,14 +5350,14 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
       <c r="B12" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5365,32 +5368,32 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
       <c r="B13" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
       </c>
       <c r="C13" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
       <c r="B14" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
@@ -5401,14 +5404,14 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
       <c r="B15" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5419,14 +5422,14 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
       <c r="B16" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5437,14 +5440,14 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
       <c r="B17" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5455,14 +5458,14 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
       <c r="B18" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
@@ -5473,14 +5476,14 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="B19" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5491,32 +5494,32 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
       </c>
       <c r="C20" s="29">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:5">
+    <row r="21" spans="2:5">
       <c r="B21" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
@@ -5527,14 +5530,14 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
@@ -5545,14 +5548,14 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
       <c r="B23" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
@@ -5563,11 +5566,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5581,14 +5584,14 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
       <c r="B25" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
@@ -5599,11 +5602,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5617,14 +5620,14 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
       <c r="B27" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
@@ -5635,14 +5638,14 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
       <c r="B28" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5653,14 +5656,14 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
       <c r="B29" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
@@ -5671,14 +5674,14 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
       <c r="B30" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
@@ -5689,14 +5692,14 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" spans="2:5">
       <c r="B31" s="43" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
@@ -5707,14 +5710,14 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5733,7 +5736,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.425" customWidth="1"/>
@@ -5741,8 +5744,8 @@
     <col min="5" max="5" width="10.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
       <c r="B2" s="24" t="s">
         <v>80</v>
       </c>
@@ -5760,7 +5763,7 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:8">
+    <row r="3" spans="2:8">
       <c r="B3" s="67" t="s">
         <v>84</v>
       </c>
@@ -5781,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:8">
+    <row r="4" spans="2:8">
       <c r="B4" s="30" t="s">
         <v>86</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="2:8">
+    <row r="5" spans="2:8">
       <c r="B5" s="67" t="s">
         <v>87</v>
       </c>
@@ -5823,7 +5826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:8">
+    <row r="6" spans="2:8">
       <c r="B6" s="30" t="s">
         <v>89</v>
       </c>
@@ -5844,7 +5847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:8">
+    <row r="7" ht="18.75" spans="1:8">
       <c r="A7" s="68"/>
       <c r="B7" s="67" t="s">
         <v>90</v>
@@ -5867,7 +5870,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:5">
+    <row r="8" ht="18.75" spans="2:5">
       <c r="B8" s="30" t="s">
         <v>91</v>
       </c>
@@ -5882,7 +5885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:6">
+    <row r="9" spans="1:6">
       <c r="A9" s="69"/>
       <c r="B9" s="67" t="s">
         <v>92</v>
@@ -5899,7 +5902,7 @@
       </c>
       <c r="F9" s="69"/>
     </row>
-    <row r="10" ht="15" spans="2:5">
+    <row r="10" spans="2:5">
       <c r="B10" s="30" t="s">
         <v>93</v>
       </c>
@@ -5914,7 +5917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="2:5">
+    <row r="11" spans="2:5">
       <c r="B11" s="67" t="s">
         <v>94</v>
       </c>
@@ -5929,7 +5932,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:5">
+    <row r="12" spans="2:5">
       <c r="B12" s="30" t="s">
         <v>95</v>
       </c>
@@ -5944,7 +5947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:5">
+    <row r="13" spans="2:5">
       <c r="B13" s="67" t="s">
         <v>96</v>
       </c>
@@ -5959,7 +5962,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="2:5">
+    <row r="14" spans="2:5">
       <c r="B14" s="30" t="s">
         <v>97</v>
       </c>
@@ -5974,7 +5977,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:5">
+    <row r="15" spans="2:5">
       <c r="B15" s="67" t="s">
         <v>98</v>
       </c>
@@ -5989,7 +5992,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:5">
+    <row r="16" spans="2:5">
       <c r="B16" s="30" t="s">
         <v>100</v>
       </c>
@@ -6004,7 +6007,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:5">
+    <row r="17" spans="2:5">
       <c r="B17" s="67"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -6013,7 +6016,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:5">
+    <row r="18" spans="2:5">
       <c r="B18" s="30"/>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -6022,7 +6025,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:5">
+    <row r="19" spans="2:5">
       <c r="B19" s="67"/>
       <c r="C19" s="26"/>
       <c r="D19" s="27"/>
@@ -6031,7 +6034,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:5">
+    <row r="20" spans="2:5">
       <c r="B20" s="30"/>
       <c r="C20" s="28"/>
       <c r="D20" s="29"/>
@@ -6040,7 +6043,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:5">
+    <row r="21" spans="2:5">
       <c r="B21" s="67"/>
       <c r="C21" s="26"/>
       <c r="D21" s="27"/>
@@ -6049,7 +6052,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:5">
+    <row r="22" spans="2:5">
       <c r="B22" s="30"/>
       <c r="C22" s="28"/>
       <c r="D22" s="29"/>
@@ -6058,7 +6061,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:5">
+    <row r="23" spans="2:5">
       <c r="B23" s="67"/>
       <c r="C23" s="26"/>
       <c r="D23" s="27"/>
@@ -6067,7 +6070,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:5">
+    <row r="24" spans="2:5">
       <c r="B24" s="30"/>
       <c r="C24" s="28"/>
       <c r="D24" s="29"/>
@@ -6076,7 +6079,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:5">
+    <row r="25" spans="2:5">
       <c r="B25" s="67"/>
       <c r="C25" s="26"/>
       <c r="D25" s="27"/>
@@ -6085,7 +6088,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:5">
+    <row r="26" spans="2:5">
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29"/>
@@ -6094,7 +6097,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:5">
+    <row r="27" spans="2:5">
       <c r="B27" s="67"/>
       <c r="C27" s="26"/>
       <c r="D27" s="27"/>
@@ -6103,7 +6106,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" s="30"/>
       <c r="C28" s="28"/>
       <c r="D28" s="29"/>
@@ -6112,7 +6115,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:5">
+    <row r="29" spans="2:5">
       <c r="B29" s="67"/>
       <c r="C29" s="26"/>
       <c r="D29" s="27"/>
@@ -6121,7 +6124,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="30"/>
       <c r="C30" s="28"/>
       <c r="D30" s="29"/>
@@ -6130,7 +6133,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:5">
+    <row r="31" spans="2:5">
       <c r="B31" s="67"/>
       <c r="C31" s="26"/>
       <c r="D31" s="27"/>
@@ -6139,7 +6142,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:5">
+    <row r="32" spans="2:5">
       <c r="B32" s="30"/>
       <c r="C32" s="28"/>
       <c r="D32" s="29"/>
@@ -6148,7 +6151,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:5">
+    <row r="33" spans="2:5">
       <c r="B33" s="67"/>
       <c r="C33" s="26"/>
       <c r="D33" s="27"/>
@@ -6157,7 +6160,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" spans="2:5">
+    <row r="34" spans="2:5">
       <c r="B34" s="30"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
@@ -6166,7 +6169,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="2:5">
+    <row r="35" spans="2:5">
       <c r="B35" s="70"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
@@ -6192,15 +6195,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="21.1416666666667" customWidth="1"/>
     <col min="4" max="4" width="17.7083333333333" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:6">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:6">
       <c r="B2" s="35" t="s">
         <v>101</v>
       </c>
@@ -6209,7 +6212,7 @@
       <c r="E2" s="62"/>
       <c r="F2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:6">
+    <row r="3" spans="2:6">
       <c r="B3" s="38" t="s">
         <v>23</v>
       </c>
@@ -6226,7 +6229,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:6">
+    <row r="4" spans="2:6">
       <c r="B4" s="41" t="s">
         <v>29</v>
       </c>
@@ -6234,7 +6237,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="29">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E4" s="40">
         <v>20</v>
@@ -6243,15 +6246,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:6">
+    <row r="5" ht="18.75" spans="2:6">
       <c r="B5" s="43"/>
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
       <c r="E5" s="63"/>
       <c r="F5" s="44"/>
     </row>
-    <row r="6" ht="15"/>
-    <row r="7" ht="15.75" spans="2:8">
+    <row r="6" ht="19.5"/>
+    <row r="7" ht="18.75" spans="2:8">
       <c r="B7" s="50" t="s">
         <v>104</v>
       </c>
@@ -6262,7 +6265,7 @@
       <c r="G7" s="51"/>
       <c r="H7" s="64"/>
     </row>
-    <row r="8" ht="14.25" spans="2:8">
+    <row r="8" spans="2:8">
       <c r="B8" s="38" t="s">
         <v>23</v>
       </c>
@@ -6285,54 +6288,66 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:8">
+    <row r="9" spans="2:8">
       <c r="B9" s="41" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="2:8">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="B10" s="38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="37">
         <v>2</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="2:8">
-      <c r="B11" s="41"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="2:8">
+      <c r="B11" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>114</v>
+      </c>
       <c r="E11" s="29"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="42"/>
-    </row>
-    <row r="12" ht="14.25" spans="2:8">
+      <c r="F11" s="40">
+        <v>6</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
       <c r="B12" s="38"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -6341,7 +6356,7 @@
       <c r="G12" s="37"/>
       <c r="H12" s="39"/>
     </row>
-    <row r="13" ht="15.75" spans="2:8">
+    <row r="13" ht="18.75" spans="2:8">
       <c r="B13" s="45"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
@@ -6350,10 +6365,10 @@
       <c r="G13" s="65"/>
       <c r="H13" s="46"/>
     </row>
-    <row r="14" ht="15"/>
-    <row r="15" ht="15.75" spans="2:9">
+    <row r="14" ht="19.5"/>
+    <row r="15" ht="18.75" spans="2:9">
       <c r="B15" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -6363,7 +6378,7 @@
       <c r="H15" s="48"/>
       <c r="I15" s="36"/>
     </row>
-    <row r="16" ht="14.25" spans="2:9">
+    <row r="16" spans="2:9">
       <c r="B16" s="53" t="s">
         <v>23</v>
       </c>
@@ -6372,27 +6387,27 @@
       </c>
       <c r="D16" s="54"/>
       <c r="E16" s="54" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F16" s="54" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G16" s="54" t="s">
         <v>103</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I16" s="66" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:9">
+    <row r="17" spans="2:9">
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C17" s="94" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="29">
@@ -6413,36 +6428,22 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="2:9">
-      <c r="B18" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="54" t="s">
-        <v>119</v>
-      </c>
+    <row r="18" spans="2:9">
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="54"/>
-      <c r="E18" s="54">
-        <v>1</v>
-      </c>
-      <c r="F18" s="54">
-        <v>2</v>
-      </c>
-      <c r="G18" s="54">
-        <f>PRODUCT(E18:F18)</f>
-        <v>2</v>
-      </c>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
       <c r="H18" s="54"/>
-      <c r="I18" s="66">
-        <f>PRODUCT(H18,E18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="2:9">
+      <c r="I18" s="66"/>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="29">
@@ -6461,9 +6462,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="2:9">
+    <row r="20" spans="2:9">
       <c r="B20" s="53" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C20" s="54"/>
       <c r="D20" s="54"/>
@@ -6483,9 +6484,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:9">
+    <row r="21" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -6501,7 +6502,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="42"/>
     </row>
-    <row r="22" ht="14.25" spans="2:9">
+    <row r="22" spans="2:9">
       <c r="B22" s="53"/>
       <c r="C22" s="54"/>
       <c r="D22" s="54"/>
@@ -6511,7 +6512,7 @@
       <c r="H22" s="54"/>
       <c r="I22" s="66"/>
     </row>
-    <row r="23" ht="15" spans="2:9">
+    <row r="23" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -6521,7 +6522,7 @@
       <c r="H23" s="29"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" ht="14.25" spans="2:9">
+    <row r="24" spans="2:9">
       <c r="B24" s="53"/>
       <c r="C24" s="54"/>
       <c r="D24" s="54"/>
@@ -6531,7 +6532,7 @@
       <c r="H24" s="54"/>
       <c r="I24" s="66"/>
     </row>
-    <row r="25" ht="15" spans="2:9">
+    <row r="25" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -6541,7 +6542,7 @@
       <c r="H25" s="29"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" ht="14.25" spans="2:9">
+    <row r="26" spans="2:9">
       <c r="B26" s="53"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -6551,7 +6552,7 @@
       <c r="H26" s="54"/>
       <c r="I26" s="66"/>
     </row>
-    <row r="27" ht="15" spans="2:9">
+    <row r="27" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -6561,7 +6562,7 @@
       <c r="H27" s="29"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" ht="14.25" spans="2:9">
+    <row r="28" spans="2:9">
       <c r="B28" s="53"/>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -6571,7 +6572,7 @@
       <c r="H28" s="54"/>
       <c r="I28" s="66"/>
     </row>
-    <row r="29" ht="15.75" spans="2:9">
+    <row r="29" ht="18.75" spans="2:9">
       <c r="B29" s="7"/>
       <c r="C29" s="55"/>
       <c r="D29" s="55"/>
@@ -6581,15 +6582,15 @@
       <c r="H29" s="52"/>
       <c r="I29" s="46"/>
     </row>
-    <row r="30" ht="14.25"/>
-    <row r="31" ht="14.25"/>
-    <row r="32" ht="15.75" spans="2:4">
+    <row r="30" ht="18.75"/>
+    <row r="31" ht="18.75"/>
+    <row r="32" ht="18.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2">
         <f>Clebina!C3*3</f>
@@ -6598,7 +6599,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
       <c r="B33" s="57" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C33" s="58">
         <f>Clebina!C3*10</f>
@@ -6608,7 +6609,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
@@ -6616,7 +6617,7 @@
       </c>
       <c r="D34" s="61"/>
     </row>
-    <row r="35" ht="14.25"/>
+    <row r="35" ht="18.75"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6648,7 +6649,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
@@ -6665,22 +6666,22 @@
     <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6689,31 +6690,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:16">
+    <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6732,16 +6733,16 @@
       <c r="I3" s="27"/>
       <c r="J3" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6750,12 +6751,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6777,13 +6778,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6792,12 +6793,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6819,13 +6820,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -6834,12 +6835,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6861,21 +6862,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6897,25 +6898,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6937,13 +6938,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -6953,12 +6954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6980,13 +6981,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -6996,12 +6997,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7023,13 +7024,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7039,12 +7040,12 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7066,13 +7067,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7082,12 +7083,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
+    <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7109,13 +7110,13 @@
         <v>5</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7125,12 +7126,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7149,16 +7150,16 @@
       <c r="I13" s="27"/>
       <c r="J13" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7168,12 +7169,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7195,21 +7196,21 @@
         <v>10</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7231,21 +7232,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7267,21 +7268,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:17">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7303,25 +7304,25 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7343,21 +7344,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7379,21 +7380,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M19" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7412,24 +7413,24 @@
       <c r="I20" s="29"/>
       <c r="J20" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7451,21 +7452,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7489,21 +7490,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7525,21 +7526,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L23" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M23" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7561,21 +7562,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7597,21 +7598,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7633,21 +7634,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7671,21 +7672,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7707,21 +7708,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L28" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M28" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7743,21 +7744,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7779,21 +7780,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7815,21 +7816,21 @@
         <v>6</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L31" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7851,21 +7852,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7887,13 +7888,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -7914,7 +7915,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
@@ -7931,22 +7932,22 @@
     <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -7955,31 +7956,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:16">
+    <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7998,16 +7999,16 @@
       <c r="I3" s="27"/>
       <c r="J3" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D16,0)</f>
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8016,12 +8017,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8043,13 +8044,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8058,12 +8059,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8085,13 +8086,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -8100,12 +8101,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8127,21 +8128,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8163,25 +8164,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8203,13 +8204,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M8" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8219,12 +8220,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8246,13 +8247,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8262,12 +8263,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8289,13 +8290,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8305,12 +8306,12 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8332,13 +8333,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8348,12 +8349,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
+    <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8375,13 +8376,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8391,12 +8392,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8418,13 +8419,13 @@
         <v>4</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8434,12 +8435,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8463,21 +8464,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L14" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M14" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8499,21 +8500,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8535,21 +8536,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8571,21 +8572,21 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8607,21 +8608,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M18" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8643,21 +8644,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L19" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M19" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8679,21 +8680,21 @@
         <v>4</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8715,21 +8716,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8753,21 +8754,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M22" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8789,21 +8790,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L23" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M23" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8825,21 +8826,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L24" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M24" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8861,21 +8862,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L25" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8897,21 +8898,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L26" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8935,21 +8936,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L27" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8971,21 +8972,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L28" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M28" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9007,21 +9008,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9043,21 +9044,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M30" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9079,21 +9080,21 @@
         <v>8</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L31" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9115,21 +9116,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9151,13 +9152,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L33" s="32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M33" s="47" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -9178,7 +9179,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="10.2833333333333" customWidth="1"/>
     <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
@@ -9187,10 +9188,10 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:13">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9200,23 +9201,23 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:13">
+    <row r="3" spans="2:13">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9240,13 +9241,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:13">
+    <row r="4" ht="18.75" spans="2:13">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9270,13 +9271,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:10">
+    <row r="5" ht="18.75" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9294,7 +9295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:10">
+    <row r="6" spans="2:10">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9312,7 +9313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:10">
+    <row r="7" spans="2:10">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9330,7 +9331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:10">
+    <row r="8" ht="18.75" spans="2:10">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9348,7 +9349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:10">
+    <row r="9" ht="18.75" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9360,7 +9361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:10">
+    <row r="10" spans="8:10">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
@@ -9372,7 +9373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:10">
+    <row r="11" ht="18.75" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9384,9 +9385,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:10">
+    <row r="12" ht="18.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9403,9 +9404,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:10">
+    <row r="13" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9422,7 +9423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:10">
+    <row r="14" ht="18.75" spans="2:10">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
@@ -9436,7 +9437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:10">
+    <row r="15" ht="19.5" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9448,15 +9449,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:10">
+    <row r="16" ht="18.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>
@@ -9472,7 +9473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:10">
+    <row r="17" spans="2:10">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9495,7 +9496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:10">
+    <row r="18" spans="2:10">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9518,7 +9519,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:10">
+    <row r="19" spans="2:10">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9541,7 +9542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:10">
+    <row r="20" spans="2:10">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:10">
+    <row r="21" spans="2:10">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9589,7 +9590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:10">
+    <row r="22" ht="18.75" spans="2:10">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="14.25"/>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7860"/>
+    <workbookView windowWidth="19770" windowHeight="7455"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="191">
   <si>
     <t>Atributos</t>
   </si>
@@ -1340,6 +1340,9 @@
   </si>
   <si>
     <t>Imagem espelhada</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Capacidade</t>
@@ -1536,10 +1539,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1585,8 +1588,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1600,8 +1612,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1623,6 +1644,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
@@ -1631,20 +1659,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1660,7 +1680,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1682,32 +1702,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1718,6 +1714,13 @@
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1766,7 +1769,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1784,48 +1787,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1838,19 +1799,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1862,13 +1895,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1880,73 +1949,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2486,25 +2489,32 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -2525,6 +2535,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2536,175 +2561,153 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="41" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="42" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2992,6 +2995,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4400,7 +4404,6 @@
         <v>7</v>
       </c>
       <c r="G4" s="29">
-        <f>H4-L26-SUM(M4:M22)</f>
         <v>25</v>
       </c>
       <c r="H4" s="42">
@@ -4495,7 +4498,7 @@
       <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" ht="18.75" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4521,12 +4524,12 @@
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" spans="6:14">
+    <row r="9" ht="18.75" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="27">
-        <v>682</v>
+        <v>562</v>
       </c>
       <c r="H9" s="39"/>
       <c r="K9" s="38">
@@ -4536,7 +4539,7 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" spans="6:14">
+    <row r="10" ht="18.75" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
@@ -5199,18 +5202,18 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>79</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="18.75" spans="2:5">
@@ -5224,11 +5227,11 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -5242,11 +5245,11 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -5260,11 +5263,11 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -5278,11 +5281,11 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -5296,11 +5299,11 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -5314,11 +5317,11 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -5332,11 +5335,11 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -5350,11 +5353,11 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -5368,11 +5371,11 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -5386,11 +5389,11 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -5404,11 +5407,11 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -5422,11 +5425,11 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:5">
@@ -5440,11 +5443,11 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -5458,11 +5461,11 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -5476,11 +5479,11 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -5494,11 +5497,11 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -5512,11 +5515,11 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -5530,11 +5533,11 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -5548,11 +5551,11 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -5566,11 +5569,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5584,11 +5587,11 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -5602,11 +5605,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5620,11 +5623,11 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -5638,11 +5641,11 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -5656,11 +5659,11 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -5674,11 +5677,11 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -5692,11 +5695,11 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="18.75" spans="2:5">
@@ -5710,11 +5713,11 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" ht="18.75"/>
@@ -6194,10 +6197,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:I35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="21.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="11.25" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
     <col min="4" max="4" width="17.7083333333333" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
@@ -6417,7 +6421,7 @@
         <v>4</v>
       </c>
       <c r="G17" s="29">
-        <f>PRODUCT(E17:F17)</f>
+        <f t="shared" ref="G17:G27" si="0">PRODUCT(E17:F17)</f>
         <v>4</v>
       </c>
       <c r="H17" s="29">
@@ -6434,7 +6438,10 @@
       <c r="D18" s="54"/>
       <c r="E18" s="54"/>
       <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
+      <c r="G18" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H18" s="54"/>
       <c r="I18" s="66"/>
     </row>
@@ -6453,7 +6460,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="29">
-        <f>PRODUCT(E19:F19)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H19" s="29"/>
@@ -6475,7 +6482,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="54">
-        <f>PRODUCT(E20:F20)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H20" s="54"/>
@@ -6497,6 +6504,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="29">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H21" s="29"/>
@@ -6508,7 +6516,10 @@
       <c r="D22" s="54"/>
       <c r="E22" s="54"/>
       <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
+      <c r="G22" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H22" s="54"/>
       <c r="I22" s="66"/>
     </row>
@@ -6518,7 +6529,10 @@
       <c r="D23" s="11"/>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H23" s="29"/>
       <c r="I23" s="42"/>
     </row>
@@ -6528,7 +6542,10 @@
       <c r="D24" s="54"/>
       <c r="E24" s="54"/>
       <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
+      <c r="G24" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H24" s="54"/>
       <c r="I24" s="66"/>
     </row>
@@ -6538,7 +6555,10 @@
       <c r="D25" s="11"/>
       <c r="E25" s="29"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+      <c r="G25" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H25" s="29"/>
       <c r="I25" s="42"/>
     </row>
@@ -6548,7 +6568,10 @@
       <c r="D26" s="54"/>
       <c r="E26" s="54"/>
       <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
+      <c r="G26" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H26" s="54"/>
       <c r="I26" s="66"/>
     </row>
@@ -6558,11 +6581,17 @@
       <c r="D27" s="11"/>
       <c r="E27" s="29"/>
       <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
+      <c r="G27" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="H27" s="29"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="1:9">
+      <c r="A28" s="95" t="s">
+        <v>127</v>
+      </c>
       <c r="B28" s="53"/>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -6586,7 +6615,7 @@
     <row r="31" ht="18.75"/>
     <row r="32" ht="18.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
@@ -6599,7 +6628,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
       <c r="B33" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C33" s="58">
         <f>Clebina!C3*10</f>
@@ -6609,7 +6638,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
@@ -6669,19 +6698,19 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6690,31 +6719,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6736,13 +6765,13 @@
         <v>-6</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6753,10 +6782,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6778,13 +6807,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6795,10 +6824,10 @@
     </row>
     <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6820,13 +6849,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -6837,10 +6866,10 @@
     </row>
     <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6862,21 +6891,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6898,25 +6927,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6938,13 +6967,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -6956,10 +6985,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6981,13 +7010,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -6999,10 +7028,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7024,13 +7053,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7042,10 +7071,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7067,13 +7096,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7085,10 +7114,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7110,13 +7139,13 @@
         <v>5</v>
       </c>
       <c r="K12" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="M12" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7128,10 +7157,10 @@
     </row>
     <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7153,13 +7182,13 @@
         <v>-6</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7171,10 +7200,10 @@
     </row>
     <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7196,21 +7225,21 @@
         <v>10</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7232,21 +7261,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7268,21 +7297,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7304,13 +7333,13 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
@@ -7319,10 +7348,10 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7344,21 +7373,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7380,21 +7409,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7416,13 +7445,13 @@
         <v>-6</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -7430,7 +7459,7 @@
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7452,21 +7481,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7490,21 +7519,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7526,21 +7555,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7562,21 +7591,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7598,21 +7627,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7634,21 +7663,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7672,21 +7701,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7708,21 +7737,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7744,21 +7773,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7780,21 +7809,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7816,21 +7845,21 @@
         <v>6</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L31" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7852,21 +7881,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7888,13 +7917,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>142</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -7935,19 +7964,19 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -7956,31 +7985,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8002,13 +8031,13 @@
         <v>-6</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8019,10 +8048,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8044,13 +8073,13 @@
         <v>3</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8061,10 +8090,10 @@
     </row>
     <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8086,13 +8115,13 @@
         <v>5</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -8103,10 +8132,10 @@
     </row>
     <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8128,21 +8157,21 @@
         <v>3</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8164,25 +8193,25 @@
         <v>4</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8204,13 +8233,13 @@
         <v>10</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8222,10 +8251,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8247,13 +8276,13 @@
         <v>8</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8265,10 +8294,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8290,13 +8319,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8308,10 +8337,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8333,13 +8362,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8351,10 +8380,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8376,13 +8405,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8394,10 +8423,10 @@
     </row>
     <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8419,13 +8448,13 @@
         <v>4</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8437,10 +8466,10 @@
     </row>
     <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8464,21 +8493,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8500,21 +8529,21 @@
         <v>4</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8536,21 +8565,21 @@
         <v>3</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8572,21 +8601,21 @@
         <v>6</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8608,21 +8637,21 @@
         <v>10</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8644,21 +8673,21 @@
         <v>3</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8680,13 +8709,13 @@
         <v>4</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -8694,7 +8723,7 @@
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8716,21 +8745,21 @@
         <v>7</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8754,21 +8783,21 @@
         <v>12</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8790,21 +8819,21 @@
         <v>8</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8826,21 +8855,21 @@
         <v>10</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8862,21 +8891,21 @@
         <v>10</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8898,21 +8927,21 @@
         <v>10</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8936,21 +8965,21 @@
         <v>10</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>142</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8972,21 +9001,21 @@
         <v>4</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9008,21 +9037,21 @@
         <v>4</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9044,21 +9073,21 @@
         <v>6</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>142</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9080,21 +9109,21 @@
         <v>8</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9116,21 +9145,21 @@
         <v>6</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9152,13 +9181,13 @@
         <v>8</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>142</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -9191,7 +9220,7 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="18.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9201,16 +9230,16 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
@@ -9241,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
@@ -9271,7 +9300,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
@@ -9387,7 +9416,7 @@
     </row>
     <row r="12" ht="18.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9406,7 +9435,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9451,13 +9480,13 @@
     </row>
     <row r="16" ht="18.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7860"/>
+    <workbookView windowWidth="28800" windowHeight="12315" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="191">
   <si>
     <t>Atributos</t>
   </si>
@@ -1505,6 +1505,9 @@
   </si>
   <si>
     <t>Nível de Personagem</t>
+  </si>
+  <si>
+    <t>Bônus em Perícias Treinadas</t>
   </si>
   <si>
     <t>Bônus em Perícias</t>
@@ -1536,12 +1539,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1577,24 +1580,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1609,14 +1596,37 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1631,14 +1641,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1646,38 +1649,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1697,6 +1671,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -1705,24 +1724,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1731,6 +1734,13 @@
       <sz val="9"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1772,7 +1782,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1784,25 +1818,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1814,19 +1878,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1838,31 +1890,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1874,55 +1902,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1940,13 +1926,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2095,6 +2105,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -2174,19 +2223,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2228,19 +2264,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color auto="1"/>
@@ -2249,19 +2272,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -2486,11 +2496,48 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2510,21 +2557,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -2536,185 +2568,163 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="40" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="41" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2779,152 +2789,164 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2977,10 +2999,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2995,54 +3017,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
+    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
+    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
+    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
+    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
+    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
+    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
+    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
+    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
+    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
+    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
+    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
+    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
+    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
+    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
+    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
+    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
+    <cellStyle name="Saída" xfId="25" builtinId="21"/>
+    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
+    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bom" xfId="29" builtinId="26"/>
+    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
+    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
+    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
+    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
+    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
+    <cellStyle name="Título" xfId="36" builtinId="15"/>
+    <cellStyle name="Observação" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
+    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
+    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
+    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
+    <cellStyle name="Comma" xfId="43" builtinId="3"/>
+    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
+    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
+    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
+    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
@@ -4312,430 +4334,430 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="12.425" customWidth="1"/>
-    <col min="3" max="3" width="6.14166666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="14.5666666666667" customWidth="1"/>
-    <col min="7" max="8" width="7.85" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="6.125" customWidth="1"/>
+    <col min="4" max="4" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="8" width="7.875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="14" max="14" width="36.425" customWidth="1"/>
+    <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="36" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="52">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
-        <v>5</v>
-      </c>
-      <c r="H2" s="36"/>
-      <c r="K2" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="40"/>
+      <c r="K2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="36"/>
-    </row>
-    <row r="3" spans="2:14">
-      <c r="B3" s="38" t="s">
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="40"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:14">
+      <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>'uns dados aí'!C3+(VLOOKUP(B3,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>16</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D8" si="0">ROUNDDOWN((C3-10)/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="31">
         <f>H3-L25-SUM(L4:L22)</f>
-        <v>29</v>
-      </c>
-      <c r="H3" s="39">
-        <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
-        <v>29</v>
-      </c>
-      <c r="K3" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="43">
+        <f>'uns dados aí'!N2+((G2-1)*'uns dados aí'!C12)</f>
+        <v>33</v>
+      </c>
+      <c r="K3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="41" t="s">
+    <row r="4" ht="15" spans="2:14">
+      <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>'uns dados aí'!C4+(VLOOKUP(B4,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>14</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="33">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>25</v>
-      </c>
-      <c r="H4" s="42">
+        <v>30</v>
+      </c>
+      <c r="H4" s="46">
         <f>'uns dados aí'!C13*G2</f>
-        <v>25</v>
-      </c>
-      <c r="K4" s="41">
+        <v>30</v>
+      </c>
+      <c r="K4" s="45">
         <v>1</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="42"/>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="B5" s="38" t="s">
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="46"/>
+    </row>
+    <row r="5" ht="14.25" spans="2:14">
+      <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
         <f>'uns dados aí'!C5+(VLOOKUP(B5,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="43">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="41">
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="K5" s="38">
+      <c r="H5" s="94"/>
+      <c r="K5" s="42">
         <v>2</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="39"/>
-    </row>
-    <row r="6" spans="2:14">
-      <c r="B6" s="41" t="s">
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" ht="15" spans="2:14">
+      <c r="B6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="33">
         <f>'uns dados aí'!C6+(VLOOKUP(B6,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>22</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="46">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="44">
         <f>G5+Perícias!J12</f>
-        <v>27</v>
-      </c>
-      <c r="H6" s="91"/>
-      <c r="K6" s="41">
+        <v>31</v>
+      </c>
+      <c r="H6" s="95"/>
+      <c r="K6" s="45">
         <v>3</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="42"/>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="B7" s="38" t="s">
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" ht="14.25" spans="2:14">
+      <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="31">
         <f>'uns dados aí'!C7+(VLOOKUP(B7,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>18</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="41">
         <f>Perícias!J27+Perícias!J21</f>
-        <v>17</v>
-      </c>
-      <c r="H7" s="90"/>
-      <c r="K7" s="38">
+        <v>25</v>
+      </c>
+      <c r="H7" s="94"/>
+      <c r="K7" s="42">
         <v>4</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="39"/>
-    </row>
-    <row r="8" spans="2:14">
-      <c r="B8" s="45" t="s">
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="43"/>
+    </row>
+    <row r="8" ht="15.75" spans="2:14">
+      <c r="B8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="56">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="50">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="96">
         <v>0.5</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="K8" s="41">
+      <c r="H8" s="97"/>
+      <c r="K8" s="45">
         <v>5</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="42"/>
-    </row>
-    <row r="9" spans="6:14">
-      <c r="F9" s="38" t="s">
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="46"/>
+    </row>
+    <row r="9" ht="15" spans="6:14">
+      <c r="F9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="31">
         <v>682</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="K9" s="38">
+      <c r="H9" s="43"/>
+      <c r="K9" s="42">
         <v>6</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="39"/>
-    </row>
-    <row r="10" spans="6:14">
-      <c r="F10" s="45" t="s">
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="43"/>
+    </row>
+    <row r="10" ht="15.75" spans="6:14">
+      <c r="F10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="52">
-        <v>10700</v>
-      </c>
-      <c r="H10" s="46"/>
-      <c r="K10" s="41">
+      <c r="G10" s="56">
+        <v>15000</v>
+      </c>
+      <c r="H10" s="50"/>
+      <c r="K10" s="45">
         <v>7</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="42"/>
-    </row>
-    <row r="11" ht="19.5" spans="11:14">
-      <c r="K11" s="38">
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="46"/>
+    </row>
+    <row r="11" ht="15.75" spans="11:14">
+      <c r="K11" s="42">
         <v>8</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="39"/>
-    </row>
-    <row r="12" ht="19.5" spans="2:14">
-      <c r="B12" s="72" t="s">
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="43"/>
+    </row>
+    <row r="12" ht="16.5" spans="2:14">
+      <c r="B12" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
-      <c r="K12" s="41">
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78"/>
+      <c r="K12" s="45">
         <v>9</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="42"/>
-    </row>
-    <row r="13" ht="19.5" spans="2:14">
-      <c r="B13" s="89"/>
-      <c r="K13" s="38">
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="46"/>
+    </row>
+    <row r="13" ht="15.75" spans="2:14">
+      <c r="B13" s="93"/>
+      <c r="K13" s="42">
         <v>10</v>
       </c>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="39"/>
-    </row>
-    <row r="14" ht="18.75" spans="2:14">
-      <c r="B14" s="35" t="s">
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="43"/>
+    </row>
+    <row r="14" ht="15.75" spans="2:14">
+      <c r="B14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="36"/>
-      <c r="F14" s="35" t="s">
+      <c r="C14" s="52"/>
+      <c r="D14" s="40"/>
+      <c r="F14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="36"/>
-      <c r="K14" s="41">
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="40"/>
+      <c r="K14" s="45">
         <v>11</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="42"/>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="38" t="s">
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="46"/>
+    </row>
+    <row r="15" ht="14.25" spans="2:14">
+      <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="42">
         <v>12</v>
       </c>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="39"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="43"/>
     </row>
     <row r="16" ht="30.75" spans="2:14">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="56">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,2,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="50">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,3,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="52" t="str">
+      <c r="G16" s="56" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
         <v>1d12</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="56">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,4,FALSE),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="50" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
         <v>x3</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="45">
         <v>13</v>
       </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="42"/>
-    </row>
-    <row r="17" ht="18.75" spans="11:14">
-      <c r="K17" s="38">
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="46"/>
+    </row>
+    <row r="17" ht="15" spans="11:14">
+      <c r="K17" s="42">
         <v>14</v>
       </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="39"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="43"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K18" s="41">
+      <c r="K18" s="45">
         <v>15</v>
       </c>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="42"/>
-    </row>
-    <row r="19" spans="11:14">
-      <c r="K19" s="38">
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="46"/>
+    </row>
+    <row r="19" ht="14.25" spans="11:14">
+      <c r="K19" s="42">
         <v>16</v>
       </c>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="39"/>
-    </row>
-    <row r="20" spans="11:14">
-      <c r="K20" s="41">
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="43"/>
+    </row>
+    <row r="20" ht="15" spans="11:14">
+      <c r="K20" s="45">
         <v>17</v>
       </c>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="42"/>
-    </row>
-    <row r="21" spans="11:14">
-      <c r="K21" s="38">
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" ht="14.25" spans="11:14">
+      <c r="K21" s="42">
         <v>18</v>
       </c>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="39"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="43"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K22" s="45">
+      <c r="K22" s="49">
         <v>20</v>
       </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="46"/>
-    </row>
-    <row r="23" ht="19.5"/>
-    <row r="24" ht="18.75" spans="11:12">
-      <c r="K24" s="35" t="s">
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="50"/>
+    </row>
+    <row r="23" ht="15"/>
+    <row r="24" ht="15.75" spans="11:12">
+      <c r="K24" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="36"/>
-    </row>
-    <row r="25" spans="11:12">
-      <c r="K25" s="38" t="s">
+      <c r="L24" s="40"/>
+    </row>
+    <row r="25" ht="14.25" spans="11:12">
+      <c r="K25" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="39"/>
-    </row>
-    <row r="26" ht="18.75" spans="11:12">
-      <c r="K26" s="45" t="s">
+      <c r="L25" s="43"/>
+    </row>
+    <row r="26" ht="15.75" spans="11:12">
+      <c r="K26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="46"/>
-    </row>
-    <row r="27" ht="18.75"/>
+      <c r="L26" s="50"/>
+    </row>
+    <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4770,344 +4792,344 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
-    <col min="13" max="13" width="12.2833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
+    <col min="12" max="12" width="19.75" customWidth="1"/>
+    <col min="13" max="13" width="12.25" customWidth="1"/>
+    <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:15">
-      <c r="A1" s="72" t="s">
+    <row r="1" ht="16.5" spans="1:15">
+      <c r="A1" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
-      <c r="I1" s="72" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="78"/>
+      <c r="I1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74"/>
-    </row>
-    <row r="2" ht="19.5"/>
-    <row r="3" ht="18.75" spans="2:13">
-      <c r="B3" s="35" t="s">
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="78"/>
+    </row>
+    <row r="2" ht="15"/>
+    <row r="3" ht="15.75" spans="2:13">
+      <c r="B3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="52"/>
+      <c r="D3" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="36"/>
-      <c r="K3" s="76" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="40"/>
+      <c r="K3" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="77" t="s">
+      <c r="L3" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="85" t="s">
+      <c r="M3" s="89" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="39" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="86"/>
+      <c r="M4" s="90"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="29" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="42" t="s">
+      <c r="E5" s="33"/>
+      <c r="F5" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="80" t="s">
+      <c r="K5" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="87"/>
+      <c r="M5" s="91"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="39" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="86"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="41" t="s">
+      <c r="M6" s="90"/>
+    </row>
+    <row r="7" ht="15" spans="2:13">
+      <c r="B7" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="33"/>
+      <c r="D7" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="42" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="80" t="s">
+      <c r="K7" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="81" t="s">
+      <c r="L7" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="87"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="38" t="s">
+      <c r="M7" s="91"/>
+    </row>
+    <row r="8" ht="14.25" spans="2:13">
+      <c r="B8" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="39" t="s">
+      <c r="E8" s="31"/>
+      <c r="F8" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="82" t="s">
+      <c r="L8" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="86"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="41" t="s">
+      <c r="M8" s="90"/>
+    </row>
+    <row r="9" ht="15" spans="2:13">
+      <c r="B9" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="33"/>
+      <c r="D9" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="42" t="s">
+      <c r="E9" s="33"/>
+      <c r="F9" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="87"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="91"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="78"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="86"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="41" t="s">
+      <c r="K10" s="82"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="90"/>
+    </row>
+    <row r="11" ht="15" spans="2:13">
+      <c r="B11" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29" t="s">
+      <c r="C11" s="33"/>
+      <c r="D11" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="42" t="s">
+      <c r="E11" s="33"/>
+      <c r="F11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="87"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="38" t="s">
+      <c r="K11" s="84"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="91"/>
+    </row>
+    <row r="12" ht="14.25" spans="2:13">
+      <c r="B12" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="31"/>
+      <c r="F12" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="78"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="86"/>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="41" t="s">
+      <c r="K12" s="82"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="90"/>
+    </row>
+    <row r="13" ht="15" spans="2:13">
+      <c r="B13" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="42" t="s">
+      <c r="E13" s="33"/>
+      <c r="F13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="87"/>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="38" t="s">
+      <c r="G13" s="79"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="91"/>
+    </row>
+    <row r="14" ht="14.25" spans="2:13">
+      <c r="B14" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="39"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="86"/>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="41" t="s">
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="43"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="90"/>
+    </row>
+    <row r="15" ht="15" spans="2:13">
+      <c r="B15" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="42"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="87"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="38" t="s">
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="46"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="91"/>
+    </row>
+    <row r="16" ht="14.25" spans="2:13">
+      <c r="B16" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="39"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="86"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="41" t="s">
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="43"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="90"/>
+    </row>
+    <row r="17" ht="15" spans="2:13">
+      <c r="B17" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="42"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="87"/>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="38" t="s">
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="46"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="91"/>
+    </row>
+    <row r="18" ht="14.25" spans="2:13">
+      <c r="B18" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="39"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="86"/>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="41" t="s">
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="43"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="90"/>
+    </row>
+    <row r="19" ht="15" spans="2:13">
+      <c r="B19" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="42"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="87"/>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="38" t="s">
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="46"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="91"/>
+    </row>
+    <row r="20" ht="14.25" spans="2:13">
+      <c r="B20" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="39"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="86"/>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="41" t="s">
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="43"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="90"/>
+    </row>
+    <row r="21" ht="15" spans="2:13">
+      <c r="B21" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="42"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="87"/>
-    </row>
-    <row r="22" ht="18.75" spans="2:13">
-      <c r="B22" s="43" t="s">
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="46"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="91"/>
+    </row>
+    <row r="22" ht="15" spans="2:13">
+      <c r="B22" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="44"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="88"/>
-    </row>
-    <row r="23" ht="18.75"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="48"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="92"/>
+    </row>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5163,561 +5185,561 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.85" customWidth="1"/>
-    <col min="7" max="7" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
-      <c r="B2" s="35" t="s">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:8">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="64"/>
-    </row>
-    <row r="3" ht="18.75" spans="2:8">
-      <c r="B3" s="38" t="str">
+      <c r="H2" s="68"/>
+    </row>
+    <row r="3" ht="15" spans="2:8">
+      <c r="B3" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-6</v>
-      </c>
-      <c r="D3" s="27">
+        <v>-5</v>
+      </c>
+      <c r="D3" s="31">
         <f ca="1">RANDBETWEEN(1,20)</f>
+        <v>13</v>
+      </c>
+      <c r="E3" s="43">
+        <f ca="1">SUM(C3:D3)</f>
         <v>8</v>
       </c>
-      <c r="E3" s="39">
-        <f ca="1">SUM(C3:D3)</f>
-        <v>2</v>
-      </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="48">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" spans="2:5">
-      <c r="B4" s="41" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" spans="2:5">
+      <c r="B4" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>3</v>
-      </c>
-      <c r="D4" s="29">
+        <v>4</v>
+      </c>
+      <c r="D4" s="33">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>13</v>
-      </c>
-      <c r="E4" s="42">
+        <v>11</v>
+      </c>
+      <c r="E4" s="46">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
-      <c r="B5" s="38" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="2:5">
+      <c r="B5" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D5" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E5" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:5">
+      <c r="B6" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Atuação</v>
+      </c>
+      <c r="C6" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E6" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="2:5">
+      <c r="B7" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cavalgar</v>
+      </c>
+      <c r="C7" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>5</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D7" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E7" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="2:5">
+      <c r="B8" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Conhecimento</v>
+      </c>
+      <c r="C8" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D8" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E8" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="2:5">
+      <c r="B9" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cura</v>
+      </c>
+      <c r="C9" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>12</v>
+      </c>
+      <c r="D9" s="31">
         <f ca="1" t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E9" s="43">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="41" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:5">
+      <c r="B10" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Atuação</v>
-      </c>
-      <c r="C6" s="29">
+        <v>Diplomacia</v>
+      </c>
+      <c r="C10" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="29">
+        <v>4</v>
+      </c>
+      <c r="D10" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E10" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
+      <c r="B11" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Enganação</v>
+      </c>
+      <c r="C11" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D11" s="31">
         <f ca="1" t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E11" s="43">
         <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="2:5">
+      <c r="B12" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Fortitude</v>
+      </c>
+      <c r="C12" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D12" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="2:5">
+      <c r="B13" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Furtividade</v>
+      </c>
+      <c r="C13" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-5</v>
+      </c>
+      <c r="D13" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E13" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="2:5">
+      <c r="B14" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Guerra</v>
+      </c>
+      <c r="C14" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="38" t="str">
+      <c r="D14" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E14" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:5">
+      <c r="B15" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cavalgar</v>
-      </c>
-      <c r="C7" s="27">
+        <v>Iniciativa</v>
+      </c>
+      <c r="C15" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D15" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E15" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:5">
+      <c r="B16" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intimidação</v>
+      </c>
+      <c r="C16" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>4</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D16" s="33">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E7" s="39">
+        <v>7</v>
+      </c>
+      <c r="E16" s="46">
         <f ca="1" t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:5">
+      <c r="B17" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intuição</v>
+      </c>
+      <c r="C17" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D17" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E17" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:5">
+      <c r="B18" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Investigação</v>
+      </c>
+      <c r="C18" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="41" t="str">
+      <c r="D18" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E18" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:5">
+      <c r="B19" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Conhecimento</v>
-      </c>
-      <c r="C8" s="29">
+        <v>Jogatina</v>
+      </c>
+      <c r="C19" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E19" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:5">
+      <c r="B20" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ladinagem</v>
+      </c>
+      <c r="C20" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-5</v>
+      </c>
+      <c r="D20" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E20" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:5">
+      <c r="B21" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Luta</v>
+      </c>
+      <c r="C21" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D21" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E21" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:5">
+      <c r="B22" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Misticismo</v>
+      </c>
+      <c r="C22" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>16</v>
+      </c>
+      <c r="D22" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E22" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:5">
+      <c r="B23" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Nobreza</v>
+      </c>
+      <c r="C23" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D23" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E23" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="2:5">
+      <c r="B24" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Alquimista)</v>
+      </c>
+      <c r="C24" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D24" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E24" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:5">
+      <c r="B25" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Armeiro)</v>
+      </c>
+      <c r="C25" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D25" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E25" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="2:5">
+      <c r="B26" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Engenhoqueiro)</v>
+      </c>
+      <c r="C26" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D26" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E26" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:5">
+      <c r="B27" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Percepção</v>
+      </c>
+      <c r="C27" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D27" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E27" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:5">
+      <c r="B28" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pilotagem</v>
+      </c>
+      <c r="C28" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D28" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E28" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:5">
+      <c r="B29" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pontaria</v>
+      </c>
+      <c r="C29" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D29" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E29" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:5">
+      <c r="B30" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Reflexos</v>
+      </c>
+      <c r="C30" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>10</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D30" s="33">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E8" s="42">
+        <v>11</v>
+      </c>
+      <c r="E30" s="46">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="38" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="2:5">
+      <c r="B31" s="47" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cura</v>
-      </c>
-      <c r="C9" s="27">
+        <v>Religião</v>
+      </c>
+      <c r="C31" s="53">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D9" s="27">
+        <v>7</v>
+      </c>
+      <c r="D31" s="53">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E9" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Diplomacia</v>
-      </c>
-      <c r="C10" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
         <v>3</v>
       </c>
-      <c r="D10" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E10" s="42">
+      <c r="E31" s="48">
         <f ca="1" t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Enganação</v>
-      </c>
-      <c r="C11" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>3</v>
-      </c>
-      <c r="D11" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E11" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Fortitude</v>
-      </c>
-      <c r="C12" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D12" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Furtividade</v>
-      </c>
-      <c r="C13" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-6</v>
-      </c>
-      <c r="D13" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E13" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Guerra</v>
-      </c>
-      <c r="C14" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D14" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E14" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Iniciativa</v>
-      </c>
-      <c r="C15" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D15" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E15" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intimidação</v>
-      </c>
-      <c r="C16" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>3</v>
-      </c>
-      <c r="D16" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E16" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intuição</v>
-      </c>
-      <c r="C17" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>6</v>
-      </c>
-      <c r="D17" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E17" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Investigação</v>
-      </c>
-      <c r="C18" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D18" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E18" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Jogatina</v>
-      </c>
-      <c r="C19" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>3</v>
-      </c>
-      <c r="D19" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E19" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ladinagem</v>
-      </c>
-      <c r="C20" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-6</v>
-      </c>
-      <c r="D20" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E20" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Luta</v>
-      </c>
-      <c r="C21" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D21" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E21" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Misticismo</v>
-      </c>
-      <c r="C22" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>12</v>
-      </c>
-      <c r="D22" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E22" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Nobreza</v>
-      </c>
-      <c r="C23" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D23" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E23" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
-      <c r="B24" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Alquimista)</v>
-      </c>
-      <c r="C24" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D24" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E24" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Armeiro)</v>
-      </c>
-      <c r="C25" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D25" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="E25" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="2:5">
-      <c r="B26" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Engenhoqueiro)</v>
-      </c>
-      <c r="C26" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D26" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E26" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Percepção</v>
-      </c>
-      <c r="C27" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D27" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E27" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pilotagem</v>
-      </c>
-      <c r="C28" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D28" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E28" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pontaria</v>
-      </c>
-      <c r="C29" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D29" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E29" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Reflexos</v>
-      </c>
-      <c r="C30" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>6</v>
-      </c>
-      <c r="D30" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E30" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" spans="2:5">
-      <c r="B31" s="43" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Religião</v>
-      </c>
-      <c r="C31" s="49">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>6</v>
-      </c>
-      <c r="D31" s="49">
-        <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E31" s="44">
-        <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75"/>
+    <row r="32" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5736,444 +5758,443 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="11.85" customWidth="1"/>
-    <col min="5" max="5" width="10.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.25" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
-      <c r="B2" s="24" t="s">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:8">
+      <c r="B2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="67" t="s">
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:8">
+      <c r="B3" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <v>1</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="41">
         <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="42">
         <v>1</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="30" t="s">
+    <row r="4" ht="15" spans="2:8">
+      <c r="B4" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>1</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="45">
         <v>2</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="67" t="s">
+    <row r="5" ht="14.25" spans="2:8">
+      <c r="B5" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="42">
         <v>3</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="30" t="s">
+    <row r="6" ht="15" spans="2:8">
+      <c r="B6" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <v>1</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="45">
         <v>4</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" spans="1:8">
-      <c r="A7" s="68"/>
-      <c r="B7" s="67" t="s">
+    <row r="7" ht="15" spans="2:8">
+      <c r="B7" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <v>1</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F7" s="68"/>
-      <c r="G7" s="43">
+      <c r="G7" s="47">
         <v>5</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="48">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="2:5">
-      <c r="B8" s="30" t="s">
+    <row r="8" ht="15.75" spans="2:5">
+      <c r="B8" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <v>1</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="69"/>
-      <c r="B9" s="67" t="s">
+    <row r="9" ht="14.25" spans="2:6">
+      <c r="B9" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <v>1</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F9" s="69"/>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="30" t="s">
+      <c r="F9" s="75"/>
+    </row>
+    <row r="10" ht="15" spans="1:6">
+      <c r="A10" s="72"/>
+      <c r="B10" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <v>1</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="67" t="s">
+      <c r="F10" s="72"/>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
+      <c r="B11" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <v>2</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="30" t="s">
+    <row r="12" ht="15" spans="2:5">
+      <c r="B12" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <v>1</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="67" t="s">
+    <row r="13" ht="14.25" spans="2:5">
+      <c r="B13" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <v>2</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="30" t="s">
+    <row r="14" ht="15" spans="2:5">
+      <c r="B14" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <v>2</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="44">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="67" t="s">
+    <row r="15" ht="14.25" spans="2:5">
+      <c r="B15" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <v>2</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="30" t="s">
+    <row r="16" ht="15" spans="2:5">
+      <c r="B16" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <v>3</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="44">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="67"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="37" t="str">
+    <row r="17" ht="14.25" spans="2:5">
+      <c r="B17" s="71"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="30"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="40" t="str">
+    <row r="18" ht="15" spans="2:5">
+      <c r="B18" s="34"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="67"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="37" t="str">
+    <row r="19" ht="14.25" spans="2:5">
+      <c r="B19" s="71"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="30"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="40" t="str">
+    <row r="20" ht="15" spans="2:5">
+      <c r="B20" s="34"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="67"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="37" t="str">
+    <row r="21" ht="14.25" spans="2:5">
+      <c r="B21" s="71"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="30"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="40" t="str">
+    <row r="22" ht="15" spans="2:5">
+      <c r="B22" s="34"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="67"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="37" t="str">
+    <row r="23" ht="14.25" spans="2:5">
+      <c r="B23" s="71"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="30"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="40" t="str">
+    <row r="24" ht="15" spans="2:5">
+      <c r="B24" s="34"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="67"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="37" t="str">
+    <row r="25" ht="14.25" spans="2:5">
+      <c r="B25" s="71"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="40" t="str">
+    <row r="26" ht="15" spans="2:5">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="67"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="37" t="str">
+    <row r="27" ht="14.25" spans="2:5">
+      <c r="B27" s="71"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="30"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="40" t="str">
+    <row r="28" ht="15" spans="2:5">
+      <c r="B28" s="34"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="67"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="37" t="str">
+    <row r="29" ht="14.25" spans="2:5">
+      <c r="B29" s="71"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="30"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="40" t="str">
+    <row r="30" ht="15" spans="2:5">
+      <c r="B30" s="34"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="67"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="37" t="str">
+    <row r="31" ht="14.25" spans="2:5">
+      <c r="B31" s="71"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="30"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="40" t="str">
+    <row r="32" ht="15" spans="2:5">
+      <c r="B32" s="34"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="67"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="37" t="str">
+    <row r="33" ht="14.25" spans="2:5">
+      <c r="B33" s="71"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="30"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="40" t="str">
+    <row r="34" ht="15" spans="2:5">
+      <c r="B34" s="34"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="70"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="47" t="str">
+    <row r="35" ht="14.25" spans="2:5">
+      <c r="B35" s="73"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -6195,250 +6216,250 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="21.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="17.7083333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.125" customWidth="1"/>
+    <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:6">
-      <c r="B2" s="35" t="s">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:6">
+      <c r="B2" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="36"/>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="38" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="40"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:6">
+      <c r="B3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="41" t="s">
+    <row r="4" ht="15" spans="2:6">
+      <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <v>10</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>10</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <v>20</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="46">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:6">
-      <c r="B5" s="43"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="44"/>
-    </row>
-    <row r="6" ht="19.5"/>
-    <row r="7" ht="18.75" spans="2:8">
-      <c r="B7" s="50" t="s">
+    <row r="5" ht="15" spans="2:6">
+      <c r="B5" s="47"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="48"/>
+    </row>
+    <row r="6" ht="15"/>
+    <row r="7" ht="15.75" spans="2:8">
+      <c r="B7" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="64"/>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="38" t="s">
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="68"/>
+    </row>
+    <row r="8" ht="14.25" spans="2:8">
+      <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="41" t="s">
+    <row r="9" ht="15" spans="2:8">
+      <c r="B9" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="46" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="38" t="s">
+    <row r="10" ht="14.25" spans="2:8">
+      <c r="B10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="37">
+      <c r="E10" s="31"/>
+      <c r="F10" s="41">
         <v>2</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="43" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="11" ht="30" spans="2:8">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="40">
+      <c r="E11" s="33"/>
+      <c r="F11" s="44">
         <v>6</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="46" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="38"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="39"/>
-    </row>
-    <row r="13" ht="18.75" spans="2:8">
-      <c r="B13" s="45"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="46"/>
-    </row>
-    <row r="14" ht="19.5"/>
-    <row r="15" ht="18.75" spans="2:9">
-      <c r="B15" s="35" t="s">
+    <row r="12" ht="14.25" spans="2:8">
+      <c r="B12" s="42"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="43"/>
+    </row>
+    <row r="13" ht="15.75" spans="2:8">
+      <c r="B13" s="49"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="50"/>
+    </row>
+    <row r="14" ht="15"/>
+    <row r="15" ht="15.75" spans="2:9">
+      <c r="B15" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="36"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="53" t="s">
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="40"/>
+    </row>
+    <row r="16" ht="14.25" spans="2:9">
+      <c r="B16" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G16" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="66" t="s">
+      <c r="I16" s="70" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" ht="15" spans="2:9">
       <c r="B17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="98" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="29">
+      <c r="E17" s="33">
         <v>1</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="33">
         <v>4</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="33">
         <f>PRODUCT(E17:F17)</f>
         <v>4</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="33">
         <v>30</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="46">
         <f>PRODUCT(H17,E17)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="66"/>
-    </row>
-    <row r="19" spans="2:9">
+    <row r="18" ht="14.25" spans="2:9">
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="70"/>
+    </row>
+    <row r="19" ht="15" spans="2:9">
       <c r="B19" s="5" t="s">
         <v>123</v>
       </c>
@@ -6446,149 +6467,149 @@
         <v>124</v>
       </c>
       <c r="D19" s="11"/>
-      <c r="E19" s="29">
+      <c r="E19" s="33">
         <v>2</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="33">
         <v>2</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="33">
         <f>PRODUCT(E19:F19)</f>
         <v>4</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="42">
+      <c r="H19" s="33"/>
+      <c r="I19" s="46">
         <f>PRODUCT(H19,E19)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="53" t="s">
+    <row r="20" ht="14.25" spans="2:9">
+      <c r="B20" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54">
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58">
         <v>1</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="58">
         <v>2</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="58">
         <f>PRODUCT(E20:F20)</f>
         <v>2</v>
       </c>
-      <c r="H20" s="54"/>
-      <c r="I20" s="66">
+      <c r="H20" s="58"/>
+      <c r="I20" s="70">
         <f>PRODUCT(H20,E20)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
         <v>126</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="29">
+      <c r="E21" s="33">
         <v>1</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="33">
         <v>2</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="33">
         <v>2</v>
       </c>
-      <c r="H21" s="29"/>
-      <c r="I21" s="42"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="66"/>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="H21" s="33"/>
+      <c r="I21" s="46"/>
+    </row>
+    <row r="22" ht="14.25" spans="2:9">
+      <c r="B22" s="57"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="70"/>
+    </row>
+    <row r="23" ht="15" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="42"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="53"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="66"/>
-    </row>
-    <row r="25" spans="2:9">
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="46"/>
+    </row>
+    <row r="24" ht="14.25" spans="2:9">
+      <c r="B24" s="57"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="70"/>
+    </row>
+    <row r="25" ht="15" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="42"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="53"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="66"/>
-    </row>
-    <row r="27" spans="2:9">
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="46"/>
+    </row>
+    <row r="26" ht="14.25" spans="2:9">
+      <c r="B26" s="57"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="70"/>
+    </row>
+    <row r="27" ht="15" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="42"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="53"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="66"/>
-    </row>
-    <row r="29" ht="18.75" spans="2:9">
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="46"/>
+    </row>
+    <row r="28" ht="14.25" spans="2:9">
+      <c r="B28" s="57"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="70"/>
+    </row>
+    <row r="29" ht="15.75" spans="2:9">
       <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="46"/>
-    </row>
-    <row r="30" ht="18.75"/>
-    <row r="31" ht="18.75"/>
-    <row r="32" ht="18.75" spans="2:4">
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="50"/>
+    </row>
+    <row r="30" ht="14.25"/>
+    <row r="31" ht="14.25"/>
+    <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="56">
+      <c r="C32" s="60">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
         <v>35</v>
       </c>
@@ -6598,26 +6619,26 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="C33" s="58">
+      <c r="C33" s="62">
         <f>Clebina!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="63"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="60" t="str">
+      <c r="C34" s="64" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D34" s="61"/>
-    </row>
-    <row r="35" ht="18.75"/>
+      <c r="D34" s="65"/>
+    </row>
+    <row r="35" ht="14.25"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6649,667 +6670,667 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="7" width="11.425" customWidth="1"/>
-    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
-    <col min="9" max="9" width="21.425" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="13.85" customWidth="1"/>
-    <col min="12" max="12" width="21.425" customWidth="1"/>
-    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
-    <col min="14" max="14" width="9.85" customWidth="1"/>
-    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="7" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
+    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="21.375" customWidth="1"/>
+    <col min="13" max="13" width="26.75" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E3" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F3" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>-5</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="43">
         <v>2</v>
       </c>
-      <c r="F3" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-6</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M3" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="O3" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16">
-      <c r="B4" s="28" t="s">
+    </row>
+    <row r="4" ht="15" spans="2:16">
+      <c r="B4" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F4" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E4" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K4" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O4" s="41" t="s">
+      <c r="O4" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="46">
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:16">
-      <c r="B5" s="26" t="s">
+    <row r="5" ht="15" spans="2:16">
+      <c r="B5" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E5" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="O5" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="2:13">
+      <c r="B6" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="33">
+        <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>4</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B7" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="31">
+        <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E7" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K7" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L7" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M7" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O5" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="44">
+      <c r="O7" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="P7" s="40"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="33">
+        <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="6" ht="19.5" spans="2:13">
-      <c r="B6" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="29" t="s">
+      <c r="E8" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="O8" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="43">
+        <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="2:16">
+      <c r="B9" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="31">
+        <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F9" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>12</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="O9" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="46">
+        <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:16">
+      <c r="B10" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="29">
-        <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
+      <c r="D10" s="33">
+        <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E10" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="27">
-        <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E7" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K10" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L10" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M10" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O7" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="29">
-        <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="39">
-        <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16">
-      <c r="B9" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="27">
-        <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E9" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="42">
-        <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16">
-      <c r="B10" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="29">
-        <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
-      <c r="B11" s="26" t="s">
+    <row r="11" ht="15" spans="2:16">
+      <c r="B11" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E11" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K11" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
-      <c r="B12" s="28" t="s">
+    <row r="12" ht="15" spans="2:16">
+      <c r="B12" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E12" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="O12" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="43">
+        <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+    </row>
+    <row r="13" ht="15.75" spans="2:16">
+      <c r="B13" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="31">
+        <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+      <c r="E13" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>-5</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="P13" s="50">
+        <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" spans="2:13">
+      <c r="B14" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="33">
+        <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:13">
+      <c r="B15" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="31">
+        <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E15" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F15" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K12" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L12" s="29" t="s">
+      <c r="K15" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L15" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M15" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O12" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="39">
-        <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" spans="2:16">
-      <c r="B13" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="27">
-        <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E13" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+    </row>
+    <row r="16" ht="15" spans="2:13">
+      <c r="B16" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="33">
+        <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F16" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-6</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="P13" s="46">
-        <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" spans="2:13">
-      <c r="B14" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="29">
-        <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="27">
-        <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E15" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K16" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L16" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M16" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="29">
-        <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E16" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17">
-      <c r="B17" s="26" t="s">
+    <row r="17" ht="14.25" spans="2:17">
+      <c r="B17" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="31">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E17" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F17" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="41" t="s">
         <v>142</v>
       </c>
       <c r="Q17" t="str">
@@ -7317,583 +7338,583 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="28" t="s">
+    <row r="18" ht="15" spans="2:13">
+      <c r="B18" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="33">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E18" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:13">
+      <c r="B19" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="31">
+        <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>4</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:13">
+      <c r="B20" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="33">
+        <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="F18" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="E20" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>-5</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:13">
+      <c r="B21" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="31">
+        <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>11</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:13">
+      <c r="B22" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="33">
+        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G22" s="33">
         <v>2</v>
       </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>16</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:13">
+      <c r="B23" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="31">
+        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="M23" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="2:13">
+      <c r="B24" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="33">
+        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:13">
+      <c r="B25" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="31">
+        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F25" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="L25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="2:13">
+      <c r="B26" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="33">
+        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E26" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F26" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:13">
+      <c r="B27" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="31">
+        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E27" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G27" s="31">
+        <v>2</v>
+      </c>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:13">
+      <c r="B28" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="33">
+        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E28" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F28" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:13">
+      <c r="B29" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="31">
+        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E29" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F29" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L29" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M29" s="41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:13">
+      <c r="B30" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="33">
+        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E30" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F30" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>10</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K30" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L30" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M30" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="27">
-        <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F19" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+    <row r="31" ht="14.25" spans="2:13">
+      <c r="B31" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" s="31">
+        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F31" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L19" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="29">
-        <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E20" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F20" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-6</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="27">
-        <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E21" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F21" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K31" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="L31" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L21" s="27" t="s">
+      <c r="M31" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="37" t="s">
+    </row>
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="33">
+        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F32" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L32" s="33" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="29">
-        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E22" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F22" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G22" s="29">
-        <v>2</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
+      <c r="M32" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" s="36">
+        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E33" s="36">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="36">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>12</v>
       </c>
-      <c r="K22" s="29" t="s">
+      <c r="K33" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="L22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="40" t="s">
+      <c r="L33" s="36" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="2:13">
-      <c r="B23" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="27">
-        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E23" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F23" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K23" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L23" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13">
-      <c r="B24" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="29">
-        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E24" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F24" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
-      <c r="B25" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="27">
-        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13">
-      <c r="B26" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="29">
-        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E26" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F26" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
-      <c r="B27" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="27">
-        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E27" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G27" s="27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M27" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
-      <c r="B28" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="29">
-        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E28" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F28" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K28" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L28" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="27">
-        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E29" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F29" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K29" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M29" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13">
-      <c r="B30" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="29">
-        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E30" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F30" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M30" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13">
-      <c r="B31" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="27">
-        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F31" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K31" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13">
-      <c r="B32" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="29">
-        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F32" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="32">
-        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33" s="32">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F33" s="32">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="M33" s="47" t="s">
+      <c r="M33" s="51" t="s">
         <v>142</v>
       </c>
     </row>
@@ -7915,1249 +7936,1249 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="7" width="11.425" customWidth="1"/>
-    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
-    <col min="9" max="9" width="21.425" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="13.85" customWidth="1"/>
-    <col min="12" max="12" width="21.425" customWidth="1"/>
-    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
-    <col min="14" max="14" width="9.85" customWidth="1"/>
-    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="7" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
+    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="21.375" customWidth="1"/>
+    <col min="13" max="13" width="26.75" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="27" t="str">
+      <c r="E3" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F3" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D16,0)</f>
-        <v>-6</v>
-      </c>
-      <c r="K3" s="27" t="s">
+        <v>-3</v>
+      </c>
+      <c r="K3" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="39">
+      <c r="P3" s="43">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
-      <c r="B4" s="28" t="s">
+    <row r="4" ht="15" spans="2:16">
+      <c r="B4" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F4" s="29" t="str">
+      <c r="E4" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F4" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D17,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K4" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O4" s="41" t="s">
+      <c r="O4" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="46">
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:16">
-      <c r="B5" s="26" t="s">
+    <row r="5" ht="15" spans="2:16">
+      <c r="B5" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="27" t="str">
+      <c r="E5" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F5" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C1,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="48">
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="19.5" spans="2:13">
-      <c r="B6" s="28" t="s">
+    <row r="6" ht="16.5" spans="2:13">
+      <c r="B6" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="29" t="str">
+      <c r="E6" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F6" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K6" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="44" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="27" t="str">
+      <c r="E7" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C3,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K7" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O7" s="35" t="s">
+      <c r="O7" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="P7" s="36"/>
+      <c r="P7" s="40"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="29">
+      <c r="E8" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F8" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C4,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K8" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O8" s="38" t="s">
+      <c r="O8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="43">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
-      <c r="B9" s="26" t="s">
+    <row r="9" ht="15" spans="2:16">
+      <c r="B9" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F9" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C5,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="46">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
-      <c r="B10" s="28" t="s">
+    <row r="10" ht="15" spans="2:16">
+      <c r="B10" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="29" t="str">
+      <c r="E10" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C6,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K10" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
-      <c r="B11" s="26" t="s">
+    <row r="11" ht="15" spans="2:16">
+      <c r="B11" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="27" t="str">
+      <c r="E11" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F11" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C7,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K11" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
-      <c r="B12" s="28" t="s">
+    <row r="12" ht="15" spans="2:16">
+      <c r="B12" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F12" s="29" t="str">
+      <c r="E12" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F12" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C8,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K12" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="43">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="2:16">
-      <c r="B13" s="26" t="s">
+    <row r="13" ht="15.75" spans="2:16">
+      <c r="B13" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="27" t="str">
+      <c r="E13" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F13" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C9,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="L13" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="46">
+      <c r="P13" s="50">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:13">
-      <c r="B14" s="28" t="s">
+    <row r="14" ht="15.75" spans="2:13">
+      <c r="B14" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="E14" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F14" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29">
+      <c r="G14" s="33"/>
+      <c r="H14" s="33">
         <v>1</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C10,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K14" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="26" t="s">
+    <row r="15" ht="14.25" spans="2:13">
+      <c r="B15" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F15" s="27" t="str">
+      <c r="E15" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F15" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C11,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K15" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L15" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="28" t="s">
+    <row r="16" ht="15" spans="2:13">
+      <c r="B16" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F16" s="29" t="str">
+      <c r="E16" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F16" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C12,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K16" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M16" s="40" t="s">
+      <c r="M16" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="26" t="s">
+    <row r="17" ht="14.25" spans="2:13">
+      <c r="B17" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="31">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="27" t="str">
+      <c r="E17" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F17" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C13,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="28" t="s">
+    <row r="18" ht="15" spans="2:13">
+      <c r="B18" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="33">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="E18" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F18" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C14,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K18" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L18" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="26" t="s">
+    <row r="19" ht="14.25" spans="2:13">
+      <c r="B19" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="31">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F19" s="27" t="str">
+      <c r="E19" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F19" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C15,0)</f>
-        <v>3</v>
-      </c>
-      <c r="K19" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="27" t="s">
+      <c r="L19" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="M19" s="37" t="s">
+      <c r="M19" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="28" t="s">
+    <row r="20" ht="15" spans="2:13">
+      <c r="B20" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="33">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F20" s="29" t="str">
+      <c r="E20" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F20" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K20" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="29" t="s">
+      <c r="L20" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M20" s="40" t="s">
+      <c r="M20" s="44" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="26" t="s">
+    <row r="21" ht="14.25" spans="2:13">
+      <c r="B21" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="31">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F21" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C17,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K21" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L21" s="27" t="s">
+      <c r="L21" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="37" t="s">
+      <c r="M21" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="28" t="s">
+    <row r="22" ht="15" spans="2:13">
+      <c r="B22" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="33">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F22" s="29">
+      <c r="E22" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F22" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="33">
         <v>2</v>
       </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C18,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K22" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L22" s="29" t="s">
+      <c r="L22" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="2:13">
-      <c r="B23" s="26" t="s">
+    <row r="23" ht="14.25" spans="2:13">
+      <c r="B23" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="31">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E23" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F23" s="27" t="str">
+      <c r="E23" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F23" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C19,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K23" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="27" t="s">
+      <c r="L23" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="2:13">
-      <c r="B24" s="28" t="s">
+    <row r="24" ht="15" spans="2:13">
+      <c r="B24" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="33">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F24" s="29">
+      <c r="E24" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F24" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C20,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K24" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L24" s="29" t="s">
+      <c r="L24" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M24" s="40" t="s">
+      <c r="M24" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:13">
-      <c r="B25" s="26" t="s">
+    <row r="25" ht="14.25" spans="2:13">
+      <c r="B25" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="31">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E25" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="27">
+      <c r="E25" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F25" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C21,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L25" s="27" t="s">
+      <c r="L25" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="M25" s="37" t="s">
+      <c r="M25" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="2:13">
-      <c r="B26" s="30" t="s">
+    <row r="26" ht="15" spans="2:13">
+      <c r="B26" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="33">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E26" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F26" s="29">
+      <c r="E26" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F26" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C22,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K26" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="L26" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M26" s="40" t="s">
+      <c r="M26" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="2:13">
-      <c r="B27" s="26" t="s">
+    <row r="27" ht="14.25" spans="2:13">
+      <c r="B27" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="31">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E27" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="27">
+      <c r="E27" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F27" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="31">
         <v>2</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D40,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K27" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="27" t="s">
+      <c r="L27" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
-      <c r="B28" s="28" t="s">
+    <row r="28" ht="15" spans="2:13">
+      <c r="B28" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="33">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E28" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F28" s="29" t="str">
+      <c r="E28" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F28" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K1,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K28" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="K28" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L28" s="29" t="s">
+      <c r="L28" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="M28" s="40" t="s">
+      <c r="M28" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="26" t="s">
+    <row r="29" ht="14.25" spans="2:13">
+      <c r="B29" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="31">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E29" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F29" s="27" t="str">
+      <c r="E29" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F29" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K2,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K29" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L29" s="27" t="s">
+      <c r="L29" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M29" s="37" t="s">
+      <c r="M29" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="2:13">
-      <c r="B30" s="28" t="s">
+    <row r="30" ht="15" spans="2:13">
+      <c r="B30" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="33">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E30" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F30" s="29">
+      <c r="E30" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F30" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K30" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="L30" s="29" t="s">
+      <c r="L30" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M30" s="40" t="s">
+      <c r="M30" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="2:13">
-      <c r="B31" s="26" t="s">
+    <row r="31" ht="14.25" spans="2:13">
+      <c r="B31" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="31">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E31" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F31" s="27">
+      <c r="E31" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F31" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K31" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="L31" s="27" t="s">
+      <c r="L31" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="M31" s="37" t="s">
+      <c r="M31" s="41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="2:13">
-      <c r="B32" s="28" t="s">
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="33">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E32" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F32" s="29" t="str">
+      <c r="E32" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F32" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K32" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L32" s="29" t="s">
+      <c r="L32" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M32" s="40" t="s">
+      <c r="M32" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="31" t="s">
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="36">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E33" s="32">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="F33" s="32">
+      <c r="E33" s="36">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F33" s="36">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K33" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="L33" s="32" t="s">
+      <c r="L33" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="M33" s="47" t="s">
+      <c r="M33" s="51" t="s">
         <v>142</v>
       </c>
     </row>
@@ -9178,18 +9199,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="B1:N23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="3" width="10.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
-    <col min="8" max="8" width="20.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="19.85" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="2" max="3" width="10.25" customWidth="1"/>
+    <col min="4" max="4" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="20.25" customWidth="1"/>
+    <col min="9" max="9" width="19.875" customWidth="1"/>
+    <col min="10" max="10" width="23.125" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:13">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:14">
       <c r="B2" s="1" t="s">
         <v>179</v>
       </c>
@@ -9206,18 +9228,21 @@
       <c r="I2" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="N2" s="2">
         <f>12+Clebina!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" ht="14.25" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9236,18 +9261,21 @@
       <c r="I3" s="12">
         <v>1</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="23">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4">
         <f>ROUNDDOWN(I3/2,0)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="18.75" spans="2:13">
+    <row r="4" ht="15.75" spans="2:14">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9263,21 +9291,24 @@
       <c r="H4" s="16">
         <v>1000</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="24">
         <v>2</v>
       </c>
-      <c r="J4" s="6">
-        <f t="shared" ref="J4:J22" si="0">ROUNDDOWN(I4/2,0)</f>
+      <c r="J4" s="25">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:K22" si="0">ROUNDDOWN(I4/2,0)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="N4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:10">
+    <row r="5" ht="15" spans="2:11">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9290,12 +9321,15 @@
       <c r="I5" s="12">
         <v>3</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="23">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" ht="15" spans="2:11">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9305,15 +9339,18 @@
       <c r="H6" s="16">
         <v>6000</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="24">
         <v>4</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="25">
+        <v>4</v>
+      </c>
+      <c r="K6" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" ht="14.25" spans="2:11">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9326,12 +9363,15 @@
       <c r="I7" s="12">
         <v>5</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="23">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="2:10">
+    <row r="8" ht="15.75" spans="2:11">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9341,53 +9381,65 @@
       <c r="H8" s="16">
         <v>15000</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="24">
         <v>6</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="25">
+        <v>5</v>
+      </c>
+      <c r="K8" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="18.75" spans="8:10">
+    <row r="9" ht="15" spans="8:11">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
       <c r="I9" s="12">
         <v>7</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="23">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" ht="15" spans="8:11">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="24">
         <v>8</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="25">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="18.75" spans="8:10">
+    <row r="11" ht="15" spans="8:11">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
       <c r="I11" s="12">
         <v>9</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="23">
+        <v>8</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="18.75" spans="2:10">
+    <row r="12" ht="15.75" spans="2:11">
       <c r="B12" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9396,20 +9448,23 @@
       <c r="H12" s="16">
         <v>45000</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="24">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="25">
+        <v>9</v>
+      </c>
+      <c r="K12" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" ht="14.25" spans="2:11">
       <c r="B13" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="4">
-        <f>SUM(M3:M4)</f>
+        <f>SUM(N3:N4)</f>
         <v>5</v>
       </c>
       <c r="H13" s="17">
@@ -9418,46 +9473,55 @@
       <c r="I13" s="12">
         <v>11</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="23">
+        <v>9</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:10">
+    <row r="14" ht="15.75" spans="2:11">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
         <v>66000</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="24">
         <v>12</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="25">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="19.5" spans="8:10">
+    <row r="15" ht="15.75" spans="8:11">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
       <c r="I15" s="12">
         <v>13</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="23">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="18.75" spans="2:10">
+    <row r="16" ht="15.75" spans="2:11">
       <c r="B16" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>
@@ -9465,15 +9529,18 @@
       <c r="H16" s="16">
         <v>91000</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="24">
         <v>14</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="25">
+        <v>11</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" ht="15" spans="2:11">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9491,12 +9558,15 @@
       <c r="I17" s="12">
         <v>15</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="23">
+        <v>13</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" ht="15" spans="2:11">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9511,15 +9581,18 @@
       <c r="H18" s="16">
         <v>120000</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="24">
         <v>16</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="25">
+        <v>14</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" ht="15" spans="2:11">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9537,12 +9610,15 @@
       <c r="I19" s="12">
         <v>17</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="23">
+        <v>14</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" ht="15" spans="2:11">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9557,15 +9633,18 @@
       <c r="H20" s="16">
         <v>153000</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="24">
         <v>18</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="25">
+        <v>15</v>
+      </c>
+      <c r="K20" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" ht="15" spans="2:11">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9585,12 +9664,15 @@
       <c r="I21" s="12">
         <v>19</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="23">
+        <v>15</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="18.75" spans="2:10">
+    <row r="22" ht="15.75" spans="2:11">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9605,15 +9687,18 @@
       <c r="H22" s="20">
         <v>190000</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="26">
         <v>20</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="27">
+        <v>16</v>
+      </c>
+      <c r="K22" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="18.75"/>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12315" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="189">
   <si>
     <t>Atributos</t>
   </si>
@@ -1051,7 +1051,7 @@
     <t>Armadura de Gelo Eterno</t>
   </si>
   <si>
-    <t>Alabarda</t>
+    <t>Martelo de Guerra</t>
   </si>
   <si>
     <t>Status Anteriores</t>
@@ -1300,15 +1300,12 @@
     <t>Equilibrada</t>
   </si>
   <si>
-    <t>1d12</t>
+    <t>1d10</t>
   </si>
   <si>
     <t>Material Especial (adamante)</t>
   </si>
   <si>
-    <t>Cortante/Perfurante</t>
-  </si>
-  <si>
     <t>x3</t>
   </si>
   <si>
@@ -1505,9 +1502,6 @@
   </si>
   <si>
     <t>Nível de Personagem</t>
-  </si>
-  <si>
-    <t>Bônus em Perícias Treinadas</t>
   </si>
   <si>
     <t>Bônus em Perícias</t>
@@ -1539,8 +1533,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -1588,7 +1582,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1596,7 +1604,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1610,23 +1633,55 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1634,6 +1689,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1656,44 +1718,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
@@ -1701,31 +1725,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1734,13 +1735,6 @@
       <sz val="9"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1776,7 +1770,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1788,61 +1860,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1860,7 +1890,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1872,7 +1920,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1884,79 +1950,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2105,45 +2099,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -2223,6 +2178,19 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2264,6 +2232,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thick">
         <color auto="1"/>
@@ -2272,6 +2253,19 @@
         <color auto="1"/>
       </top>
       <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -2479,6 +2473,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2518,6 +2523,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2541,180 +2570,145 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="41" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="40" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2724,7 +2718,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2789,161 +2783,149 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2999,10 +2981,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4348,414 +4330,414 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="40" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="48">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
         <v>6</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="K2" s="39" t="s">
+      <c r="H2" s="36"/>
+      <c r="K2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="40"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:14">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="27">
         <f>'uns dados aí'!C3+(VLOOKUP(B3,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>16</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="39">
         <f t="shared" ref="D3:D8" si="0">ROUNDDOWN((C3-10)/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="27">
         <f>H3-L25-SUM(L4:L22)</f>
         <v>33</v>
       </c>
-      <c r="H3" s="43">
-        <f>'uns dados aí'!N2+((G2-1)*'uns dados aí'!C12)</f>
+      <c r="H3" s="39">
+        <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
         <v>33</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="M3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="43" t="s">
+      <c r="N3" s="39" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:14">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="29">
         <f>'uns dados aí'!C4+(VLOOKUP(B4,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>14</v>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="42">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
         <v>30</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
         <v>30</v>
       </c>
-      <c r="K4" s="45">
+      <c r="K4" s="41">
         <v>1</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="46"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="42"/>
     </row>
     <row r="5" ht="14.25" spans="2:14">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="27">
         <f>'uns dados aí'!C5+(VLOOKUP(B5,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="37">
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="94"/>
-      <c r="K5" s="42">
+      <c r="H5" s="90"/>
+      <c r="K5" s="38">
         <v>2</v>
       </c>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="43"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="39"/>
     </row>
     <row r="6" ht="15" spans="2:14">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="29">
         <f>'uns dados aí'!C6+(VLOOKUP(B6,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>22</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="42">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="40">
         <f>G5+Perícias!J12</f>
-        <v>31</v>
-      </c>
-      <c r="H6" s="95"/>
-      <c r="K6" s="45">
+        <v>28</v>
+      </c>
+      <c r="H6" s="91"/>
+      <c r="K6" s="41">
         <v>3</v>
       </c>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="46"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="42"/>
     </row>
     <row r="7" ht="14.25" spans="2:14">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="27">
         <f>'uns dados aí'!C7+(VLOOKUP(B7,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>18</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="37">
         <f>Perícias!J27+Perícias!J21</f>
-        <v>25</v>
-      </c>
-      <c r="H7" s="94"/>
-      <c r="K7" s="42">
+        <v>19</v>
+      </c>
+      <c r="H7" s="90"/>
+      <c r="K7" s="38">
         <v>4</v>
       </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="43"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="39"/>
     </row>
     <row r="8" ht="15.75" spans="2:14">
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="52">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D8" s="50">
+      <c r="D8" s="46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="92">
         <v>0.5</v>
       </c>
-      <c r="H8" s="97"/>
-      <c r="K8" s="45">
+      <c r="H8" s="93"/>
+      <c r="K8" s="41">
         <v>5</v>
       </c>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="46"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="42"/>
     </row>
     <row r="9" ht="15" spans="6:14">
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="27">
         <v>682</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="K9" s="42">
+      <c r="H9" s="39"/>
+      <c r="K9" s="38">
         <v>6</v>
       </c>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="43"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="39"/>
     </row>
     <row r="10" ht="15.75" spans="6:14">
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="56">
-        <v>15000</v>
-      </c>
-      <c r="H10" s="50"/>
-      <c r="K10" s="45">
+      <c r="G10" s="52">
+        <v>15850</v>
+      </c>
+      <c r="H10" s="46"/>
+      <c r="K10" s="41">
         <v>7</v>
       </c>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="46"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="42"/>
     </row>
     <row r="11" ht="15.75" spans="11:14">
-      <c r="K11" s="42">
+      <c r="K11" s="38">
         <v>8</v>
       </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="43"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="39"/>
     </row>
     <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78"/>
-      <c r="K12" s="45">
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="74"/>
+      <c r="K12" s="41">
         <v>9</v>
       </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="46"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="42"/>
     </row>
     <row r="13" ht="15.75" spans="2:14">
-      <c r="B13" s="93"/>
-      <c r="K13" s="42">
+      <c r="B13" s="89"/>
+      <c r="K13" s="38">
         <v>10</v>
       </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="43"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="39"/>
     </row>
     <row r="14" ht="15.75" spans="2:14">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="40"/>
-      <c r="F14" s="39" t="s">
+      <c r="C14" s="48"/>
+      <c r="D14" s="36"/>
+      <c r="F14" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="40"/>
-      <c r="K14" s="45">
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="36"/>
+      <c r="K14" s="41">
         <v>11</v>
       </c>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="46"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="42"/>
     </row>
     <row r="15" ht="14.25" spans="2:14">
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="43" t="s">
+      <c r="I15" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="38">
         <v>12</v>
       </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="43"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="39"/>
     </row>
     <row r="16" ht="30.75" spans="2:14">
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="52">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,2,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="46">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,3,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="56" t="str">
+      <c r="G16" s="52" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
-        <v>1d12</v>
-      </c>
-      <c r="H16" s="56">
+        <v>1d10</v>
+      </c>
+      <c r="H16" s="52">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,4,FALSE),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="50" t="str">
+      <c r="I16" s="46" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
         <v>x3</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="41">
         <v>13</v>
       </c>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="46"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="42"/>
     </row>
     <row r="17" ht="15" spans="11:14">
-      <c r="K17" s="42">
+      <c r="K17" s="38">
         <v>14</v>
       </c>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="43"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="39"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K18" s="45">
+      <c r="K18" s="41">
         <v>15</v>
       </c>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="46"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="42"/>
     </row>
     <row r="19" ht="14.25" spans="11:14">
-      <c r="K19" s="42">
+      <c r="K19" s="38">
         <v>16</v>
       </c>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="43"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="39"/>
     </row>
     <row r="20" ht="15" spans="11:14">
-      <c r="K20" s="45">
+      <c r="K20" s="41">
         <v>17</v>
       </c>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="46"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="42"/>
     </row>
     <row r="21" ht="14.25" spans="11:14">
-      <c r="K21" s="42">
+      <c r="K21" s="38">
         <v>18</v>
       </c>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="43"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="39"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K22" s="49">
+      <c r="K22" s="45">
         <v>20</v>
       </c>
-      <c r="L22" s="56"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="50"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="46"/>
     </row>
     <row r="23" ht="15"/>
     <row r="24" ht="15.75" spans="11:12">
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="40"/>
+      <c r="L24" s="36"/>
     </row>
     <row r="25" ht="14.25" spans="11:12">
-      <c r="K25" s="42" t="s">
+      <c r="K25" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="43"/>
+      <c r="L25" s="39"/>
     </row>
     <row r="26" ht="15.75" spans="11:12">
-      <c r="K26" s="49" t="s">
+      <c r="K26" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="50"/>
+      <c r="L26" s="46"/>
     </row>
     <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -4800,334 +4782,334 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="78"/>
-      <c r="I1" s="76" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="74"/>
+      <c r="I1" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="78"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74"/>
     </row>
     <row r="2" ht="15"/>
     <row r="3" ht="15.75" spans="2:13">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52" t="s">
+      <c r="C3" s="48"/>
+      <c r="D3" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="40"/>
-      <c r="K3" s="80" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="36"/>
+      <c r="K3" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="81" t="s">
+      <c r="L3" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="89" t="s">
+      <c r="M3" s="85" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="43" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="K4" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="83" t="s">
+      <c r="L4" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="90"/>
+      <c r="M4" s="86"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="40"/>
+      <c r="D5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="46" t="s">
+      <c r="E5" s="29"/>
+      <c r="F5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="K5" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="85" t="s">
+      <c r="L5" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="91"/>
+      <c r="M5" s="87"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="31" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="43" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="82" t="s">
+      <c r="K6" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="83" t="s">
+      <c r="L6" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="90"/>
+      <c r="M6" s="86"/>
     </row>
     <row r="7" ht="15" spans="2:13">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="29"/>
+      <c r="D7" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="46" t="s">
+      <c r="E7" s="29"/>
+      <c r="F7" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="84" t="s">
+      <c r="K7" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="85" t="s">
+      <c r="L7" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="91"/>
+      <c r="M7" s="87"/>
     </row>
     <row r="8" ht="14.25" spans="2:13">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="43" t="s">
+      <c r="E8" s="27"/>
+      <c r="F8" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="82" t="s">
+      <c r="K8" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="86" t="s">
+      <c r="L8" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="90"/>
+      <c r="M8" s="86"/>
     </row>
     <row r="9" ht="15" spans="2:13">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="46" t="s">
+      <c r="E9" s="29"/>
+      <c r="F9" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="84"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="91"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="87"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="43" t="s">
+      <c r="E10" s="27"/>
+      <c r="F10" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="82"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="90"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="86"/>
     </row>
     <row r="11" ht="15" spans="2:13">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33" t="s">
+      <c r="C11" s="29"/>
+      <c r="D11" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="46" t="s">
+      <c r="E11" s="29"/>
+      <c r="F11" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="84"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="91"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="87"/>
     </row>
     <row r="12" ht="14.25" spans="2:13">
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31" t="s">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="43" t="s">
+      <c r="E12" s="27"/>
+      <c r="F12" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="82"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="90"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="86"/>
     </row>
     <row r="13" ht="15" spans="2:13">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33" t="s">
+      <c r="C13" s="29"/>
+      <c r="D13" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="46" t="s">
+      <c r="E13" s="29"/>
+      <c r="F13" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="79"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="91"/>
+      <c r="G13" s="75"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="87"/>
     </row>
     <row r="14" ht="14.25" spans="2:13">
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="43"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="90"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="39"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="86"/>
     </row>
     <row r="15" ht="15" spans="2:13">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="46"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="91"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="42"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="87"/>
     </row>
     <row r="16" ht="14.25" spans="2:13">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="43"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="90"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="39"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="86"/>
     </row>
     <row r="17" ht="15" spans="2:13">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="46"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="91"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="42"/>
+      <c r="K17" s="80"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="87"/>
     </row>
     <row r="18" ht="14.25" spans="2:13">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="43"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="90"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="39"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="86"/>
     </row>
     <row r="19" ht="15" spans="2:13">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="46"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="91"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="42"/>
+      <c r="K19" s="80"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="87"/>
     </row>
     <row r="20" ht="14.25" spans="2:13">
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="43"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="90"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="39"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="86"/>
     </row>
     <row r="21" ht="15" spans="2:13">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="46"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="85"/>
-      <c r="M21" s="91"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="42"/>
+      <c r="K21" s="80"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="87"/>
     </row>
     <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="48"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="92"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="44"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="88"/>
     </row>
     <row r="23" ht="14.25"/>
   </sheetData>
@@ -5193,550 +5175,550 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="68"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" ht="15" spans="2:8">
-      <c r="B3" s="42" t="str">
+      <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>-5</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>13</v>
-      </c>
-      <c r="E3" s="43">
+        <v>5</v>
+      </c>
+      <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>8</v>
-      </c>
-      <c r="G3" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="48">
+      <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="2:5">
-      <c r="B4" s="45" t="str">
+      <c r="B4" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="29">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>4</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
+        <v>7</v>
+      </c>
+      <c r="E4" s="42">
+        <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
         <v>11</v>
       </c>
-      <c r="E4" s="46">
-        <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>15</v>
-      </c>
     </row>
     <row r="5" ht="14.25" spans="2:5">
-      <c r="B5" s="42" t="str">
+      <c r="B5" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>6</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E5" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:5">
+      <c r="B6" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Atuação</v>
+      </c>
+      <c r="C6" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E6" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="2:5">
+      <c r="B7" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cavalgar</v>
+      </c>
+      <c r="C7" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D7" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E7" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="2:5">
+      <c r="B8" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Conhecimento</v>
+      </c>
+      <c r="C8" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D8" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E8" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="2:5">
+      <c r="B9" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cura</v>
+      </c>
+      <c r="C9" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D9" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E9" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:5">
+      <c r="B10" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Diplomacia</v>
+      </c>
+      <c r="C10" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E10" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
+      <c r="B11" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Enganação</v>
+      </c>
+      <c r="C11" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D11" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E11" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="2:5">
+      <c r="B12" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Fortitude</v>
+      </c>
+      <c r="C12" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D12" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E12" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="2:5">
+      <c r="B13" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Furtividade</v>
+      </c>
+      <c r="C13" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-5</v>
+      </c>
+      <c r="D13" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E13" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="2:5">
+      <c r="B14" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Guerra</v>
+      </c>
+      <c r="C14" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D14" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E14" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:5">
+      <c r="B15" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Iniciativa</v>
+      </c>
+      <c r="C15" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D15" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E15" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:5">
+      <c r="B16" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intimidação</v>
+      </c>
+      <c r="C16" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E16" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:5">
+      <c r="B17" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intuição</v>
+      </c>
+      <c r="C17" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D17" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E17" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:5">
+      <c r="B18" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Investigação</v>
+      </c>
+      <c r="C18" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D18" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E18" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:5">
+      <c r="B19" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Jogatina</v>
+      </c>
+      <c r="C19" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E19" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:5">
+      <c r="B20" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ladinagem</v>
+      </c>
+      <c r="C20" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-5</v>
+      </c>
+      <c r="D20" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E20" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:5">
+      <c r="B21" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Luta</v>
+      </c>
+      <c r="C21" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D21" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E21" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:5">
+      <c r="B22" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Misticismo</v>
+      </c>
+      <c r="C22" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>13</v>
+      </c>
+      <c r="D22" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E22" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:5">
+      <c r="B23" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Nobreza</v>
+      </c>
+      <c r="C23" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D23" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E23" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="2:5">
+      <c r="B24" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Alquimista)</v>
+      </c>
+      <c r="C24" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D24" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E24" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:5">
+      <c r="B25" s="38" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Armeiro)</v>
+      </c>
+      <c r="C25" s="27">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="2:5">
+      <c r="B26" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Engenhoqueiro)</v>
+      </c>
+      <c r="C26" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="6" ht="15" spans="2:5">
-      <c r="B6" s="45" t="str">
+      <c r="D26" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E26" s="42">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:5">
+      <c r="B27" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Atuação</v>
-      </c>
-      <c r="C6" s="33">
+        <v>Percepção</v>
+      </c>
+      <c r="C27" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D6" s="33">
+        <v>11</v>
+      </c>
+      <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E6" s="46">
+        <v>2</v>
+      </c>
+      <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
-      <c r="B7" s="42" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:5">
+      <c r="B28" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cavalgar</v>
-      </c>
-      <c r="C7" s="31">
+        <v>Pilotagem</v>
+      </c>
+      <c r="C28" s="29">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>5</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="2:5">
-      <c r="B8" s="45" t="str">
+    <row r="29" ht="14.25" spans="2:5">
+      <c r="B29" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Conhecimento</v>
-      </c>
-      <c r="C8" s="33">
+        <v>Pontaria</v>
+      </c>
+      <c r="C29" s="27">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D29" s="27">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E29" s="39">
+        <f ca="1" t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:5">
+      <c r="B30" s="41" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Reflexos</v>
+      </c>
+      <c r="C30" s="29">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D30" s="29">
+        <f ca="1" t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E30" s="42">
+        <f ca="1" t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="D8" s="33">
+    </row>
+    <row r="31" ht="15" spans="2:5">
+      <c r="B31" s="43" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Religião</v>
+      </c>
+      <c r="C31" s="49">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E8" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
-      <c r="B9" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cura</v>
-      </c>
-      <c r="C9" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>12</v>
-      </c>
-      <c r="D9" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E9" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="2:5">
-      <c r="B10" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Diplomacia</v>
-      </c>
-      <c r="C10" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D10" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E10" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
-      <c r="B11" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Enganação</v>
-      </c>
-      <c r="C11" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D11" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E11" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
-      <c r="B12" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Fortitude</v>
-      </c>
-      <c r="C12" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>9</v>
-      </c>
-      <c r="D12" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="2:5">
-      <c r="B13" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Furtividade</v>
-      </c>
-      <c r="C13" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-5</v>
-      </c>
-      <c r="D13" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E13" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
-      <c r="B14" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Guerra</v>
-      </c>
-      <c r="C14" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D14" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E14" s="46">
+        <v>16</v>
+      </c>
+      <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
         <v>23</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
-      <c r="B15" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Iniciativa</v>
-      </c>
-      <c r="C15" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D15" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E15" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intimidação</v>
-      </c>
-      <c r="C16" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E16" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intuição</v>
-      </c>
-      <c r="C17" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D17" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E17" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Investigação</v>
-      </c>
-      <c r="C18" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D18" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E18" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Jogatina</v>
-      </c>
-      <c r="C19" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D19" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E19" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ladinagem</v>
-      </c>
-      <c r="C20" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-5</v>
-      </c>
-      <c r="D20" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E20" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Luta</v>
-      </c>
-      <c r="C21" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D21" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E21" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Misticismo</v>
-      </c>
-      <c r="C22" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>16</v>
-      </c>
-      <c r="D22" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E22" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Nobreza</v>
-      </c>
-      <c r="C23" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>9</v>
-      </c>
-      <c r="D23" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="E23" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
-      <c r="B24" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Alquimista)</v>
-      </c>
-      <c r="C24" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D24" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E24" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Armeiro)</v>
-      </c>
-      <c r="C25" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D25" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E25" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="2:5">
-      <c r="B26" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Engenhoqueiro)</v>
-      </c>
-      <c r="C26" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D26" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E26" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Percepção</v>
-      </c>
-      <c r="C27" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>14</v>
-      </c>
-      <c r="D27" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E27" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pilotagem</v>
-      </c>
-      <c r="C28" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D28" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E28" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="42" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pontaria</v>
-      </c>
-      <c r="C29" s="31">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D29" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E29" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="45" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Reflexos</v>
-      </c>
-      <c r="C30" s="33">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>10</v>
-      </c>
-      <c r="D30" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E30" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
-      <c r="B31" s="47" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Religião</v>
-      </c>
-      <c r="C31" s="53">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D31" s="53">
-        <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E31" s="48">
-        <f ca="1" t="shared" si="1"/>
-        <v>10</v>
       </c>
     </row>
     <row r="32" ht="14.25"/>
@@ -5768,433 +5750,433 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="E2" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="40"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:8">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="27">
         <v>1</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="37">
         <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="38">
         <v>1</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:8">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="45">
+      <c r="G4" s="41">
         <v>2</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="42">
         <v>3</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="2:8">
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="27">
         <v>1</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="38">
         <v>3</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="39">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:8">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="29">
         <v>1</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="41">
         <v>4</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="42">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="15" spans="2:8">
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="27">
         <v>1</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="43">
         <v>5</v>
       </c>
-      <c r="H7" s="48">
+      <c r="H7" s="44">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="2:5">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="29">
         <v>1</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="2:6">
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="27">
         <v>1</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F9" s="75"/>
+      <c r="F9" s="71"/>
     </row>
     <row r="10" ht="15" spans="1:6">
-      <c r="A10" s="72"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="68"/>
+      <c r="B10" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="29">
         <v>1</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F10" s="72"/>
+      <c r="F10" s="68"/>
     </row>
     <row r="11" ht="14.25" spans="2:5">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="27">
         <v>2</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="37">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:5">
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="29">
         <v>1</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="40">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="2:5">
-      <c r="B13" s="71" t="s">
+      <c r="B13" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="27">
         <v>2</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="37">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
     <row r="14" ht="15" spans="2:5">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <v>2</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="40">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:5">
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="27">
         <v>2</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="37">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="29">
         <v>3</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="40">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="71"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="41" t="str">
+      <c r="B17" s="67"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="34"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="44" t="str">
+      <c r="B18" s="30"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="71"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="41" t="str">
+      <c r="B19" s="67"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="34"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="44" t="str">
+      <c r="B20" s="30"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="71"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="41" t="str">
+      <c r="B21" s="67"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="34"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="44" t="str">
+      <c r="B22" s="30"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="71"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="41" t="str">
+      <c r="B23" s="67"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" spans="2:5">
-      <c r="B24" s="34"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="44" t="str">
+      <c r="B24" s="30"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="71"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="41" t="str">
+      <c r="B25" s="67"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" spans="2:5">
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="44" t="str">
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="71"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="41" t="str">
+      <c r="B27" s="67"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="34"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="44" t="str">
+      <c r="B28" s="30"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="71"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="41" t="str">
+      <c r="B29" s="67"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="34"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="44" t="str">
+      <c r="B30" s="30"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:5">
-      <c r="B31" s="71"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="41" t="str">
+      <c r="B31" s="67"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" spans="2:5">
-      <c r="B32" s="34"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="44" t="str">
+      <c r="B32" s="30"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:5">
-      <c r="B33" s="71"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="41" t="str">
+      <c r="B33" s="67"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" spans="2:5">
-      <c r="B34" s="34"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="44" t="str">
+      <c r="B34" s="30"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" ht="14.25" spans="2:5">
-      <c r="B35" s="73"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="51" t="str">
+      <c r="B35" s="69"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="47" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -6225,391 +6207,391 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:6">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:6">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="39" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:6">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="29">
         <v>10</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <v>10</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="40">
         <v>20</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="42">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:6">
-      <c r="B5" s="47"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="48"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" ht="15"/>
     <row r="7" ht="15.75" spans="2:8">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="68"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" ht="14.25" spans="2:8">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="H8" s="39" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:8">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44" t="s">
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="46" t="s">
+      <c r="H9" s="42" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="2:8">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="41">
+      <c r="E10" s="27"/>
+      <c r="F10" s="37">
         <v>2</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="H10" s="39" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="11" ht="30" spans="2:8">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="44">
+      <c r="E11" s="29"/>
+      <c r="F11" s="40">
         <v>6</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="46" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="12" ht="14.25" spans="2:8">
-      <c r="B12" s="42"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="43"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" ht="15.75" spans="2:8">
-      <c r="B13" s="49"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="50"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="46"/>
     </row>
     <row r="14" ht="15"/>
     <row r="15" ht="15.75" spans="2:9">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="36"/>
+    </row>
+    <row r="16" ht="14.25" spans="2:9">
+      <c r="B16" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" ht="14.25" spans="2:9">
-      <c r="B16" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58" t="s">
+      <c r="F16" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="G16" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" s="70" t="s">
+      <c r="I16" s="66" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" ht="15" spans="2:9">
       <c r="B17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="94" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="98" t="s">
-        <v>122</v>
-      </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="33">
+      <c r="E17" s="29">
         <v>1</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="29">
         <v>4</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="29">
         <f>PRODUCT(E17:F17)</f>
         <v>4</v>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="29">
         <v>30</v>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="42">
         <f>PRODUCT(H17,E17)</f>
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:9">
-      <c r="B18" s="57"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="70"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="66"/>
     </row>
     <row r="19" ht="15" spans="2:9">
       <c r="B19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="D19" s="11"/>
-      <c r="E19" s="33">
+      <c r="E19" s="29">
         <v>2</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="29">
         <v>2</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="29">
         <f>PRODUCT(E19:F19)</f>
         <v>4</v>
       </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="46">
+      <c r="H19" s="29"/>
+      <c r="I19" s="42">
         <f>PRODUCT(H19,E19)</f>
         <v>2</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="2:9">
-      <c r="B20" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58">
+      <c r="B20" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54">
         <v>1</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="54">
         <v>2</v>
       </c>
-      <c r="G20" s="58">
+      <c r="G20" s="54">
         <f>PRODUCT(E20:F20)</f>
         <v>2</v>
       </c>
-      <c r="H20" s="58"/>
-      <c r="I20" s="70">
+      <c r="H20" s="54"/>
+      <c r="I20" s="66">
         <f>PRODUCT(H20,E20)</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="33">
+      <c r="E21" s="29">
         <v>1</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="29">
         <v>2</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="29">
         <v>2</v>
       </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="46"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" ht="14.25" spans="2:9">
-      <c r="B22" s="57"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="70"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="66"/>
     </row>
     <row r="23" ht="15" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="46"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" ht="14.25" spans="2:9">
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="70"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" ht="15" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="46"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" ht="14.25" spans="2:9">
-      <c r="B26" s="57"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="70"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="66"/>
     </row>
     <row r="27" ht="15" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="46"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" ht="14.25" spans="2:9">
-      <c r="B28" s="57"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="70"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="66"/>
     </row>
     <row r="29" ht="15.75" spans="2:9">
       <c r="B29" s="7"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="50"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="46"/>
     </row>
     <row r="30" ht="14.25"/>
     <row r="31" ht="14.25"/>
     <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="60">
+        <v>126</v>
+      </c>
+      <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
         <v>35</v>
       </c>
@@ -6619,24 +6601,24 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
-      <c r="B33" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" s="62">
+      <c r="B33" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="58">
         <f>Clebina!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D33" s="63"/>
+      <c r="D33" s="59"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="64" t="str">
+        <v>128</v>
+      </c>
+      <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D34" s="65"/>
+      <c r="D34" s="61"/>
     </row>
     <row r="35" ht="14.25"/>
   </sheetData>
@@ -6689,649 +6671,649 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="G2" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="29" t="s">
+      <c r="J2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="37" t="s">
+      <c r="L2" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="M2" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="O2" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="P2" s="36"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="30" t="s">
+      <c r="C3" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="31">
+      <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F3" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>-5</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="M3" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="O3" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:16">
+      <c r="B4" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="O3" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F4" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F4" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33">
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="46">
+      <c r="P4" s="42">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="31">
+      <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F5" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F5" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>6</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="K5" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M5" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O5" s="47" t="s">
+      <c r="M5" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="44">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F6" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33">
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K6" s="33" t="s">
+      <c r="K6" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="44" t="s">
-        <v>142</v>
+      <c r="M6" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="31">
+      <c r="B7" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F7" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F7" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O7" s="39" t="s">
+      <c r="M7" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O7" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="36"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F8" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33">
+      <c r="F8" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="O8" s="42" t="s">
+      <c r="L8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O8" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="43">
+      <c r="P8" s="39">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="31">
+      <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F9" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31">
+      <c r="F9" s="27">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="M9" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="45" t="s">
+      <c r="L9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="46">
+      <c r="P9" s="42">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="B10" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F10" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F10" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33">
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K10" s="33" t="s">
+      <c r="K10" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="42" t="s">
+      <c r="M10" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="39">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="B11" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F11" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F11" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31">
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K11" s="31" t="s">
+      <c r="K11" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="45" t="s">
+      <c r="M11" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="46">
+      <c r="P11" s="42">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="33">
+      <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33">
+      <c r="F12" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K12" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L12" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="M12" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O12" s="42" t="s">
+      <c r="L12" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M12" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="39">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="B13" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F13" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F13" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31">
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>-5</v>
       </c>
-      <c r="K13" s="31" t="s">
+      <c r="K13" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="M13" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="M13" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="49" t="s">
+      <c r="O13" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="50">
+      <c r="P13" s="46">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F14" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33">
+      <c r="F14" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K14" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="29" t="s">
         <v>142</v>
       </c>
+      <c r="L14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="31">
+      <c r="B15" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F15" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F15" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="K15" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="41" t="s">
-        <v>142</v>
+      <c r="M15" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F16" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F16" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33">
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K16" s="33" t="s">
+      <c r="K16" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="44" t="s">
-        <v>142</v>
+      <c r="M16" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:17">
-      <c r="B17" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="31">
+      <c r="B17" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F17" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F17" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31">
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K17" s="31" t="s">
+      <c r="K17" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="41" t="s">
-        <v>142</v>
+      <c r="M17" s="37" t="s">
+        <v>141</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
@@ -7339,583 +7321,583 @@
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F18" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33">
+      <c r="F18" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K18" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="44" t="s">
-        <v>142</v>
+      <c r="L18" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="31">
+      <c r="B19" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F19" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F19" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31">
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>4</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M19" s="41" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F20" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F20" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33">
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>-5</v>
       </c>
-      <c r="K20" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M20" s="44" t="s">
-        <v>143</v>
+      <c r="K20" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="40" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="31">
+      <c r="C21" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F21" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31">
+      <c r="F21" s="27">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>8</v>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:13">
+      <c r="B22" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="29">
+        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="29">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G22" s="29">
+        <v>2</v>
+      </c>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>13</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:13">
+      <c r="B23" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="27">
+        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="27">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="2:13">
+      <c r="B24" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="29">
+        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="29">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>11</v>
       </c>
-      <c r="K21" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" s="31" t="s">
+      <c r="K24" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="41" t="s">
+      <c r="L24" s="29" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="33">
-        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
+      <c r="M24" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:13">
+      <c r="B25" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="27">
+        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E25" s="27">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F22" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G22" s="33">
+      <c r="F25" s="27">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>16</v>
-      </c>
-      <c r="K22" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="27" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="31">
-        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
+      <c r="L25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="2:13">
+      <c r="B26" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="29">
+        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E26" s="29">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F23" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+      <c r="F26" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>11</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:13">
+      <c r="B27" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="27">
+        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E27" s="27">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="27">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G27" s="27">
+        <v>2</v>
+      </c>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>11</v>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M27" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:13">
+      <c r="B28" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="29">
+        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E28" s="29">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F28" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31">
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:13">
+      <c r="B29" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="27">
+        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E29" s="27">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F29" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M29" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:13">
+      <c r="B30" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="29">
+        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E30" s="29">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F30" s="29">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M30" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="2:13">
+      <c r="B31" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="27">
+        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="27">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F31" s="27" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K31" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="29">
+        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="29">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F32" s="29" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M32" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="32">
+        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E33" s="32">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="32">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>9</v>
       </c>
-      <c r="K23" s="31" t="s">
+      <c r="K33" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="33">
-        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E24" s="33">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="31">
-        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="31">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K25" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="33">
-        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E26" s="33">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="31">
-        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E27" s="31">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G27" s="31">
-        <v>2</v>
-      </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M27" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="33">
-        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E28" s="33">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F28" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K28" s="33" t="s">
+      <c r="M33" s="47" t="s">
         <v>141</v>
-      </c>
-      <c r="L28" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="31">
-        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E29" s="31">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F29" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K29" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="L29" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M29" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="33">
-        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E30" s="33">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F30" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K30" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M30" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="31">
-        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31" s="31">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F31" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K31" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="L31" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="33">
-        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32" s="33">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F32" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K32" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="L32" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="36">
-        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33" s="36">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F33" s="36">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>5</v>
-      </c>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="M33" s="51" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -7955,1231 +7937,1231 @@
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="29" t="s">
+      <c r="F2" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="G2" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="29" t="s">
+      <c r="J2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="37" t="s">
+      <c r="L2" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="M2" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="O2" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="P2" s="36"/>
+    </row>
+    <row r="3" ht="14.25" spans="2:16">
+      <c r="B3" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="30" t="s">
+      <c r="C3" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="31">
+      <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F3" s="31" t="str">
+      <c r="E3" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F3" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D16,0)</f>
-        <v>-3</v>
-      </c>
-      <c r="K3" s="31" t="s">
+        <v>-5</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="M3" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="O3" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:16">
+      <c r="B4" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="O3" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F4" s="33" t="str">
+      <c r="E4" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33">
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D17,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K4" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="L4" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="45" t="s">
+      <c r="O4" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="46">
+      <c r="P4" s="42">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="31">
+      <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F5" s="31" t="str">
+      <c r="E5" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C1,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K5" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M5" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O5" s="47" t="s">
+      <c r="M5" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="44">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F6" s="33" t="str">
+      <c r="E6" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33">
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C2,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K6" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="44" t="s">
-        <v>142</v>
+      <c r="M6" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="31">
+      <c r="B7" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F7" s="31" t="str">
+      <c r="E7" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C3,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K7" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O7" s="39" t="s">
+      <c r="M7" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O7" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="36"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F8" s="33">
+      <c r="E8" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33">
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C4,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="O8" s="42" t="s">
+      <c r="L8" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O8" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="43">
+      <c r="P8" s="39">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="31">
+      <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F9" s="31">
+      <c r="E9" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F9" s="27">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C5,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="M9" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="45" t="s">
+      <c r="L9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="46">
+      <c r="P9" s="42">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="B10" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="33" t="str">
+      <c r="E10" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33">
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C6,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K10" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="42" t="s">
+      <c r="M10" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="39">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="B11" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F11" s="31" t="str">
+      <c r="E11" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31">
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C7,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K11" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="45" t="s">
+      <c r="M11" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="46">
+      <c r="P11" s="42">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="33">
+      <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F12" s="33" t="str">
+      <c r="E12" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33">
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C8,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K12" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L12" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M12" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="O12" s="42" t="s">
+      <c r="M12" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="39">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="B13" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F13" s="31" t="str">
+      <c r="E13" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F13" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31">
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C9,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K13" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="31" t="s">
+      <c r="M13" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="M13" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="49" t="s">
+      <c r="O13" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="50">
+      <c r="P13" s="46">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F14" s="33">
+      <c r="E14" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33">
+      <c r="G14" s="29"/>
+      <c r="H14" s="29">
         <v>1</v>
       </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33">
+      <c r="I14" s="29"/>
+      <c r="J14" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C10,0)</f>
-        <v>14</v>
-      </c>
-      <c r="K14" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="29" t="s">
         <v>142</v>
       </c>
+      <c r="L14" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="31">
+      <c r="B15" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F15" s="31" t="str">
+      <c r="E15" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F15" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31">
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C11,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K15" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="41" t="s">
-        <v>142</v>
+      <c r="M15" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F16" s="33" t="str">
+      <c r="E16" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F16" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33">
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C12,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K16" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="44" t="s">
-        <v>142</v>
+      <c r="M16" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:13">
-      <c r="B17" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="31">
+      <c r="B17" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F17" s="31" t="str">
+      <c r="E17" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F17" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31">
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C13,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K17" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="41" t="s">
-        <v>142</v>
+      <c r="M17" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="33">
+      <c r="E18" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F18" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33">
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C14,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K18" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="44" t="s">
-        <v>142</v>
+      <c r="L18" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="40" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="31">
+      <c r="B19" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F19" s="31" t="str">
+      <c r="E19" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31">
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C15,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K19" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M19" s="41" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F20" s="33" t="str">
+      <c r="E20" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33">
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M20" s="44" t="s">
-        <v>143</v>
+        <v>5</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="40" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="31">
+      <c r="C21" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F21" s="31">
+      <c r="E21" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="27">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31">
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C17,0)</f>
-        <v>10</v>
-      </c>
-      <c r="K21" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="41" t="s">
-        <v>142</v>
+      <c r="L21" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="33">
+      <c r="B22" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F22" s="33">
+      <c r="E22" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F22" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="29">
         <v>2</v>
       </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33">
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C18,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K22" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="29" t="s">
         <v>142</v>
       </c>
+      <c r="L22" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="31">
+      <c r="B23" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E23" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F23" s="31" t="str">
+      <c r="E23" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F23" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31">
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C19,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K23" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="41" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="33">
+      <c r="B24" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F24" s="33">
+      <c r="E24" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33">
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C20,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" s="29" t="s">
         <v>142</v>
       </c>
+      <c r="L24" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="31">
+      <c r="B25" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E25" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F25" s="31">
+      <c r="E25" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F25" s="27">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C21,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K25" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="27" t="s">
         <v>142</v>
       </c>
+      <c r="L25" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="37" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="33">
+      <c r="B26" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E26" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F26" s="33">
+      <c r="E26" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F26" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33">
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C22,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="29" t="s">
         <v>142</v>
       </c>
+      <c r="L26" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="40" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="31">
+      <c r="B27" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E27" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="31">
+      <c r="E27" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F27" s="27">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="27">
         <v>2</v>
       </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31">
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D40,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="M27" s="41" t="s">
-        <v>142</v>
+      <c r="L27" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="M27" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="33">
+      <c r="B28" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E28" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F28" s="33" t="str">
+      <c r="E28" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F28" s="29" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33">
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K1,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K28" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="L28" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="31">
+      <c r="B29" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E29" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F29" s="31" t="str">
+      <c r="E29" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F29" s="27" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31">
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K2,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K29" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="L29" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="M29" s="41" t="s">
-        <v>142</v>
+      <c r="M29" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="33">
+      <c r="B30" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E30" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F30" s="33">
+      <c r="E30" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F30" s="29">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33">
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29">
+        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M30" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="2:13">
+      <c r="B31" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="27">
+        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="27">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F31" s="27">
+        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>2</v>
+      </c>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
         <v>9</v>
       </c>
-      <c r="K30" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" s="33" t="s">
+      <c r="K31" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="M30" s="44" t="s">
+      <c r="L31" s="27" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="30" t="s">
+      <c r="M31" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="31">
-        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
+      <c r="C32" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="29">
+        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E31" s="31">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F31" s="31">
+      <c r="E32" s="29">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F32" s="29" t="str">
+        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29">
+        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M32" s="40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="32">
+        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E33" s="32">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="32">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>2</v>
       </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31">
-        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K31" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="L31" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="33">
-        <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32" s="33">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F32" s="33" t="str">
-        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33">
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
         <v>9</v>
       </c>
-      <c r="K32" s="33" t="s">
+      <c r="K33" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="L32" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="36">
-        <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E33" s="36">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F33" s="36">
-        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36">
-        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="M33" s="51" t="s">
-        <v>142</v>
+      <c r="M33" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -9199,21 +9181,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:N23"/>
+  <dimension ref="B2:M22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
     <col min="8" max="8" width="20.25" customWidth="1"/>
     <col min="9" max="9" width="19.875" customWidth="1"/>
-    <col min="10" max="10" width="23.125" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:14">
+    <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9223,26 +9203,23 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="J2" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="L2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N2" s="2">
+      <c r="M2" s="2">
         <f>12+Clebina!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:14">
+    <row r="3" ht="14.25" spans="2:13">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9261,21 +9238,18 @@
       <c r="I3" s="12">
         <v>1</v>
       </c>
-      <c r="J3" s="23">
-        <v>2</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="J3" s="4">
         <f>ROUNDDOWN(I3/2,0)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="N3" s="4">
+      <c r="L3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="M3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:14">
+    <row r="4" ht="15.75" spans="2:13">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9291,24 +9265,21 @@
       <c r="H4" s="16">
         <v>1000</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="22">
         <v>2</v>
       </c>
-      <c r="J4" s="25">
-        <v>3</v>
-      </c>
-      <c r="K4" s="6">
-        <f t="shared" ref="K4:K22" si="0">ROUNDDOWN(I4/2,0)</f>
+      <c r="J4" s="6">
+        <f t="shared" ref="J4:J22" si="0">ROUNDDOWN(I4/2,0)</f>
         <v>1</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="L4" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="M4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:11">
+    <row r="5" ht="15" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9321,15 +9292,12 @@
       <c r="I5" s="12">
         <v>3</v>
       </c>
-      <c r="J5" s="23">
-        <v>3</v>
-      </c>
-      <c r="K5" s="4">
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:11">
+    <row r="6" ht="15" spans="2:10">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9339,18 +9307,15 @@
       <c r="H6" s="16">
         <v>6000</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="22">
         <v>4</v>
       </c>
-      <c r="J6" s="25">
-        <v>4</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="J6" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:11">
+    <row r="7" ht="14.25" spans="2:10">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9363,15 +9328,12 @@
       <c r="I7" s="12">
         <v>5</v>
       </c>
-      <c r="J7" s="23">
-        <v>4</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="J7" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:11">
+    <row r="8" ht="15.75" spans="2:10">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9381,65 +9343,53 @@
       <c r="H8" s="16">
         <v>15000</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="22">
         <v>6</v>
       </c>
-      <c r="J8" s="25">
-        <v>5</v>
-      </c>
-      <c r="K8" s="6">
+      <c r="J8" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:11">
+    <row r="9" ht="15" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
       <c r="I9" s="12">
         <v>7</v>
       </c>
-      <c r="J9" s="23">
-        <v>7</v>
-      </c>
-      <c r="K9" s="4">
+      <c r="J9" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:11">
+    <row r="10" ht="15" spans="8:10">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="22">
         <v>8</v>
       </c>
-      <c r="J10" s="25">
-        <v>8</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="J10" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:11">
+    <row r="11" ht="15" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
       <c r="I11" s="12">
         <v>9</v>
       </c>
-      <c r="J11" s="23">
-        <v>8</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="J11" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:11">
+    <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9448,23 +9398,20 @@
       <c r="H12" s="16">
         <v>45000</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="22">
         <v>10</v>
       </c>
-      <c r="J12" s="25">
-        <v>9</v>
-      </c>
-      <c r="K12" s="6">
+      <c r="J12" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:11">
+    <row r="13" ht="14.25" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4">
-        <f>SUM(N3:N4)</f>
+        <f>SUM(M3:M4)</f>
         <v>5</v>
       </c>
       <c r="H13" s="17">
@@ -9473,55 +9420,46 @@
       <c r="I13" s="12">
         <v>11</v>
       </c>
-      <c r="J13" s="23">
-        <v>9</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="J13" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:11">
+    <row r="14" ht="15.75" spans="2:10">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
         <v>66000</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="22">
         <v>12</v>
       </c>
-      <c r="J14" s="25">
-        <v>10</v>
-      </c>
-      <c r="K14" s="6">
+      <c r="J14" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:11">
+    <row r="15" ht="15.75" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
       <c r="I15" s="12">
         <v>13</v>
       </c>
-      <c r="J15" s="23">
-        <v>10</v>
-      </c>
-      <c r="K15" s="4">
+      <c r="J15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:11">
+    <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>
@@ -9529,18 +9467,15 @@
       <c r="H16" s="16">
         <v>91000</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="22">
         <v>14</v>
       </c>
-      <c r="J16" s="25">
-        <v>11</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="J16" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:11">
+    <row r="17" ht="15" spans="2:10">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9558,15 +9493,12 @@
       <c r="I17" s="12">
         <v>15</v>
       </c>
-      <c r="J17" s="23">
-        <v>13</v>
-      </c>
-      <c r="K17" s="4">
+      <c r="J17" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:11">
+    <row r="18" ht="15" spans="2:10">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9581,18 +9513,15 @@
       <c r="H18" s="16">
         <v>120000</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="22">
         <v>16</v>
       </c>
-      <c r="J18" s="25">
-        <v>14</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="J18" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:11">
+    <row r="19" ht="15" spans="2:10">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9610,15 +9539,12 @@
       <c r="I19" s="12">
         <v>17</v>
       </c>
-      <c r="J19" s="23">
-        <v>14</v>
-      </c>
-      <c r="K19" s="4">
+      <c r="J19" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:11">
+    <row r="20" ht="15" spans="2:10">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9633,18 +9559,15 @@
       <c r="H20" s="16">
         <v>153000</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="22">
         <v>18</v>
       </c>
-      <c r="J20" s="25">
-        <v>15</v>
-      </c>
-      <c r="K20" s="6">
+      <c r="J20" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:11">
+    <row r="21" ht="15" spans="2:10">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9664,15 +9587,12 @@
       <c r="I21" s="12">
         <v>19</v>
       </c>
-      <c r="J21" s="23">
-        <v>15</v>
-      </c>
-      <c r="K21" s="4">
+      <c r="J21" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:11">
+    <row r="22" ht="15.75" spans="2:10">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9687,18 +9607,14 @@
       <c r="H22" s="20">
         <v>190000</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="23">
         <v>20</v>
       </c>
-      <c r="J22" s="27">
-        <v>16</v>
-      </c>
-      <c r="K22" s="8">
+      <c r="J22" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12315"/>
+    <workbookView windowWidth="19770" windowHeight="7455"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -1533,10 +1533,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1582,9 +1582,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1595,8 +1603,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1605,13 +1660,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1626,15 +1674,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1642,6 +1690,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1663,63 +1718,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1770,13 +1770,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1788,19 +1800,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1812,31 +1812,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1854,13 +1866,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1872,19 +1932,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1896,61 +1944,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2475,10 +2475,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -2503,7 +2501,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2525,24 +2538,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2565,156 +2565,156 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="42" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="41" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2999,54 +2999,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
-    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
-    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
-    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
-    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
-    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
-    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
-    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
-    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
-    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
-    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
-    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
-    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
-    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
-    <cellStyle name="Saída" xfId="25" builtinId="21"/>
-    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
-    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bom" xfId="29" builtinId="26"/>
-    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
-    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
-    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
-    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
-    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
-    <cellStyle name="Título" xfId="36" builtinId="15"/>
-    <cellStyle name="Observação" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
-    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
-    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
-    <cellStyle name="Comma" xfId="43" builtinId="3"/>
-    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
-    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
-    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
-    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
@@ -4316,7 +4316,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="6.125" customWidth="1"/>
@@ -4328,7 +4328,7 @@
     <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -4352,7 +4352,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:14">
+    <row r="3" spans="2:14">
       <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:14">
+    <row r="4" spans="2:14">
       <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
@@ -4415,10 +4415,12 @@
         <v>1</v>
       </c>
       <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
+      <c r="M4" s="29">
+        <v>3</v>
+      </c>
       <c r="N4" s="42"/>
     </row>
-    <row r="5" ht="14.25" spans="2:14">
+    <row r="5" spans="2:14">
       <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
@@ -4445,7 +4447,7 @@
       <c r="M5" s="27"/>
       <c r="N5" s="39"/>
     </row>
-    <row r="6" ht="15" spans="2:14">
+    <row r="6" spans="2:14">
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
@@ -4472,7 +4474,7 @@
       <c r="M6" s="29"/>
       <c r="N6" s="42"/>
     </row>
-    <row r="7" ht="14.25" spans="2:14">
+    <row r="7" spans="2:14">
       <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
@@ -4499,7 +4501,7 @@
       <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" ht="15.75" spans="2:14">
+    <row r="8" ht="18.75" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4525,7 +4527,7 @@
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" ht="15" spans="6:14">
+    <row r="9" ht="18.75" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
@@ -4540,7 +4542,7 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" ht="15.75" spans="6:14">
+    <row r="10" ht="18.75" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
@@ -4555,7 +4557,7 @@
       <c r="M10" s="29"/>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" ht="15.75" spans="11:14">
+    <row r="11" ht="19.5" spans="11:14">
       <c r="K11" s="38">
         <v>8</v>
       </c>
@@ -4563,7 +4565,7 @@
       <c r="M11" s="27"/>
       <c r="N11" s="39"/>
     </row>
-    <row r="12" ht="16.5" spans="2:14">
+    <row r="12" ht="19.5" spans="2:14">
       <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
@@ -4581,7 +4583,7 @@
       <c r="M12" s="29"/>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" ht="15.75" spans="2:14">
+    <row r="13" ht="19.5" spans="2:14">
       <c r="B13" s="89"/>
       <c r="K13" s="38">
         <v>10</v>
@@ -4590,7 +4592,7 @@
       <c r="M13" s="27"/>
       <c r="N13" s="39"/>
     </row>
-    <row r="14" ht="15.75" spans="2:14">
+    <row r="14" ht="18.75" spans="2:14">
       <c r="B14" s="35" t="s">
         <v>21</v>
       </c>
@@ -4609,7 +4611,7 @@
       <c r="M14" s="29"/>
       <c r="N14" s="42"/>
     </row>
-    <row r="15" ht="14.25" spans="2:14">
+    <row r="15" spans="2:14">
       <c r="B15" s="38" t="s">
         <v>23</v>
       </c>
@@ -4672,7 +4674,7 @@
       <c r="M16" s="29"/>
       <c r="N16" s="42"/>
     </row>
-    <row r="17" ht="15" spans="11:14">
+    <row r="17" ht="18.75" spans="11:14">
       <c r="K17" s="38">
         <v>14</v>
       </c>
@@ -4688,7 +4690,7 @@
       <c r="M18" s="29"/>
       <c r="N18" s="42"/>
     </row>
-    <row r="19" ht="14.25" spans="11:14">
+    <row r="19" spans="11:14">
       <c r="K19" s="38">
         <v>16</v>
       </c>
@@ -4696,7 +4698,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="39"/>
     </row>
-    <row r="20" ht="15" spans="11:14">
+    <row r="20" spans="11:14">
       <c r="K20" s="41">
         <v>17</v>
       </c>
@@ -4704,7 +4706,7 @@
       <c r="M20" s="29"/>
       <c r="N20" s="42"/>
     </row>
-    <row r="21" ht="14.25" spans="11:14">
+    <row r="21" spans="11:14">
       <c r="K21" s="38">
         <v>18</v>
       </c>
@@ -4720,26 +4722,26 @@
       <c r="M22" s="52"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15.75" spans="11:12">
+    <row r="23" ht="19.5"/>
+    <row r="24" ht="18.75" spans="11:12">
       <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="36"/>
     </row>
-    <row r="25" ht="14.25" spans="11:12">
+    <row r="25" spans="11:12">
       <c r="K25" s="38" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="39"/>
     </row>
-    <row r="26" ht="15.75" spans="11:12">
+    <row r="26" ht="18.75" spans="11:12">
       <c r="K26" s="45" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" ht="14.25"/>
+    <row r="27" ht="18.75"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4774,14 +4776,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="12" max="12" width="19.75" customWidth="1"/>
     <col min="13" max="13" width="12.25" customWidth="1"/>
     <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
+    <row r="1" ht="19.5" spans="1:15">
       <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
@@ -4801,8 +4803,8 @@
       <c r="N1" s="73"/>
       <c r="O1" s="74"/>
     </row>
-    <row r="2" ht="15"/>
-    <row r="3" ht="15.75" spans="2:13">
+    <row r="2" ht="19.5"/>
+    <row r="3" ht="18.75" spans="2:13">
       <c r="B3" s="35" t="s">
         <v>34</v>
       </c>
@@ -4882,7 +4884,7 @@
       </c>
       <c r="M6" s="86"/>
     </row>
-    <row r="7" ht="15" spans="2:13">
+    <row r="7" spans="2:13">
       <c r="B7" s="41" t="s">
         <v>49</v>
       </c>
@@ -4902,7 +4904,7 @@
       </c>
       <c r="M7" s="87"/>
     </row>
-    <row r="8" ht="14.25" spans="2:13">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>53</v>
       </c>
@@ -4922,7 +4924,7 @@
       </c>
       <c r="M8" s="86"/>
     </row>
-    <row r="9" ht="15" spans="2:13">
+    <row r="9" spans="2:13">
       <c r="B9" s="41" t="s">
         <v>57</v>
       </c>
@@ -4954,7 +4956,7 @@
       <c r="L10" s="79"/>
       <c r="M10" s="86"/>
     </row>
-    <row r="11" ht="15" spans="2:13">
+    <row r="11" spans="2:13">
       <c r="B11" s="41" t="s">
         <v>60</v>
       </c>
@@ -4970,7 +4972,7 @@
       <c r="L11" s="81"/>
       <c r="M11" s="87"/>
     </row>
-    <row r="12" ht="14.25" spans="2:13">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>62</v>
       </c>
@@ -4986,7 +4988,7 @@
       <c r="L12" s="79"/>
       <c r="M12" s="86"/>
     </row>
-    <row r="13" ht="15" spans="2:13">
+    <row r="13" spans="2:13">
       <c r="B13" s="41" t="s">
         <v>64</v>
       </c>
@@ -5003,7 +5005,7 @@
       <c r="L13" s="81"/>
       <c r="M13" s="87"/>
     </row>
-    <row r="14" ht="14.25" spans="2:13">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>67</v>
       </c>
@@ -5015,7 +5017,7 @@
       <c r="L14" s="79"/>
       <c r="M14" s="86"/>
     </row>
-    <row r="15" ht="15" spans="2:13">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>68</v>
       </c>
@@ -5027,7 +5029,7 @@
       <c r="L15" s="81"/>
       <c r="M15" s="87"/>
     </row>
-    <row r="16" ht="14.25" spans="2:13">
+    <row r="16" spans="2:13">
       <c r="B16" s="38" t="s">
         <v>69</v>
       </c>
@@ -5039,7 +5041,7 @@
       <c r="L16" s="79"/>
       <c r="M16" s="86"/>
     </row>
-    <row r="17" ht="15" spans="2:13">
+    <row r="17" spans="2:13">
       <c r="B17" s="41" t="s">
         <v>70</v>
       </c>
@@ -5051,7 +5053,7 @@
       <c r="L17" s="81"/>
       <c r="M17" s="87"/>
     </row>
-    <row r="18" ht="14.25" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="38" t="s">
         <v>71</v>
       </c>
@@ -5063,7 +5065,7 @@
       <c r="L18" s="79"/>
       <c r="M18" s="86"/>
     </row>
-    <row r="19" ht="15" spans="2:13">
+    <row r="19" spans="2:13">
       <c r="B19" s="41" t="s">
         <v>72</v>
       </c>
@@ -5075,7 +5077,7 @@
       <c r="L19" s="81"/>
       <c r="M19" s="87"/>
     </row>
-    <row r="20" ht="14.25" spans="2:13">
+    <row r="20" spans="2:13">
       <c r="B20" s="38" t="s">
         <v>73</v>
       </c>
@@ -5087,7 +5089,7 @@
       <c r="L20" s="79"/>
       <c r="M20" s="86"/>
     </row>
-    <row r="21" ht="15" spans="2:13">
+    <row r="21" spans="2:13">
       <c r="B21" s="41" t="s">
         <v>74</v>
       </c>
@@ -5099,7 +5101,7 @@
       <c r="L21" s="81"/>
       <c r="M21" s="87"/>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="43" t="s">
         <v>75</v>
       </c>
@@ -5111,7 +5113,7 @@
       <c r="L22" s="84"/>
       <c r="M22" s="88"/>
     </row>
-    <row r="23" ht="14.25"/>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5167,14 +5169,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
       <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
@@ -5192,7 +5194,7 @@
       </c>
       <c r="H2" s="64"/>
     </row>
-    <row r="3" ht="15" spans="2:8">
+    <row r="3" ht="18.75" spans="2:8">
       <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5203,21 +5205,21 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>79</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" spans="2:5">
       <c r="B4" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5228,14 +5230,14 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="2:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
       <c r="B5" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5246,14 +5248,14 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="2:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5264,14 +5266,14 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
       <c r="B7" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5282,14 +5284,14 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
       <c r="B8" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
@@ -5300,14 +5302,14 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
       <c r="B9" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
@@ -5318,14 +5320,14 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
       <c r="B10" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5336,14 +5338,14 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5354,14 +5356,14 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
       <c r="B12" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5372,14 +5374,14 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="2:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
       <c r="B13" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
@@ -5390,14 +5392,14 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
       <c r="B14" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
@@ -5408,14 +5410,14 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
       <c r="B15" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5426,14 +5428,14 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
       <c r="B16" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5444,14 +5446,14 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
       <c r="B17" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5462,14 +5464,14 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
       <c r="B18" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
@@ -5480,14 +5482,14 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
       <c r="B19" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5498,14 +5500,14 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
       <c r="B20" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
@@ -5516,14 +5518,14 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
       <c r="B21" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
@@ -5534,14 +5536,14 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
       <c r="B22" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
@@ -5552,14 +5554,14 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
       <c r="B23" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
@@ -5570,11 +5572,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5588,14 +5590,14 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
       <c r="B25" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
@@ -5606,11 +5608,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5624,14 +5626,14 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
       <c r="B27" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
@@ -5642,14 +5644,14 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
       <c r="B28" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5660,14 +5662,14 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
       <c r="B29" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
@@ -5678,14 +5680,14 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
       <c r="B30" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
@@ -5696,14 +5698,14 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" spans="2:5">
       <c r="B31" s="43" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
@@ -5714,14 +5716,14 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5740,7 +5742,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -5748,8 +5750,8 @@
     <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
       <c r="B2" s="24" t="s">
         <v>80</v>
       </c>
@@ -5767,7 +5769,7 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:8">
+    <row r="3" spans="2:8">
       <c r="B3" s="67" t="s">
         <v>84</v>
       </c>
@@ -5788,7 +5790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:8">
+    <row r="4" spans="2:8">
       <c r="B4" s="30" t="s">
         <v>86</v>
       </c>
@@ -5809,7 +5811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="2:8">
+    <row r="5" spans="2:8">
       <c r="B5" s="67" t="s">
         <v>87</v>
       </c>
@@ -5830,7 +5832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:8">
+    <row r="6" spans="2:8">
       <c r="B6" s="30" t="s">
         <v>89</v>
       </c>
@@ -5851,7 +5853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="2:8">
+    <row r="7" ht="18.75" spans="2:8">
       <c r="B7" s="67" t="s">
         <v>90</v>
       </c>
@@ -5872,7 +5874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:5">
+    <row r="8" ht="18.75" spans="2:5">
       <c r="B8" s="30" t="s">
         <v>91</v>
       </c>
@@ -5887,7 +5889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="2:6">
+    <row r="9" spans="2:6">
       <c r="B9" s="67" t="s">
         <v>92</v>
       </c>
@@ -5903,7 +5905,7 @@
       </c>
       <c r="F9" s="71"/>
     </row>
-    <row r="10" ht="15" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10" s="68"/>
       <c r="B10" s="30" t="s">
         <v>93</v>
@@ -5920,7 +5922,7 @@
       </c>
       <c r="F10" s="68"/>
     </row>
-    <row r="11" ht="14.25" spans="2:5">
+    <row r="11" spans="2:5">
       <c r="B11" s="67" t="s">
         <v>94</v>
       </c>
@@ -5935,7 +5937,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:5">
+    <row r="12" spans="2:5">
       <c r="B12" s="30" t="s">
         <v>95</v>
       </c>
@@ -5950,7 +5952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:5">
+    <row r="13" spans="2:5">
       <c r="B13" s="67" t="s">
         <v>96</v>
       </c>
@@ -5965,7 +5967,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="2:5">
+    <row r="14" spans="2:5">
       <c r="B14" s="30" t="s">
         <v>97</v>
       </c>
@@ -5980,7 +5982,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:5">
+    <row r="15" spans="2:5">
       <c r="B15" s="67" t="s">
         <v>98</v>
       </c>
@@ -5995,7 +5997,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:5">
+    <row r="16" spans="2:5">
       <c r="B16" s="30" t="s">
         <v>100</v>
       </c>
@@ -6010,7 +6012,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:5">
+    <row r="17" spans="2:5">
       <c r="B17" s="67"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -6019,7 +6021,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:5">
+    <row r="18" spans="2:5">
       <c r="B18" s="30"/>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -6028,7 +6030,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:5">
+    <row r="19" spans="2:5">
       <c r="B19" s="67"/>
       <c r="C19" s="26"/>
       <c r="D19" s="27"/>
@@ -6037,7 +6039,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:5">
+    <row r="20" spans="2:5">
       <c r="B20" s="30"/>
       <c r="C20" s="28"/>
       <c r="D20" s="29"/>
@@ -6046,7 +6048,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:5">
+    <row r="21" spans="2:5">
       <c r="B21" s="67"/>
       <c r="C21" s="26"/>
       <c r="D21" s="27"/>
@@ -6055,7 +6057,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:5">
+    <row r="22" spans="2:5">
       <c r="B22" s="30"/>
       <c r="C22" s="28"/>
       <c r="D22" s="29"/>
@@ -6064,7 +6066,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:5">
+    <row r="23" spans="2:5">
       <c r="B23" s="67"/>
       <c r="C23" s="26"/>
       <c r="D23" s="27"/>
@@ -6073,7 +6075,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:5">
+    <row r="24" spans="2:5">
       <c r="B24" s="30"/>
       <c r="C24" s="28"/>
       <c r="D24" s="29"/>
@@ -6082,7 +6084,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:5">
+    <row r="25" spans="2:5">
       <c r="B25" s="67"/>
       <c r="C25" s="26"/>
       <c r="D25" s="27"/>
@@ -6091,7 +6093,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:5">
+    <row r="26" spans="2:5">
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29"/>
@@ -6100,7 +6102,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:5">
+    <row r="27" spans="2:5">
       <c r="B27" s="67"/>
       <c r="C27" s="26"/>
       <c r="D27" s="27"/>
@@ -6109,7 +6111,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:5">
+    <row r="28" spans="2:5">
       <c r="B28" s="30"/>
       <c r="C28" s="28"/>
       <c r="D28" s="29"/>
@@ -6118,7 +6120,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:5">
+    <row r="29" spans="2:5">
       <c r="B29" s="67"/>
       <c r="C29" s="26"/>
       <c r="D29" s="27"/>
@@ -6127,7 +6129,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:5">
+    <row r="30" spans="2:5">
       <c r="B30" s="30"/>
       <c r="C30" s="28"/>
       <c r="D30" s="29"/>
@@ -6136,7 +6138,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:5">
+    <row r="31" spans="2:5">
       <c r="B31" s="67"/>
       <c r="C31" s="26"/>
       <c r="D31" s="27"/>
@@ -6145,7 +6147,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:5">
+    <row r="32" spans="2:5">
       <c r="B32" s="30"/>
       <c r="C32" s="28"/>
       <c r="D32" s="29"/>
@@ -6154,7 +6156,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:5">
+    <row r="33" spans="2:5">
       <c r="B33" s="67"/>
       <c r="C33" s="26"/>
       <c r="D33" s="27"/>
@@ -6163,7 +6165,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" spans="2:5">
+    <row r="34" spans="2:5">
       <c r="B34" s="30"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
@@ -6172,7 +6174,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="2:5">
+    <row r="35" spans="2:5">
       <c r="B35" s="69"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
@@ -6198,15 +6200,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:6">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:6">
       <c r="B2" s="35" t="s">
         <v>101</v>
       </c>
@@ -6215,7 +6217,7 @@
       <c r="E2" s="62"/>
       <c r="F2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:6">
+    <row r="3" spans="2:6">
       <c r="B3" s="38" t="s">
         <v>23</v>
       </c>
@@ -6232,7 +6234,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:6">
+    <row r="4" spans="2:6">
       <c r="B4" s="41" t="s">
         <v>29</v>
       </c>
@@ -6249,15 +6251,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:6">
+    <row r="5" ht="18.75" spans="2:6">
       <c r="B5" s="43"/>
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
       <c r="E5" s="63"/>
       <c r="F5" s="44"/>
     </row>
-    <row r="6" ht="15"/>
-    <row r="7" ht="15.75" spans="2:8">
+    <row r="6" ht="19.5"/>
+    <row r="7" ht="18.75" spans="2:8">
       <c r="B7" s="50" t="s">
         <v>104</v>
       </c>
@@ -6268,7 +6270,7 @@
       <c r="G7" s="51"/>
       <c r="H7" s="64"/>
     </row>
-    <row r="8" ht="14.25" spans="2:8">
+    <row r="8" spans="2:8">
       <c r="B8" s="38" t="s">
         <v>23</v>
       </c>
@@ -6291,7 +6293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:8">
+    <row r="9" spans="2:8">
       <c r="B9" s="41" t="s">
         <v>106</v>
       </c>
@@ -6308,7 +6310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="2:8">
+    <row r="10" spans="2:8">
       <c r="B10" s="38" t="s">
         <v>110</v>
       </c>
@@ -6350,7 +6352,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="2:8">
+    <row r="12" spans="2:8">
       <c r="B12" s="38"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -6359,7 +6361,7 @@
       <c r="G12" s="37"/>
       <c r="H12" s="39"/>
     </row>
-    <row r="13" ht="15.75" spans="2:8">
+    <row r="13" ht="18.75" spans="2:8">
       <c r="B13" s="45"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
@@ -6368,8 +6370,8 @@
       <c r="G13" s="65"/>
       <c r="H13" s="46"/>
     </row>
-    <row r="14" ht="15"/>
-    <row r="15" ht="15.75" spans="2:9">
+    <row r="14" ht="19.5"/>
+    <row r="15" ht="18.75" spans="2:9">
       <c r="B15" s="35" t="s">
         <v>116</v>
       </c>
@@ -6381,7 +6383,7 @@
       <c r="H15" s="48"/>
       <c r="I15" s="36"/>
     </row>
-    <row r="16" ht="14.25" spans="2:9">
+    <row r="16" spans="2:9">
       <c r="B16" s="53" t="s">
         <v>23</v>
       </c>
@@ -6405,7 +6407,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:9">
+    <row r="17" spans="2:9">
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
@@ -6431,7 +6433,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="2:9">
+    <row r="18" spans="2:9">
       <c r="B18" s="53"/>
       <c r="C18" s="54"/>
       <c r="D18" s="54"/>
@@ -6441,7 +6443,7 @@
       <c r="H18" s="54"/>
       <c r="I18" s="66"/>
     </row>
-    <row r="19" ht="15" spans="2:9">
+    <row r="19" spans="2:9">
       <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
@@ -6465,7 +6467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="2:9">
+    <row r="20" spans="2:9">
       <c r="B20" s="53" t="s">
         <v>124</v>
       </c>
@@ -6487,7 +6489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:9">
+    <row r="21" spans="2:9">
       <c r="B21" s="5" t="s">
         <v>125</v>
       </c>
@@ -6505,7 +6507,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="42"/>
     </row>
-    <row r="22" ht="14.25" spans="2:9">
+    <row r="22" spans="2:9">
       <c r="B22" s="53"/>
       <c r="C22" s="54"/>
       <c r="D22" s="54"/>
@@ -6515,7 +6517,7 @@
       <c r="H22" s="54"/>
       <c r="I22" s="66"/>
     </row>
-    <row r="23" ht="15" spans="2:9">
+    <row r="23" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -6525,7 +6527,7 @@
       <c r="H23" s="29"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" ht="14.25" spans="2:9">
+    <row r="24" spans="2:9">
       <c r="B24" s="53"/>
       <c r="C24" s="54"/>
       <c r="D24" s="54"/>
@@ -6535,7 +6537,7 @@
       <c r="H24" s="54"/>
       <c r="I24" s="66"/>
     </row>
-    <row r="25" ht="15" spans="2:9">
+    <row r="25" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -6545,7 +6547,7 @@
       <c r="H25" s="29"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" ht="14.25" spans="2:9">
+    <row r="26" spans="2:9">
       <c r="B26" s="53"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -6555,7 +6557,7 @@
       <c r="H26" s="54"/>
       <c r="I26" s="66"/>
     </row>
-    <row r="27" ht="15" spans="2:9">
+    <row r="27" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -6565,7 +6567,7 @@
       <c r="H27" s="29"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" ht="14.25" spans="2:9">
+    <row r="28" spans="2:9">
       <c r="B28" s="53"/>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -6575,7 +6577,7 @@
       <c r="H28" s="54"/>
       <c r="I28" s="66"/>
     </row>
-    <row r="29" ht="15.75" spans="2:9">
+    <row r="29" ht="18.75" spans="2:9">
       <c r="B29" s="7"/>
       <c r="C29" s="55"/>
       <c r="D29" s="55"/>
@@ -6585,9 +6587,9 @@
       <c r="H29" s="52"/>
       <c r="I29" s="46"/>
     </row>
-    <row r="30" ht="14.25"/>
-    <row r="31" ht="14.25"/>
-    <row r="32" ht="15.75" spans="2:4">
+    <row r="30" ht="18.75"/>
+    <row r="31" ht="18.75"/>
+    <row r="32" ht="18.75" spans="2:4">
       <c r="B32" s="1" t="s">
         <v>126</v>
       </c>
@@ -6620,7 +6622,7 @@
       </c>
       <c r="D34" s="61"/>
     </row>
-    <row r="35" ht="14.25"/>
+    <row r="35" ht="18.75"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6652,7 +6654,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -6669,7 +6671,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
         <v>129</v>
@@ -6712,7 +6714,7 @@
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:16">
+    <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
         <v>138</v>
       </c>
@@ -6754,7 +6756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
         <v>143</v>
       </c>
@@ -6796,7 +6798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
         <v>145</v>
       </c>
@@ -6838,7 +6840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
         <v>147</v>
       </c>
@@ -6957,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
         <v>152</v>
       </c>
@@ -7000,7 +7002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
         <v>154</v>
       </c>
@@ -7043,7 +7045,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
         <v>155</v>
       </c>
@@ -7086,7 +7088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
+    <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
         <v>156</v>
       </c>
@@ -7129,7 +7131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
         <v>158</v>
       </c>
@@ -7172,7 +7174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
         <v>159</v>
       </c>
@@ -7208,7 +7210,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:13">
+    <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
         <v>160</v>
       </c>
@@ -7244,7 +7246,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:13">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>161</v>
       </c>
@@ -7280,7 +7282,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:17">
+    <row r="17" spans="2:17">
       <c r="B17" s="26" t="s">
         <v>162</v>
       </c>
@@ -7320,7 +7322,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
         <v>163</v>
       </c>
@@ -7356,7 +7358,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:13">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>164</v>
       </c>
@@ -7392,7 +7394,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:13">
+    <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
         <v>165</v>
       </c>
@@ -7428,7 +7430,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:13">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
@@ -7464,7 +7466,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
         <v>166</v>
       </c>
@@ -7502,7 +7504,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:13">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>167</v>
       </c>
@@ -7538,7 +7540,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:13">
+    <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
         <v>168</v>
       </c>
@@ -7574,7 +7576,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:13">
+    <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
         <v>169</v>
       </c>
@@ -7610,7 +7612,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:13">
+    <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
         <v>170</v>
       </c>
@@ -7646,7 +7648,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:13">
+    <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
         <v>171</v>
       </c>
@@ -7684,7 +7686,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:13">
+    <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
         <v>172</v>
       </c>
@@ -7720,7 +7722,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:13">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>173</v>
       </c>
@@ -7756,7 +7758,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:13">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>174</v>
       </c>
@@ -7792,7 +7794,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:13">
+    <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
         <v>175</v>
       </c>
@@ -7828,7 +7830,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:13">
+    <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
         <v>176</v>
       </c>
@@ -7864,7 +7866,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:13">
+    <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
         <v>177</v>
       </c>
@@ -7918,7 +7920,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -7935,7 +7937,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
         <v>129</v>
@@ -7978,7 +7980,7 @@
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:16">
+    <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
         <v>138</v>
       </c>
@@ -8020,7 +8022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
         <v>143</v>
       </c>
@@ -8062,7 +8064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
         <v>145</v>
       </c>
@@ -8104,7 +8106,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
         <v>147</v>
       </c>
@@ -8223,7 +8225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
         <v>152</v>
       </c>
@@ -8266,7 +8268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
         <v>154</v>
       </c>
@@ -8309,7 +8311,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
         <v>155</v>
       </c>
@@ -8352,7 +8354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
+    <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
         <v>156</v>
       </c>
@@ -8395,7 +8397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
         <v>158</v>
       </c>
@@ -8438,7 +8440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
         <v>159</v>
       </c>
@@ -8476,7 +8478,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:13">
+    <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
         <v>160</v>
       </c>
@@ -8512,7 +8514,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:13">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>161</v>
       </c>
@@ -8548,7 +8550,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:13">
+    <row r="17" spans="2:13">
       <c r="B17" s="26" t="s">
         <v>162</v>
       </c>
@@ -8584,7 +8586,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
+    <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
         <v>163</v>
       </c>
@@ -8620,7 +8622,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:13">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>164</v>
       </c>
@@ -8656,7 +8658,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:13">
+    <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
         <v>165</v>
       </c>
@@ -8692,7 +8694,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:13">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
@@ -8728,7 +8730,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
         <v>166</v>
       </c>
@@ -8766,7 +8768,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:13">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>167</v>
       </c>
@@ -8802,7 +8804,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:13">
+    <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
         <v>168</v>
       </c>
@@ -8838,7 +8840,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:13">
+    <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
         <v>169</v>
       </c>
@@ -8874,7 +8876,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:13">
+    <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
         <v>170</v>
       </c>
@@ -8910,7 +8912,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:13">
+    <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
         <v>171</v>
       </c>
@@ -8948,7 +8950,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:13">
+    <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
         <v>172</v>
       </c>
@@ -8984,7 +8986,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:13">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>173</v>
       </c>
@@ -9020,7 +9022,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:13">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>174</v>
       </c>
@@ -9056,7 +9058,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:13">
+    <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
         <v>175</v>
       </c>
@@ -9092,7 +9094,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:13">
+    <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
         <v>176</v>
       </c>
@@ -9128,7 +9130,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:13">
+    <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
         <v>177</v>
       </c>
@@ -9181,8 +9183,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="B1:M23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
@@ -9191,7 +9193,8 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="15.75" spans="2:13">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:13">
       <c r="B2" s="1" t="s">
         <v>178</v>
       </c>
@@ -9219,7 +9222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:13">
+    <row r="3" spans="2:13">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9249,7 +9252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:13">
+    <row r="4" ht="18.75" spans="2:13">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9279,7 +9282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:10">
+    <row r="5" ht="18.75" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9297,7 +9300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:10">
+    <row r="6" spans="2:10">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9315,7 +9318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:10">
+    <row r="7" spans="2:10">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9333,7 +9336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:10">
+    <row r="8" ht="18.75" spans="2:10">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9351,7 +9354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:10">
+    <row r="9" ht="18.75" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9363,7 +9366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:10">
+    <row r="10" spans="8:10">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
@@ -9375,7 +9378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:10">
+    <row r="11" ht="18.75" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9387,7 +9390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:10">
+    <row r="12" ht="18.75" spans="2:10">
       <c r="B12" s="1" t="s">
         <v>185</v>
       </c>
@@ -9406,7 +9409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:10">
+    <row r="13" spans="2:10">
       <c r="B13" s="3" t="s">
         <v>186</v>
       </c>
@@ -9425,7 +9428,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:10">
+    <row r="14" ht="18.75" spans="2:10">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
@@ -9439,7 +9442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:10">
+    <row r="15" ht="19.5" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9451,7 +9454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:10">
+    <row r="16" ht="18.75" spans="2:10">
       <c r="B16" s="9" t="s">
         <v>130</v>
       </c>
@@ -9475,7 +9478,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:10">
+    <row r="17" spans="2:10">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9498,7 +9501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:10">
+    <row r="18" spans="2:10">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9521,7 +9524,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:10">
+    <row r="19" spans="2:10">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9544,7 +9547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:10">
+    <row r="20" spans="2:10">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9567,7 +9570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:10">
+    <row r="21" spans="2:10">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9592,7 +9595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:10">
+    <row r="22" ht="18.75" spans="2:10">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9615,6 +9618,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19770" windowHeight="7455"/>
+    <workbookView windowWidth="19770" windowHeight="7005"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="190">
   <si>
     <t>Atributos</t>
   </si>
@@ -1337,6 +1337,9 @@
   </si>
   <si>
     <t>Imagem espelhada</t>
+  </si>
+  <si>
+    <t>cristal do balacobaco</t>
   </si>
   <si>
     <t>Capacidade</t>
@@ -1533,10 +1536,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1581,6 +1584,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
@@ -1588,24 +1614,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1620,6 +1630,37 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
@@ -1628,7 +1669,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1644,30 +1685,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1682,14 +1700,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1697,29 +1723,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1770,7 +1773,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1782,7 +1809,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1794,67 +1851,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1872,13 +1875,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1890,31 +1893,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1926,31 +1929,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2473,11 +2476,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2501,37 +2519,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2570,151 +2558,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="45" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="42" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="39" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4405,7 +4408,7 @@
       </c>
       <c r="G4" s="29">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H4" s="42">
         <f>'uns dados aí'!C13*G2</f>
@@ -4444,7 +4447,9 @@
         <v>2</v>
       </c>
       <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
+      <c r="M5" s="27">
+        <v>3</v>
+      </c>
       <c r="N5" s="39"/>
     </row>
     <row r="6" spans="2:14">
@@ -4501,7 +4506,7 @@
       <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" ht="18.75" spans="2:14">
+    <row r="8" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4527,12 +4532,12 @@
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" ht="18.75" spans="6:14">
+    <row r="9" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="27">
-        <v>682</v>
+        <v>711</v>
       </c>
       <c r="H9" s="39"/>
       <c r="K9" s="38">
@@ -4542,7 +4547,7 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" ht="18.75" spans="6:14">
+    <row r="10" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
@@ -4640,7 +4645,7 @@
       <c r="M15" s="27"/>
       <c r="N15" s="39"/>
     </row>
-    <row r="16" ht="30.75" spans="2:14">
+    <row r="16" ht="33.75" spans="2:14">
       <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
@@ -5205,18 +5210,18 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>79</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="18.75" spans="2:5">
@@ -5248,11 +5253,11 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -5266,11 +5271,11 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -5284,11 +5289,11 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -5302,11 +5307,11 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -5320,11 +5325,11 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -5338,11 +5343,11 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -5356,11 +5361,11 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -5374,11 +5379,11 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -5392,11 +5397,11 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -5410,11 +5415,11 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -5428,11 +5433,11 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:5">
@@ -5446,11 +5451,11 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -5464,11 +5469,11 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -5482,11 +5487,11 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -5500,11 +5505,11 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -5518,11 +5523,11 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -5536,11 +5541,11 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -5554,11 +5559,11 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -5572,14 +5577,14 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="33" spans="2:5">
       <c r="B24" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Alquimista)</v>
@@ -5590,11 +5595,11 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -5615,7 +5620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" ht="30" spans="2:5">
+    <row r="26" ht="49.5" spans="2:5">
       <c r="B26" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Engenhoqueiro)</v>
@@ -5626,11 +5631,11 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -5644,11 +5649,11 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -5662,11 +5667,11 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -5680,11 +5685,11 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -5698,11 +5703,11 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" ht="18.75" spans="2:5">
@@ -5716,11 +5721,11 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="18.75"/>
@@ -6331,7 +6336,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="2:8">
+    <row r="11" ht="33" spans="2:8">
       <c r="B11" s="41" t="s">
         <v>30</v>
       </c>
@@ -6502,18 +6507,28 @@
         <v>2</v>
       </c>
       <c r="G21" s="29">
+        <f>PRODUCT(E21:F21)</f>
         <v>2</v>
       </c>
       <c r="H21" s="29"/>
       <c r="I21" s="42"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="53"/>
+      <c r="B22" s="53" t="s">
+        <v>126</v>
+      </c>
       <c r="C22" s="54"/>
       <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
+      <c r="E22" s="54">
+        <v>2</v>
+      </c>
+      <c r="F22" s="54">
+        <v>1</v>
+      </c>
+      <c r="G22" s="54">
+        <f>PRODUCT(E22:F22)</f>
+        <v>2</v>
+      </c>
       <c r="H22" s="54"/>
       <c r="I22" s="66"/>
     </row>
@@ -6591,11 +6606,11 @@
     <row r="31" ht="18.75"/>
     <row r="32" ht="18.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C32" s="56">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2">
         <f>Clebina!C3*3</f>
@@ -6604,7 +6619,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
       <c r="B33" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C33" s="58">
         <f>Clebina!C3*10</f>
@@ -6614,7 +6629,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C34" s="60" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
@@ -6674,19 +6689,19 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6695,31 +6710,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6741,13 +6756,13 @@
         <v>-5</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6758,10 +6773,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6783,13 +6798,13 @@
         <v>4</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -6800,10 +6815,10 @@
     </row>
     <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6825,13 +6840,13 @@
         <v>6</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -6842,10 +6857,10 @@
     </row>
     <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6867,21 +6882,21 @@
         <v>4</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6903,25 +6918,25 @@
         <v>5</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6943,13 +6958,13 @@
         <v>11</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -6961,10 +6976,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6986,13 +7001,13 @@
         <v>9</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -7004,10 +7019,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7029,13 +7044,13 @@
         <v>4</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -7047,10 +7062,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7072,13 +7087,13 @@
         <v>4</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7090,10 +7105,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7115,13 +7130,13 @@
         <v>6</v>
       </c>
       <c r="K12" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L12" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M12" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7133,10 +7148,10 @@
     </row>
     <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7158,13 +7173,13 @@
         <v>-5</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7176,10 +7191,10 @@
     </row>
     <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7201,21 +7216,21 @@
         <v>11</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7237,21 +7252,21 @@
         <v>5</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7273,21 +7288,21 @@
         <v>4</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7309,13 +7324,13 @@
         <v>7</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
@@ -7324,10 +7339,10 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7349,21 +7364,21 @@
         <v>11</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7385,21 +7400,21 @@
         <v>4</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7421,13 +7436,13 @@
         <v>-5</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -7435,7 +7450,7 @@
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7457,21 +7472,21 @@
         <v>8</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7495,21 +7510,21 @@
         <v>13</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7531,21 +7546,21 @@
         <v>9</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7567,21 +7582,21 @@
         <v>11</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7603,21 +7618,21 @@
         <v>11</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7639,21 +7654,21 @@
         <v>11</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7677,21 +7692,21 @@
         <v>11</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7713,21 +7728,21 @@
         <v>5</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7749,21 +7764,21 @@
         <v>5</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7785,21 +7800,21 @@
         <v>7</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7821,21 +7836,21 @@
         <v>7</v>
       </c>
       <c r="K31" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L31" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7857,21 +7872,21 @@
         <v>7</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7893,13 +7908,13 @@
         <v>9</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>141</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -7940,19 +7955,19 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -7961,31 +7976,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>78</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8007,13 +8022,13 @@
         <v>-5</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -8024,10 +8039,10 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8049,13 +8064,13 @@
         <v>4</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>57</v>
@@ -8066,10 +8081,10 @@
     </row>
     <row r="5" ht="18.75" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8091,13 +8106,13 @@
         <v>6</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>70</v>
@@ -8108,10 +8123,10 @@
     </row>
     <row r="6" ht="19.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8133,21 +8148,21 @@
         <v>4</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8169,25 +8184,25 @@
         <v>5</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8209,13 +8224,13 @@
         <v>11</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>141</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8227,10 +8242,10 @@
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8252,13 +8267,13 @@
         <v>9</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8270,10 +8285,10 @@
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8295,13 +8310,13 @@
         <v>4</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8313,10 +8328,10 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8338,13 +8353,13 @@
         <v>4</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8356,10 +8371,10 @@
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8381,13 +8396,13 @@
         <v>4</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8399,10 +8414,10 @@
     </row>
     <row r="13" ht="18.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8424,13 +8439,13 @@
         <v>5</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8442,10 +8457,10 @@
     </row>
     <row r="14" ht="18.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8469,21 +8484,21 @@
         <v>12</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8505,21 +8520,21 @@
         <v>5</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8541,21 +8556,21 @@
         <v>4</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8577,21 +8592,21 @@
         <v>7</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8613,21 +8628,21 @@
         <v>11</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8649,21 +8664,21 @@
         <v>4</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8685,13 +8700,13 @@
         <v>5</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="2:13">
@@ -8699,7 +8714,7 @@
         <v>79</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8721,21 +8736,21 @@
         <v>8</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8759,21 +8774,21 @@
         <v>13</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8795,21 +8810,21 @@
         <v>9</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8831,21 +8846,21 @@
         <v>11</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8867,21 +8882,21 @@
         <v>11</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8903,21 +8918,21 @@
         <v>11</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8941,21 +8956,21 @@
         <v>11</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>141</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -8977,21 +8992,21 @@
         <v>5</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9013,21 +9028,21 @@
         <v>5</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9049,21 +9064,21 @@
         <v>7</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>141</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9085,21 +9100,21 @@
         <v>9</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>142</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9121,21 +9136,21 @@
         <v>7</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -9157,13 +9172,13 @@
         <v>9</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>141</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -9196,7 +9211,7 @@
     <row r="1" ht="18.75"/>
     <row r="2" ht="18.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9206,16 +9221,16 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M2" s="2">
         <f>12+Clebina!D5</f>
@@ -9246,7 +9261,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
@@ -9276,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
@@ -9392,7 +9407,7 @@
     </row>
     <row r="12" ht="18.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9411,7 +9426,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9456,13 +9471,13 @@
     </row>
     <row r="16" ht="18.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19770" windowHeight="7005"/>
+    <workbookView windowWidth="13905" windowHeight="11685"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -1537,9 +1537,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1584,24 +1584,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1615,7 +1599,76 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1624,21 +1677,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1660,16 +1698,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
@@ -1677,52 +1722,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1773,6 +1773,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1785,31 +1911,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1821,139 +1947,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2476,17 +2476,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2495,7 +2489,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2511,26 +2505,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2552,9 +2526,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2573,151 +2564,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="44" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="45" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3002,54 +3002,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
+    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
+    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
+    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
+    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
+    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
+    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
+    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
+    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
+    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
+    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
+    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
+    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
+    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
+    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
+    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
+    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
+    <cellStyle name="Saída" xfId="25" builtinId="21"/>
+    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
+    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bom" xfId="29" builtinId="26"/>
+    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
+    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
+    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
+    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
+    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
+    <cellStyle name="Título" xfId="36" builtinId="15"/>
+    <cellStyle name="Observação" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
+    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
+    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
+    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
+    <cellStyle name="Comma" xfId="43" builtinId="3"/>
+    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
+    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
+    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
+    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
+    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
@@ -4319,7 +4319,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="6.125" customWidth="1"/>
@@ -4331,7 +4331,7 @@
     <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
       <c r="B2" s="35" t="s">
         <v>0</v>
@@ -4355,7 +4355,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="36"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" ht="14.25" spans="2:14">
       <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" ht="15" spans="2:14">
       <c r="B4" s="41" t="s">
         <v>9</v>
       </c>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="N4" s="42"/>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" ht="14.25" spans="2:14">
       <c r="B5" s="38" t="s">
         <v>10</v>
       </c>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="N5" s="39"/>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" ht="15" spans="2:14">
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
@@ -4479,7 +4479,7 @@
       <c r="M6" s="29"/>
       <c r="N6" s="42"/>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" ht="14.25" spans="2:14">
       <c r="B7" s="38" t="s">
         <v>14</v>
       </c>
@@ -4506,7 +4506,7 @@
       <c r="M7" s="27"/>
       <c r="N7" s="39"/>
     </row>
-    <row r="8" spans="2:14">
+    <row r="8" ht="15.75" spans="2:14">
       <c r="B8" s="45" t="s">
         <v>16</v>
       </c>
@@ -4532,7 +4532,7 @@
       <c r="M8" s="29"/>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" spans="6:14">
+    <row r="9" ht="15" spans="6:14">
       <c r="F9" s="38" t="s">
         <v>18</v>
       </c>
@@ -4547,12 +4547,12 @@
       <c r="M9" s="27"/>
       <c r="N9" s="39"/>
     </row>
-    <row r="10" spans="6:14">
+    <row r="10" ht="15.75" spans="6:14">
       <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="52">
-        <v>15850</v>
+        <v>18850</v>
       </c>
       <c r="H10" s="46"/>
       <c r="K10" s="41">
@@ -4562,7 +4562,7 @@
       <c r="M10" s="29"/>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" ht="19.5" spans="11:14">
+    <row r="11" ht="15.75" spans="11:14">
       <c r="K11" s="38">
         <v>8</v>
       </c>
@@ -4570,7 +4570,7 @@
       <c r="M11" s="27"/>
       <c r="N11" s="39"/>
     </row>
-    <row r="12" ht="19.5" spans="2:14">
+    <row r="12" ht="16.5" spans="2:14">
       <c r="B12" s="72" t="s">
         <v>20</v>
       </c>
@@ -4588,7 +4588,7 @@
       <c r="M12" s="29"/>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" ht="19.5" spans="2:14">
+    <row r="13" ht="15.75" spans="2:14">
       <c r="B13" s="89"/>
       <c r="K13" s="38">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       <c r="M13" s="27"/>
       <c r="N13" s="39"/>
     </row>
-    <row r="14" ht="18.75" spans="2:14">
+    <row r="14" ht="15.75" spans="2:14">
       <c r="B14" s="35" t="s">
         <v>21</v>
       </c>
@@ -4616,7 +4616,7 @@
       <c r="M14" s="29"/>
       <c r="N14" s="42"/>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" ht="14.25" spans="2:14">
       <c r="B15" s="38" t="s">
         <v>23</v>
       </c>
@@ -4645,7 +4645,7 @@
       <c r="M15" s="27"/>
       <c r="N15" s="39"/>
     </row>
-    <row r="16" ht="33.75" spans="2:14">
+    <row r="16" ht="30.75" spans="2:14">
       <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
@@ -4679,7 +4679,7 @@
       <c r="M16" s="29"/>
       <c r="N16" s="42"/>
     </row>
-    <row r="17" ht="18.75" spans="11:14">
+    <row r="17" ht="15" spans="11:14">
       <c r="K17" s="38">
         <v>14</v>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="M18" s="29"/>
       <c r="N18" s="42"/>
     </row>
-    <row r="19" spans="11:14">
+    <row r="19" ht="14.25" spans="11:14">
       <c r="K19" s="38">
         <v>16</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="39"/>
     </row>
-    <row r="20" spans="11:14">
+    <row r="20" ht="15" spans="11:14">
       <c r="K20" s="41">
         <v>17</v>
       </c>
@@ -4711,7 +4711,7 @@
       <c r="M20" s="29"/>
       <c r="N20" s="42"/>
     </row>
-    <row r="21" spans="11:14">
+    <row r="21" ht="14.25" spans="11:14">
       <c r="K21" s="38">
         <v>18</v>
       </c>
@@ -4727,26 +4727,26 @@
       <c r="M22" s="52"/>
       <c r="N22" s="46"/>
     </row>
-    <row r="23" ht="19.5"/>
-    <row r="24" ht="18.75" spans="11:12">
+    <row r="23" ht="15"/>
+    <row r="24" ht="15.75" spans="11:12">
       <c r="K24" s="35" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="36"/>
     </row>
-    <row r="25" spans="11:12">
+    <row r="25" ht="14.25" spans="11:12">
       <c r="K25" s="38" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="39"/>
     </row>
-    <row r="26" ht="18.75" spans="11:12">
+    <row r="26" ht="15.75" spans="11:12">
       <c r="K26" s="45" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="46"/>
     </row>
-    <row r="27" ht="18.75"/>
+    <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4781,14 +4781,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="12" max="12" width="19.75" customWidth="1"/>
     <col min="13" max="13" width="12.25" customWidth="1"/>
     <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:15">
+    <row r="1" ht="16.5" spans="1:15">
       <c r="A1" s="72" t="s">
         <v>32</v>
       </c>
@@ -4808,8 +4808,8 @@
       <c r="N1" s="73"/>
       <c r="O1" s="74"/>
     </row>
-    <row r="2" ht="19.5"/>
-    <row r="3" ht="18.75" spans="2:13">
+    <row r="2" ht="15"/>
+    <row r="3" ht="15.75" spans="2:13">
       <c r="B3" s="35" t="s">
         <v>34</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="M6" s="86"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" ht="15" spans="2:13">
       <c r="B7" s="41" t="s">
         <v>49</v>
       </c>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="M7" s="87"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" ht="14.25" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>53</v>
       </c>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M8" s="86"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" ht="15" spans="2:13">
       <c r="B9" s="41" t="s">
         <v>57</v>
       </c>
@@ -4961,7 +4961,7 @@
       <c r="L10" s="79"/>
       <c r="M10" s="86"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" ht="15" spans="2:13">
       <c r="B11" s="41" t="s">
         <v>60</v>
       </c>
@@ -4977,7 +4977,7 @@
       <c r="L11" s="81"/>
       <c r="M11" s="87"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" ht="14.25" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>62</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="L12" s="79"/>
       <c r="M12" s="86"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" ht="15" spans="2:13">
       <c r="B13" s="41" t="s">
         <v>64</v>
       </c>
@@ -5010,7 +5010,7 @@
       <c r="L13" s="81"/>
       <c r="M13" s="87"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" ht="14.25" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>67</v>
       </c>
@@ -5022,7 +5022,7 @@
       <c r="L14" s="79"/>
       <c r="M14" s="86"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" ht="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>68</v>
       </c>
@@ -5034,7 +5034,7 @@
       <c r="L15" s="81"/>
       <c r="M15" s="87"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" ht="14.25" spans="2:13">
       <c r="B16" s="38" t="s">
         <v>69</v>
       </c>
@@ -5046,7 +5046,7 @@
       <c r="L16" s="79"/>
       <c r="M16" s="86"/>
     </row>
-    <row r="17" spans="2:13">
+    <row r="17" ht="15" spans="2:13">
       <c r="B17" s="41" t="s">
         <v>70</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="L17" s="81"/>
       <c r="M17" s="87"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" ht="14.25" spans="2:13">
       <c r="B18" s="38" t="s">
         <v>71</v>
       </c>
@@ -5070,7 +5070,7 @@
       <c r="L18" s="79"/>
       <c r="M18" s="86"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" ht="15" spans="2:13">
       <c r="B19" s="41" t="s">
         <v>72</v>
       </c>
@@ -5082,7 +5082,7 @@
       <c r="L19" s="81"/>
       <c r="M19" s="87"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" ht="14.25" spans="2:13">
       <c r="B20" s="38" t="s">
         <v>73</v>
       </c>
@@ -5094,7 +5094,7 @@
       <c r="L20" s="79"/>
       <c r="M20" s="86"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" ht="15" spans="2:13">
       <c r="B21" s="41" t="s">
         <v>74</v>
       </c>
@@ -5106,7 +5106,7 @@
       <c r="L21" s="81"/>
       <c r="M21" s="87"/>
     </row>
-    <row r="22" ht="18.75" spans="2:13">
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="43" t="s">
         <v>75</v>
       </c>
@@ -5118,7 +5118,7 @@
       <c r="L22" s="84"/>
       <c r="M22" s="88"/>
     </row>
-    <row r="23" ht="18.75"/>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5174,14 +5174,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="H2" s="64"/>
     </row>
-    <row r="3" ht="18.75" spans="2:8">
+    <row r="3" ht="15" spans="2:8">
       <c r="B3" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5210,11 +5210,11 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>79</v>
@@ -5224,7 +5224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="18.75" spans="2:5">
+    <row r="4" ht="15.75" spans="2:5">
       <c r="B4" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5235,14 +5235,14 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="2:5">
       <c r="B5" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:5">
       <c r="B6" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5271,14 +5271,14 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="2:5">
       <c r="B7" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="2:5">
       <c r="B8" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
@@ -5307,14 +5307,14 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="2:5">
       <c r="B9" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:5">
       <c r="B10" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5343,14 +5343,14 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
       <c r="B11" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5361,14 +5361,14 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="2:5">
       <c r="B12" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5379,14 +5379,14 @@
       </c>
       <c r="D12" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E12" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="2:5">
       <c r="B13" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="2:5">
       <c r="B14" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
@@ -5422,7 +5422,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" ht="14.25" spans="2:5">
       <c r="B15" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5440,7 +5440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="15" spans="2:5">
       <c r="B16" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5451,14 +5451,14 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:5">
       <c r="B17" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:5">
       <c r="B18" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
@@ -5487,14 +5487,14 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:5">
       <c r="B19" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5505,14 +5505,14 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:5">
       <c r="B20" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
@@ -5523,14 +5523,14 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:5">
       <c r="B21" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
@@ -5548,7 +5548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" ht="15" spans="2:5">
       <c r="B22" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
@@ -5559,14 +5559,14 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:5">
       <c r="B23" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
@@ -5577,14 +5577,14 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" ht="33" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="2:5">
       <c r="B24" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Alquimista)</v>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:5">
       <c r="B25" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" ht="49.5" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="2:5">
       <c r="B26" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Engenhoqueiro)</v>
@@ -5631,14 +5631,14 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:5">
       <c r="B27" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
@@ -5649,14 +5649,14 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:5">
       <c r="B28" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5667,14 +5667,14 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:5">
       <c r="B29" s="38" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:5">
       <c r="B30" s="41" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" spans="2:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="2:5">
       <c r="B31" s="43" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
@@ -5721,14 +5721,14 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5747,7 +5747,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -5755,8 +5755,8 @@
     <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:8">
       <c r="B2" s="24" t="s">
         <v>80</v>
       </c>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" spans="2:8">
+    <row r="3" ht="14.25" spans="2:8">
       <c r="B3" s="67" t="s">
         <v>84</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" ht="15" spans="2:8">
       <c r="B4" s="30" t="s">
         <v>86</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" ht="14.25" spans="2:8">
       <c r="B5" s="67" t="s">
         <v>87</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" ht="15" spans="2:8">
       <c r="B6" s="30" t="s">
         <v>89</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" spans="2:8">
+    <row r="7" ht="15" spans="2:8">
       <c r="B7" s="67" t="s">
         <v>90</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="2:5">
+    <row r="8" ht="15.75" spans="2:5">
       <c r="B8" s="30" t="s">
         <v>91</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" ht="14.25" spans="2:6">
       <c r="B9" s="67" t="s">
         <v>92</v>
       </c>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="F9" s="71"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" ht="15" spans="1:6">
       <c r="A10" s="68"/>
       <c r="B10" s="30" t="s">
         <v>93</v>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="F10" s="68"/>
     </row>
-    <row r="11" spans="2:5">
+    <row r="11" ht="14.25" spans="2:5">
       <c r="B11" s="67" t="s">
         <v>94</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
+    <row r="12" ht="15" spans="2:5">
       <c r="B12" s="30" t="s">
         <v>95</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" ht="14.25" spans="2:5">
       <c r="B13" s="67" t="s">
         <v>96</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="2:5">
+    <row r="14" ht="15" spans="2:5">
       <c r="B14" s="30" t="s">
         <v>97</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="2:5">
+    <row r="15" ht="14.25" spans="2:5">
       <c r="B15" s="67" t="s">
         <v>98</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" ht="15" spans="2:5">
       <c r="B16" s="30" t="s">
         <v>100</v>
       </c>
@@ -6017,7 +6017,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:5">
+    <row r="17" ht="14.25" spans="2:5">
       <c r="B17" s="67"/>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -6026,7 +6026,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" ht="15" spans="2:5">
       <c r="B18" s="30"/>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -6035,7 +6035,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" ht="14.25" spans="2:5">
       <c r="B19" s="67"/>
       <c r="C19" s="26"/>
       <c r="D19" s="27"/>
@@ -6044,7 +6044,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5">
+    <row r="20" ht="15" spans="2:5">
       <c r="B20" s="30"/>
       <c r="C20" s="28"/>
       <c r="D20" s="29"/>
@@ -6053,7 +6053,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5">
+    <row r="21" ht="14.25" spans="2:5">
       <c r="B21" s="67"/>
       <c r="C21" s="26"/>
       <c r="D21" s="27"/>
@@ -6062,7 +6062,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="2:5">
+    <row r="22" ht="15" spans="2:5">
       <c r="B22" s="30"/>
       <c r="C22" s="28"/>
       <c r="D22" s="29"/>
@@ -6071,7 +6071,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:5">
+    <row r="23" ht="14.25" spans="2:5">
       <c r="B23" s="67"/>
       <c r="C23" s="26"/>
       <c r="D23" s="27"/>
@@ -6080,7 +6080,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:5">
+    <row r="24" ht="15" spans="2:5">
       <c r="B24" s="30"/>
       <c r="C24" s="28"/>
       <c r="D24" s="29"/>
@@ -6089,7 +6089,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:5">
+    <row r="25" ht="14.25" spans="2:5">
       <c r="B25" s="67"/>
       <c r="C25" s="26"/>
       <c r="D25" s="27"/>
@@ -6098,7 +6098,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:5">
+    <row r="26" ht="15" spans="2:5">
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="29"/>
@@ -6107,7 +6107,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:5">
+    <row r="27" ht="14.25" spans="2:5">
       <c r="B27" s="67"/>
       <c r="C27" s="26"/>
       <c r="D27" s="27"/>
@@ -6116,7 +6116,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:5">
+    <row r="28" ht="15" spans="2:5">
       <c r="B28" s="30"/>
       <c r="C28" s="28"/>
       <c r="D28" s="29"/>
@@ -6125,7 +6125,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:5">
+    <row r="29" ht="14.25" spans="2:5">
       <c r="B29" s="67"/>
       <c r="C29" s="26"/>
       <c r="D29" s="27"/>
@@ -6134,7 +6134,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:5">
+    <row r="30" ht="15" spans="2:5">
       <c r="B30" s="30"/>
       <c r="C30" s="28"/>
       <c r="D30" s="29"/>
@@ -6143,7 +6143,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:5">
+    <row r="31" ht="14.25" spans="2:5">
       <c r="B31" s="67"/>
       <c r="C31" s="26"/>
       <c r="D31" s="27"/>
@@ -6152,7 +6152,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:5">
+    <row r="32" ht="15" spans="2:5">
       <c r="B32" s="30"/>
       <c r="C32" s="28"/>
       <c r="D32" s="29"/>
@@ -6161,7 +6161,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" ht="14.25" spans="2:5">
       <c r="B33" s="67"/>
       <c r="C33" s="26"/>
       <c r="D33" s="27"/>
@@ -6170,7 +6170,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" ht="15" spans="2:5">
       <c r="B34" s="30"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
@@ -6179,7 +6179,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" ht="14.25" spans="2:5">
       <c r="B35" s="69"/>
       <c r="C35" s="31"/>
       <c r="D35" s="32"/>
@@ -6205,15 +6205,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:6">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:6">
       <c r="B2" s="35" t="s">
         <v>101</v>
       </c>
@@ -6222,7 +6222,7 @@
       <c r="E2" s="62"/>
       <c r="F2" s="36"/>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" ht="14.25" spans="2:6">
       <c r="B3" s="38" t="s">
         <v>23</v>
       </c>
@@ -6239,7 +6239,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" ht="15" spans="2:6">
       <c r="B4" s="41" t="s">
         <v>29</v>
       </c>
@@ -6256,15 +6256,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:6">
+    <row r="5" ht="15" spans="2:6">
       <c r="B5" s="43"/>
       <c r="C5" s="49"/>
       <c r="D5" s="49"/>
       <c r="E5" s="63"/>
       <c r="F5" s="44"/>
     </row>
-    <row r="6" ht="19.5"/>
-    <row r="7" ht="18.75" spans="2:8">
+    <row r="6" ht="15"/>
+    <row r="7" ht="15.75" spans="2:8">
       <c r="B7" s="50" t="s">
         <v>104</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="G7" s="51"/>
       <c r="H7" s="64"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" ht="14.25" spans="2:8">
       <c r="B8" s="38" t="s">
         <v>23</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" ht="15" spans="2:8">
       <c r="B9" s="41" t="s">
         <v>106</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" ht="14.25" spans="2:8">
       <c r="B10" s="38" t="s">
         <v>110</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" ht="33" spans="2:8">
+    <row r="11" ht="30" spans="2:8">
       <c r="B11" s="41" t="s">
         <v>30</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" ht="14.25" spans="2:8">
       <c r="B12" s="38"/>
       <c r="C12" s="27"/>
       <c r="D12" s="27"/>
@@ -6366,7 +6366,7 @@
       <c r="G12" s="37"/>
       <c r="H12" s="39"/>
     </row>
-    <row r="13" ht="18.75" spans="2:8">
+    <row r="13" ht="15.75" spans="2:8">
       <c r="B13" s="45"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
@@ -6375,8 +6375,8 @@
       <c r="G13" s="65"/>
       <c r="H13" s="46"/>
     </row>
-    <row r="14" ht="19.5"/>
-    <row r="15" ht="18.75" spans="2:9">
+    <row r="14" ht="15"/>
+    <row r="15" ht="15.75" spans="2:9">
       <c r="B15" s="35" t="s">
         <v>116</v>
       </c>
@@ -6388,7 +6388,7 @@
       <c r="H15" s="48"/>
       <c r="I15" s="36"/>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" ht="14.25" spans="2:9">
       <c r="B16" s="53" t="s">
         <v>23</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" ht="15" spans="2:9">
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" ht="14.25" spans="2:9">
       <c r="B18" s="53"/>
       <c r="C18" s="54"/>
       <c r="D18" s="54"/>
@@ -6448,7 +6448,7 @@
       <c r="H18" s="54"/>
       <c r="I18" s="66"/>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" ht="15" spans="2:9">
       <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" ht="14.25" spans="2:9">
       <c r="B20" s="53" t="s">
         <v>124</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" ht="15" spans="2:9">
       <c r="B21" s="5" t="s">
         <v>125</v>
       </c>
@@ -6513,7 +6513,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="42"/>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" ht="14.25" spans="2:9">
       <c r="B22" s="53" t="s">
         <v>126</v>
       </c>
@@ -6532,7 +6532,7 @@
       <c r="H22" s="54"/>
       <c r="I22" s="66"/>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" ht="15" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -6542,7 +6542,7 @@
       <c r="H23" s="29"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" ht="14.25" spans="2:9">
       <c r="B24" s="53"/>
       <c r="C24" s="54"/>
       <c r="D24" s="54"/>
@@ -6552,7 +6552,7 @@
       <c r="H24" s="54"/>
       <c r="I24" s="66"/>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" ht="15" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -6562,7 +6562,7 @@
       <c r="H25" s="29"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" ht="14.25" spans="2:9">
       <c r="B26" s="53"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -6572,7 +6572,7 @@
       <c r="H26" s="54"/>
       <c r="I26" s="66"/>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" ht="15" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -6582,7 +6582,7 @@
       <c r="H27" s="29"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" ht="14.25" spans="2:9">
       <c r="B28" s="53"/>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
@@ -6592,7 +6592,7 @@
       <c r="H28" s="54"/>
       <c r="I28" s="66"/>
     </row>
-    <row r="29" ht="18.75" spans="2:9">
+    <row r="29" ht="15.75" spans="2:9">
       <c r="B29" s="7"/>
       <c r="C29" s="55"/>
       <c r="D29" s="55"/>
@@ -6602,9 +6602,9 @@
       <c r="H29" s="52"/>
       <c r="I29" s="46"/>
     </row>
-    <row r="30" ht="18.75"/>
-    <row r="31" ht="18.75"/>
-    <row r="32" ht="18.75" spans="2:4">
+    <row r="30" ht="14.25"/>
+    <row r="31" ht="14.25"/>
+    <row r="32" ht="15.75" spans="2:4">
       <c r="B32" s="1" t="s">
         <v>127</v>
       </c>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D34" s="61"/>
     </row>
-    <row r="35" ht="18.75"/>
+    <row r="35" ht="14.25"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6669,7 +6669,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -6686,7 +6686,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
         <v>130</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
         <v>139</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
         <v>144</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:16">
+    <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
         <v>146</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="19.5" spans="2:13">
+    <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
         <v>148</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
         <v>153</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
         <v>155</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
         <v>156</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
         <v>157</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="2:16">
+    <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
         <v>159</v>
       </c>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:13">
+    <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
         <v>160</v>
       </c>
@@ -7225,7 +7225,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
         <v>161</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>162</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="2:17">
+    <row r="17" ht="14.25" spans="2:17">
       <c r="B17" s="26" t="s">
         <v>163</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
         <v>164</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>165</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
         <v>166</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
         <v>167</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>168</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
         <v>169</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
         <v>170</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="2:13">
+    <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
         <v>171</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
         <v>172</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
         <v>173</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>174</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>175</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
         <v>176</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
         <v>177</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
         <v>178</v>
       </c>
@@ -7935,7 +7935,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -7952,7 +7952,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
+    <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
         <v>130</v>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
         <v>139</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
         <v>144</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:16">
+    <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
         <v>146</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="19.5" spans="2:13">
+    <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
         <v>148</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
         <v>153</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
         <v>155</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
         <v>156</v>
       </c>
@@ -8369,7 +8369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
         <v>157</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="2:16">
+    <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
         <v>159</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:13">
+    <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
         <v>160</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
         <v>161</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>162</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="2:13">
+    <row r="17" ht="14.25" spans="2:13">
       <c r="B17" s="26" t="s">
         <v>163</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
         <v>164</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>165</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
         <v>166</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" ht="14.25" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>79</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
         <v>167</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>168</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
         <v>169</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
         <v>170</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="2:13">
+    <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
         <v>171</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
         <v>172</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
         <v>173</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>174</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>175</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
         <v>176</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
         <v>177</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
         <v>178</v>
       </c>
@@ -9199,7 +9199,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
@@ -9208,8 +9208,8 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:13">
+    <row r="1" ht="14.25"/>
+    <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
         <v>179</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" ht="14.25" spans="2:13">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="18.75" spans="2:13">
+    <row r="4" ht="15.75" spans="2:13">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:10">
+    <row r="5" ht="15" spans="2:10">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" ht="15" spans="2:10">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" ht="14.25" spans="2:10">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="2:10">
+    <row r="8" ht="15.75" spans="2:10">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="18.75" spans="8:10">
+    <row r="9" ht="15" spans="8:10">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="8:10">
+    <row r="10" ht="15" spans="8:10">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="18.75" spans="8:10">
+    <row r="11" ht="15" spans="8:10">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="18.75" spans="2:10">
+    <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
         <v>186</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" ht="14.25" spans="2:10">
       <c r="B13" s="3" t="s">
         <v>187</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:10">
+    <row r="14" ht="15.75" spans="2:10">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
@@ -9457,7 +9457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="19.5" spans="8:10">
+    <row r="15" ht="15.75" spans="8:10">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="18.75" spans="2:10">
+    <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
         <v>131</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" ht="15" spans="2:10">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" ht="15" spans="2:10">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" ht="15" spans="2:10">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" ht="15" spans="2:10">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" ht="15" spans="2:10">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="18.75" spans="2:10">
+    <row r="22" ht="15.75" spans="2:10">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="18.75"/>
+    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13905" windowHeight="11685"/>
+    <workbookView windowWidth="19770" windowHeight="7005"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -959,7 +959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="189">
   <si>
     <t>Atributos</t>
   </si>
@@ -1306,7 +1306,7 @@
     <t>Material Especial (adamante)</t>
   </si>
   <si>
-    <t>x3</t>
+    <t>x4</t>
   </si>
   <si>
     <t>Itens</t>
@@ -1331,9 +1331,6 @@
   </si>
   <si>
     <t>2d8+2</t>
-  </si>
-  <si>
-    <t>Curar ferimentos</t>
   </si>
   <si>
     <t>Imagem espelhada</t>
@@ -1591,10 +1588,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1605,9 +1625,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1621,24 +1656,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1646,9 +1688,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1667,44 +1709,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1714,15 +1718,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1779,7 +1776,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1797,13 +1818,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1815,145 +1950,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2102,6 +2099,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -2181,19 +2217,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2235,19 +2258,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color auto="1"/>
@@ -2256,19 +2266,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -2476,11 +2473,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2490,6 +2493,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2509,17 +2521,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2551,155 +2557,146 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="44" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2708,7 +2705,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2721,7 +2718,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2786,149 +2783,161 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2984,10 +2993,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4319,7 +4328,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="6.125" customWidth="1"/>
@@ -4331,422 +4340,436 @@
     <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="36" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="52">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
-        <v>6</v>
-      </c>
-      <c r="H2" s="36"/>
-      <c r="K2" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="40"/>
+      <c r="K2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="36"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:14">
-      <c r="B3" s="38" t="s">
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="40"/>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>'uns dados aí'!C3+(VLOOKUP(B3,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>16</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D8" si="0">ROUNDDOWN((C3-10)/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="31">
         <f>H3-L25-SUM(L4:L22)</f>
-        <v>33</v>
-      </c>
-      <c r="H3" s="39">
-        <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
-        <v>33</v>
-      </c>
-      <c r="K3" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="43">
+        <f>'uns dados aí'!N2+((G2-1)*'uns dados aí'!C12)</f>
+        <v>41</v>
+      </c>
+      <c r="K3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:14">
-      <c r="B4" s="41" t="s">
+    <row r="4" spans="2:14">
+      <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>'uns dados aí'!C4+(VLOOKUP(B4,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>14</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="33">
         <f>H4-L26-SUM(M4:M22)</f>
-        <v>24</v>
-      </c>
-      <c r="H4" s="42">
+        <v>29</v>
+      </c>
+      <c r="H4" s="46">
         <f>'uns dados aí'!C13*G2</f>
-        <v>30</v>
-      </c>
-      <c r="K4" s="41">
+        <v>40</v>
+      </c>
+      <c r="K4" s="45">
         <v>1</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29">
+      <c r="L4" s="33"/>
+      <c r="M4" s="33">
         <v>3</v>
       </c>
-      <c r="N4" s="42"/>
-    </row>
-    <row r="5" ht="14.25" spans="2:14">
-      <c r="B5" s="38" t="s">
+      <c r="N4" s="46"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
         <f>'uns dados aí'!C5+(VLOOKUP(B5,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="43">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="41">
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="K5" s="38">
+      <c r="H5" s="94"/>
+      <c r="K5" s="42">
         <v>2</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27">
+      <c r="L5" s="31"/>
+      <c r="M5" s="31">
         <v>3</v>
       </c>
-      <c r="N5" s="39"/>
-    </row>
-    <row r="6" ht="15" spans="2:14">
-      <c r="B6" s="41" t="s">
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="33">
         <f>'uns dados aí'!C6+(VLOOKUP(B6,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>22</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="46">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="44">
         <f>G5+Perícias!J12</f>
-        <v>28</v>
-      </c>
-      <c r="H6" s="91"/>
-      <c r="K6" s="41">
+        <v>35</v>
+      </c>
+      <c r="H6" s="95"/>
+      <c r="K6" s="45">
         <v>3</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="42"/>
-    </row>
-    <row r="7" ht="14.25" spans="2:14">
-      <c r="B7" s="38" t="s">
+      <c r="L6" s="33"/>
+      <c r="M6" s="33">
+        <v>5</v>
+      </c>
+      <c r="N6" s="46"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="31">
         <f>'uns dados aí'!C7+(VLOOKUP(B7,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>18</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="41">
         <f>Perícias!J27+Perícias!J21</f>
-        <v>19</v>
-      </c>
-      <c r="H7" s="90"/>
-      <c r="K7" s="38">
+        <v>33</v>
+      </c>
+      <c r="H7" s="94"/>
+      <c r="K7" s="42">
         <v>4</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="39"/>
-    </row>
-    <row r="8" ht="15.75" spans="2:14">
-      <c r="B8" s="45" t="s">
+      <c r="L7" s="31">
+        <v>13</v>
+      </c>
+      <c r="M7" s="31"/>
+      <c r="N7" s="43"/>
+    </row>
+    <row r="8" ht="18.75" spans="2:14">
+      <c r="B8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="56">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="50">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="96">
         <v>0.5</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="K8" s="41">
+      <c r="H8" s="97"/>
+      <c r="K8" s="45">
         <v>5</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="42"/>
-    </row>
-    <row r="9" ht="15" spans="6:14">
-      <c r="F9" s="38" t="s">
+      <c r="L8" s="33">
+        <v>-13</v>
+      </c>
+      <c r="M8" s="33"/>
+      <c r="N8" s="46"/>
+    </row>
+    <row r="9" spans="6:14">
+      <c r="F9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="27">
-        <v>711</v>
-      </c>
-      <c r="H9" s="39"/>
-      <c r="K9" s="38">
+      <c r="G9" s="31">
+        <v>706</v>
+      </c>
+      <c r="H9" s="43"/>
+      <c r="K9" s="42">
         <v>6</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="39"/>
-    </row>
-    <row r="10" ht="15.75" spans="6:14">
-      <c r="F10" s="45" t="s">
+      <c r="L9" s="31">
+        <v>12</v>
+      </c>
+      <c r="M9" s="31"/>
+      <c r="N9" s="43"/>
+    </row>
+    <row r="10" spans="6:14">
+      <c r="F10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="52">
-        <v>18850</v>
-      </c>
-      <c r="H10" s="46"/>
-      <c r="K10" s="41">
+      <c r="G10" s="56">
+        <v>28850</v>
+      </c>
+      <c r="H10" s="50"/>
+      <c r="K10" s="45">
         <v>7</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="42"/>
-    </row>
-    <row r="11" ht="15.75" spans="11:14">
-      <c r="K11" s="38">
+      <c r="L10" s="33">
+        <v>23</v>
+      </c>
+      <c r="M10" s="33"/>
+      <c r="N10" s="46"/>
+    </row>
+    <row r="11" spans="11:14">
+      <c r="K11" s="42">
         <v>8</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="39"/>
-    </row>
-    <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="72" t="s">
+      <c r="L11" s="31">
+        <v>-3</v>
+      </c>
+      <c r="M11" s="31"/>
+      <c r="N11" s="43"/>
+    </row>
+    <row r="12" ht="19.5" spans="2:14">
+      <c r="B12" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="74"/>
-      <c r="K12" s="41">
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="78"/>
+      <c r="K12" s="45">
         <v>9</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="42"/>
-    </row>
-    <row r="13" ht="15.75" spans="2:14">
-      <c r="B13" s="89"/>
-      <c r="K13" s="38">
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="46"/>
+    </row>
+    <row r="13" ht="19.5" spans="2:14">
+      <c r="B13" s="93"/>
+      <c r="K13" s="42">
         <v>10</v>
       </c>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="39"/>
-    </row>
-    <row r="14" ht="15.75" spans="2:14">
-      <c r="B14" s="35" t="s">
+      <c r="L13" s="31">
+        <v>-11</v>
+      </c>
+      <c r="M13" s="31"/>
+      <c r="N13" s="43"/>
+    </row>
+    <row r="14" ht="18.75" spans="2:14">
+      <c r="B14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="36"/>
-      <c r="F14" s="35" t="s">
+      <c r="C14" s="52"/>
+      <c r="D14" s="40"/>
+      <c r="F14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="36"/>
-      <c r="K14" s="41">
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="40"/>
+      <c r="K14" s="45">
         <v>11</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="42"/>
-    </row>
-    <row r="15" ht="14.25" spans="2:14">
-      <c r="B15" s="38" t="s">
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="46"/>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="42">
         <v>12</v>
       </c>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="39"/>
-    </row>
-    <row r="16" ht="30.75" spans="2:14">
-      <c r="B16" s="45" t="s">
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="43"/>
+    </row>
+    <row r="16" ht="33.75" spans="2:14">
+      <c r="B16" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="56">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,2,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="50">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,3,FALSE),"")</f>
         <v>10</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="52" t="str">
+      <c r="G16" s="56" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
         <v>1d10</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="56">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,4,FALSE),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="50" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
-        <v>x3</v>
-      </c>
-      <c r="K16" s="41">
+        <v>x4</v>
+      </c>
+      <c r="K16" s="45">
         <v>13</v>
       </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="42"/>
-    </row>
-    <row r="17" ht="15" spans="11:14">
-      <c r="K17" s="38">
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="46"/>
+    </row>
+    <row r="17" ht="18.75" spans="11:14">
+      <c r="K17" s="42">
         <v>14</v>
       </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="39"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="43"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K18" s="41">
+      <c r="K18" s="45">
         <v>15</v>
       </c>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="42"/>
-    </row>
-    <row r="19" ht="14.25" spans="11:14">
-      <c r="K19" s="38">
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="46"/>
+    </row>
+    <row r="19" spans="11:14">
+      <c r="K19" s="42">
         <v>16</v>
       </c>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="39"/>
-    </row>
-    <row r="20" ht="15" spans="11:14">
-      <c r="K20" s="41">
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="43"/>
+    </row>
+    <row r="20" spans="11:14">
+      <c r="K20" s="45">
         <v>17</v>
       </c>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="42"/>
-    </row>
-    <row r="21" ht="14.25" spans="11:14">
-      <c r="K21" s="38">
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="46"/>
+    </row>
+    <row r="21" spans="11:14">
+      <c r="K21" s="42">
         <v>18</v>
       </c>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="39"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="43"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K22" s="45">
+      <c r="K22" s="49">
         <v>20</v>
       </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="46"/>
-    </row>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15.75" spans="11:12">
-      <c r="K24" s="35" t="s">
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="50"/>
+    </row>
+    <row r="23" ht="19.5"/>
+    <row r="24" ht="18.75" spans="11:12">
+      <c r="K24" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="36"/>
-    </row>
-    <row r="25" ht="14.25" spans="11:12">
-      <c r="K25" s="38" t="s">
+      <c r="L24" s="40"/>
+    </row>
+    <row r="25" spans="11:12">
+      <c r="K25" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="39"/>
-    </row>
-    <row r="26" ht="15.75" spans="11:12">
-      <c r="K26" s="45" t="s">
+      <c r="L25" s="43"/>
+    </row>
+    <row r="26" ht="18.75" spans="11:12">
+      <c r="K26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="46"/>
-    </row>
-    <row r="27" ht="14.25"/>
+      <c r="L26" s="50"/>
+    </row>
+    <row r="27" ht="18.75"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4781,344 +4804,344 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="12" max="12" width="19.75" customWidth="1"/>
     <col min="13" max="13" width="12.25" customWidth="1"/>
     <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="72" t="s">
+    <row r="1" ht="19.5" spans="1:15">
+      <c r="A1" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74"/>
-      <c r="I1" s="72" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="78"/>
+      <c r="I1" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="74"/>
-    </row>
-    <row r="2" ht="15"/>
-    <row r="3" ht="15.75" spans="2:13">
-      <c r="B3" s="35" t="s">
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="78"/>
+    </row>
+    <row r="2" ht="19.5"/>
+    <row r="3" ht="18.75" spans="2:13">
+      <c r="B3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="52"/>
+      <c r="D3" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="36"/>
-      <c r="K3" s="76" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="40"/>
+      <c r="K3" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="77" t="s">
+      <c r="L3" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="85" t="s">
+      <c r="M3" s="89" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="39" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="78" t="s">
+      <c r="K4" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="86"/>
+      <c r="M4" s="90"/>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="29" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="42" t="s">
+      <c r="E5" s="33"/>
+      <c r="F5" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="80" t="s">
+      <c r="K5" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="87"/>
+      <c r="M5" s="91"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="39" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="86"/>
-    </row>
-    <row r="7" ht="15" spans="2:13">
-      <c r="B7" s="41" t="s">
+      <c r="M6" s="90"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="33"/>
+      <c r="D7" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="42" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="80" t="s">
+      <c r="K7" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="81" t="s">
+      <c r="L7" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="87"/>
-    </row>
-    <row r="8" ht="14.25" spans="2:13">
-      <c r="B8" s="38" t="s">
+      <c r="M7" s="91"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="39" t="s">
+      <c r="E8" s="31"/>
+      <c r="F8" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="82" t="s">
+      <c r="L8" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="86"/>
-    </row>
-    <row r="9" ht="15" spans="2:13">
-      <c r="B9" s="41" t="s">
+      <c r="M8" s="90"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="33"/>
+      <c r="D9" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="42" t="s">
+      <c r="E9" s="33"/>
+      <c r="F9" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="87"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="91"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="78"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="86"/>
-    </row>
-    <row r="11" ht="15" spans="2:13">
-      <c r="B11" s="41" t="s">
+      <c r="K10" s="82"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="90"/>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29" t="s">
+      <c r="C11" s="33"/>
+      <c r="D11" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="42" t="s">
+      <c r="E11" s="33"/>
+      <c r="F11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="87"/>
-    </row>
-    <row r="12" ht="14.25" spans="2:13">
-      <c r="B12" s="38" t="s">
+      <c r="K11" s="84"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="91"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="31"/>
+      <c r="F12" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="78"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="86"/>
-    </row>
-    <row r="13" ht="15" spans="2:13">
-      <c r="B13" s="41" t="s">
+      <c r="K12" s="82"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="90"/>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="42" t="s">
+      <c r="E13" s="33"/>
+      <c r="F13" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="87"/>
-    </row>
-    <row r="14" ht="14.25" spans="2:13">
-      <c r="B14" s="38" t="s">
+      <c r="G13" s="79"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="91"/>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="39"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="86"/>
-    </row>
-    <row r="15" ht="15" spans="2:13">
-      <c r="B15" s="41" t="s">
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="43"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="90"/>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="42"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="87"/>
-    </row>
-    <row r="16" ht="14.25" spans="2:13">
-      <c r="B16" s="38" t="s">
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="46"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="91"/>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="39"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="86"/>
-    </row>
-    <row r="17" ht="15" spans="2:13">
-      <c r="B17" s="41" t="s">
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="43"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="90"/>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="42"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="87"/>
-    </row>
-    <row r="18" ht="14.25" spans="2:13">
-      <c r="B18" s="38" t="s">
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="46"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="91"/>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="39"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="86"/>
-    </row>
-    <row r="19" ht="15" spans="2:13">
-      <c r="B19" s="41" t="s">
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="43"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="90"/>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="42"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="87"/>
-    </row>
-    <row r="20" ht="14.25" spans="2:13">
-      <c r="B20" s="38" t="s">
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="46"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="91"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="39"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="86"/>
-    </row>
-    <row r="21" ht="15" spans="2:13">
-      <c r="B21" s="41" t="s">
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="43"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="90"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="42"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="87"/>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="43" t="s">
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="46"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="91"/>
+    </row>
+    <row r="22" ht="18.75" spans="2:13">
+      <c r="B22" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="44"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="88"/>
-    </row>
-    <row r="23" ht="14.25"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="48"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="92"/>
+    </row>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5174,561 +5197,561 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="35" t="s">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="H2" s="64"/>
-    </row>
-    <row r="3" ht="15" spans="2:8">
-      <c r="B3" s="38" t="str">
+      <c r="H2" s="68"/>
+    </row>
+    <row r="3" ht="18.75" spans="2:8">
+      <c r="B3" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-5</v>
-      </c>
-      <c r="D3" s="27">
+        <v>-4</v>
+      </c>
+      <c r="D3" s="31">
         <f ca="1">RANDBETWEEN(1,20)</f>
+        <v>19</v>
+      </c>
+      <c r="E3" s="43">
+        <f ca="1">SUM(C3:D3)</f>
         <v>15</v>
       </c>
-      <c r="E3" s="39">
-        <f ca="1">SUM(C3:D3)</f>
-        <v>10</v>
-      </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="48">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="2:5">
-      <c r="B4" s="41" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" spans="2:5">
+      <c r="B4" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D4" s="29">
+        <v>5</v>
+      </c>
+      <c r="D4" s="33">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>5</v>
-      </c>
-      <c r="E4" s="42">
+        <v>17</v>
+      </c>
+      <c r="E4" s="46">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="2:5">
-      <c r="B5" s="38" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D5" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E5" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Atuação</v>
+      </c>
+      <c r="C6" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E6" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cavalgar</v>
+      </c>
+      <c r="C7" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>6</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D7" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E7" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Conhecimento</v>
+      </c>
+      <c r="C8" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D8" s="33">
         <f ca="1" t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E8" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cura</v>
+      </c>
+      <c r="C9" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>16</v>
+      </c>
+      <c r="D9" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E9" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Diplomacia</v>
+      </c>
+      <c r="C10" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D10" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E10" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Enganação</v>
+      </c>
+      <c r="C11" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D11" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E11" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Fortitude</v>
+      </c>
+      <c r="C12" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>13</v>
+      </c>
+      <c r="D12" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E12" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Furtividade</v>
+      </c>
+      <c r="C13" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-4</v>
+      </c>
+      <c r="D13" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E13" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Guerra</v>
+      </c>
+      <c r="C14" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D14" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E14" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Iniciativa</v>
+      </c>
+      <c r="C15" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D15" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E15" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intimidação</v>
+      </c>
+      <c r="C16" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E16" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intuição</v>
+      </c>
+      <c r="C17" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D17" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E17" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Investigação</v>
+      </c>
+      <c r="C18" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D18" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E18" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Jogatina</v>
+      </c>
+      <c r="C19" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>5</v>
+      </c>
+      <c r="D19" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="E19" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ladinagem</v>
+      </c>
+      <c r="C20" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>-4</v>
+      </c>
+      <c r="D20" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E20" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Luta</v>
+      </c>
+      <c r="C21" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>15</v>
+      </c>
+      <c r="D21" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E21" s="43">
         <f ca="1" t="shared" si="1"/>
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:5">
-      <c r="B6" s="41" t="str">
+    <row r="22" spans="2:5">
+      <c r="B22" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Atuação</v>
-      </c>
-      <c r="C6" s="29">
+        <v>Misticismo</v>
+      </c>
+      <c r="C22" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D6" s="29">
+        <v>20</v>
+      </c>
+      <c r="D22" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E22" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Nobreza</v>
+      </c>
+      <c r="C23" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>10</v>
+      </c>
+      <c r="D23" s="31">
         <f ca="1" t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E23" s="43">
         <f ca="1" t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" ht="33" spans="2:5">
+      <c r="B24" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Alquimista)</v>
+      </c>
+      <c r="C24" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D24" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E24" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Armeiro)</v>
+      </c>
+      <c r="C25" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D25" s="31">
+        <f ca="1" t="shared" si="0"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
-      <c r="B7" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cavalgar</v>
-      </c>
-      <c r="C7" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D7" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E7" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="2:5">
-      <c r="B8" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Conhecimento</v>
-      </c>
-      <c r="C8" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D8" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E8" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
-      <c r="B9" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cura</v>
-      </c>
-      <c r="C9" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>9</v>
-      </c>
-      <c r="D9" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E9" s="39">
+      <c r="E25" s="43">
         <f ca="1" t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:5">
-      <c r="B10" s="41" t="str">
+    <row r="26" ht="49.5" spans="2:5">
+      <c r="B26" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Diplomacia</v>
-      </c>
-      <c r="C10" s="29">
+        <v>Ofício (Engenhoqueiro)</v>
+      </c>
+      <c r="C26" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D10" s="29">
+        <v>18</v>
+      </c>
+      <c r="D26" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E26" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Percepção</v>
+      </c>
+      <c r="C27" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D27" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E27" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pilotagem</v>
+      </c>
+      <c r="C28" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D28" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E28" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pontaria</v>
+      </c>
+      <c r="C29" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D29" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E29" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Reflexos</v>
+      </c>
+      <c r="C30" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D30" s="33">
         <f ca="1" t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E30" s="46">
         <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
-      <c r="B11" s="38" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" spans="2:5">
+      <c r="B31" s="47" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Enganação</v>
-      </c>
-      <c r="C11" s="27">
+        <v>Religião</v>
+      </c>
+      <c r="C31" s="53">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D11" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E11" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
-      <c r="B12" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Fortitude</v>
-      </c>
-      <c r="C12" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>6</v>
-      </c>
-      <c r="D12" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E12" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="2:5">
-      <c r="B13" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Furtividade</v>
-      </c>
-      <c r="C13" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-5</v>
-      </c>
-      <c r="D13" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E13" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
-      <c r="B14" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Guerra</v>
-      </c>
-      <c r="C14" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D14" s="29">
+        <v>8</v>
+      </c>
+      <c r="D31" s="53">
         <f ca="1" t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E31" s="48">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
-      <c r="B15" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Iniciativa</v>
-      </c>
-      <c r="C15" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D15" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E15" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intimidação</v>
-      </c>
-      <c r="C16" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E16" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intuição</v>
-      </c>
-      <c r="C17" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D17" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E17" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Investigação</v>
-      </c>
-      <c r="C18" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D18" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E18" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Jogatina</v>
-      </c>
-      <c r="C19" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>4</v>
-      </c>
-      <c r="D19" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E19" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ladinagem</v>
-      </c>
-      <c r="C20" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>-5</v>
-      </c>
-      <c r="D20" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E20" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Luta</v>
-      </c>
-      <c r="C21" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D21" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E21" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Misticismo</v>
-      </c>
-      <c r="C22" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>13</v>
-      </c>
-      <c r="D22" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E22" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Nobreza</v>
-      </c>
-      <c r="C23" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>9</v>
-      </c>
-      <c r="D23" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E23" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
-      <c r="B24" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Alquimista)</v>
-      </c>
-      <c r="C24" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D24" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E24" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Armeiro)</v>
-      </c>
-      <c r="C25" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D25" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E25" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="2:5">
-      <c r="B26" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Engenhoqueiro)</v>
-      </c>
-      <c r="C26" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D26" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E26" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Percepção</v>
-      </c>
-      <c r="C27" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D27" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E27" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pilotagem</v>
-      </c>
-      <c r="C28" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D28" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E28" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pontaria</v>
-      </c>
-      <c r="C29" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>5</v>
-      </c>
-      <c r="D29" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E29" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Reflexos</v>
-      </c>
-      <c r="C30" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D30" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E30" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
-      <c r="B31" s="43" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Religião</v>
-      </c>
-      <c r="C31" s="49">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D31" s="49">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E31" s="44">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
@@ -5747,7 +5770,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -5755,435 +5778,435 @@
     <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="24" t="s">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:8">
+      <c r="B2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:8">
-      <c r="B3" s="67" t="s">
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <v>1</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="41">
         <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="42">
         <v>1</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:8">
-      <c r="B4" s="30" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>1</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="45">
         <v>2</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="2:8">
-      <c r="B5" s="67" t="s">
+    <row r="5" spans="2:8">
+      <c r="B5" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="42">
         <v>3</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:8">
-      <c r="B6" s="30" t="s">
+    <row r="6" spans="2:8">
+      <c r="B6" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <v>1</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="45">
         <v>4</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="2:8">
-      <c r="B7" s="67" t="s">
+    <row r="7" ht="18.75" spans="2:8">
+      <c r="B7" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <v>1</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="47">
         <v>5</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="48">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:5">
-      <c r="B8" s="30" t="s">
+    <row r="8" ht="18.75" spans="2:5">
+      <c r="B8" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <v>1</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="2:6">
-      <c r="B9" s="67" t="s">
+    <row r="9" spans="2:6">
+      <c r="B9" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <v>1</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F9" s="71"/>
-    </row>
-    <row r="10" ht="15" spans="1:6">
-      <c r="A10" s="68"/>
-      <c r="B10" s="30" t="s">
+      <c r="F9" s="75"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="72"/>
+      <c r="B10" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <v>1</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F10" s="68"/>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
-      <c r="B11" s="67" t="s">
+      <c r="F10" s="72"/>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <v>2</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:5">
-      <c r="B12" s="30" t="s">
+    <row r="12" spans="2:5">
+      <c r="B12" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <v>1</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:5">
-      <c r="B13" s="67" t="s">
+    <row r="13" spans="2:5">
+      <c r="B13" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <v>2</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="2:5">
-      <c r="B14" s="30" t="s">
+    <row r="14" spans="2:5">
+      <c r="B14" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <v>2</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="44">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:5">
-      <c r="B15" s="67" t="s">
+    <row r="15" spans="2:5">
+      <c r="B15" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <v>2</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="30" t="s">
+    <row r="16" spans="2:5">
+      <c r="B16" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <v>3</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="44">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="67"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="37" t="str">
+    <row r="17" spans="2:5">
+      <c r="B17" s="71"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="30"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="40" t="str">
+    <row r="18" spans="2:5">
+      <c r="B18" s="34"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="67"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="37" t="str">
+    <row r="19" spans="2:5">
+      <c r="B19" s="71"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="30"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="40" t="str">
+    <row r="20" spans="2:5">
+      <c r="B20" s="34"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="67"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="37" t="str">
+    <row r="21" spans="2:5">
+      <c r="B21" s="71"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="30"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="40" t="str">
+    <row r="22" spans="2:5">
+      <c r="B22" s="34"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="67"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="37" t="str">
+    <row r="23" spans="2:5">
+      <c r="B23" s="71"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:5">
-      <c r="B24" s="30"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="40" t="str">
+    <row r="24" spans="2:5">
+      <c r="B24" s="34"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="67"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="37" t="str">
+    <row r="25" spans="2:5">
+      <c r="B25" s="71"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:5">
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="40" t="str">
+    <row r="26" spans="2:5">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="67"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="37" t="str">
+    <row r="27" spans="2:5">
+      <c r="B27" s="71"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="30"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="40" t="str">
+    <row r="28" spans="2:5">
+      <c r="B28" s="34"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="67"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="37" t="str">
+    <row r="29" spans="2:5">
+      <c r="B29" s="71"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="30"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="40" t="str">
+    <row r="30" spans="2:5">
+      <c r="B30" s="34"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:5">
-      <c r="B31" s="67"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="37" t="str">
+    <row r="31" spans="2:5">
+      <c r="B31" s="71"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:5">
-      <c r="B32" s="30"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="40" t="str">
+    <row r="32" spans="2:5">
+      <c r="B32" s="34"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:5">
-      <c r="B33" s="67"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="37" t="str">
+    <row r="33" spans="2:5">
+      <c r="B33" s="71"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" spans="2:5">
-      <c r="B34" s="30"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="40" t="str">
+    <row r="34" spans="2:5">
+      <c r="B34" s="34"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="2:5">
-      <c r="B35" s="69"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="47" t="str">
+    <row r="35" spans="2:5">
+      <c r="B35" s="73"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -6205,250 +6228,250 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:6">
-      <c r="B2" s="35" t="s">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:6">
+      <c r="B2" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="36"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:6">
-      <c r="B3" s="38" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="40"/>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:6">
-      <c r="B4" s="41" t="s">
+    <row r="4" spans="2:6">
+      <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <v>10</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>10</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <v>20</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="46">
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:6">
-      <c r="B5" s="43"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="44"/>
-    </row>
-    <row r="6" ht="15"/>
-    <row r="7" ht="15.75" spans="2:8">
-      <c r="B7" s="50" t="s">
+    <row r="5" ht="18.75" spans="2:6">
+      <c r="B5" s="47"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="48"/>
+    </row>
+    <row r="6" ht="19.5"/>
+    <row r="7" ht="18.75" spans="2:8">
+      <c r="B7" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="64"/>
-    </row>
-    <row r="8" ht="14.25" spans="2:8">
-      <c r="B8" s="38" t="s">
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="68"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:8">
-      <c r="B9" s="41" t="s">
+    <row r="9" spans="2:8">
+      <c r="B9" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="46" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="2:8">
-      <c r="B10" s="38" t="s">
+    <row r="10" spans="2:8">
+      <c r="B10" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="37">
+      <c r="E10" s="31"/>
+      <c r="F10" s="41">
         <v>2</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="43" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="2:8">
-      <c r="B11" s="41" t="s">
+    <row r="11" ht="33" spans="2:8">
+      <c r="B11" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="40">
+      <c r="E11" s="33"/>
+      <c r="F11" s="44">
         <v>6</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="46" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="2:8">
-      <c r="B12" s="38"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="39"/>
-    </row>
-    <row r="13" ht="15.75" spans="2:8">
-      <c r="B13" s="45"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="46"/>
-    </row>
-    <row r="14" ht="15"/>
-    <row r="15" ht="15.75" spans="2:9">
-      <c r="B15" s="35" t="s">
+    <row r="12" spans="2:8">
+      <c r="B12" s="42"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="43"/>
+    </row>
+    <row r="13" ht="18.75" spans="2:8">
+      <c r="B13" s="49"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="50"/>
+    </row>
+    <row r="14" ht="19.5"/>
+    <row r="15" ht="18.75" spans="2:9">
+      <c r="B15" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="36"/>
-    </row>
-    <row r="16" ht="14.25" spans="2:9">
-      <c r="B16" s="53" t="s">
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="40"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G16" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="66" t="s">
+      <c r="I16" s="70" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:9">
+    <row r="17" spans="2:9">
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="98" t="s">
         <v>121</v>
       </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="29">
+      <c r="E17" s="33">
         <v>1</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="33">
         <v>4</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="33">
         <f>PRODUCT(E17:F17)</f>
         <v>4</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="33">
         <v>30</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="46">
         <f>PRODUCT(H17,E17)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="2:9">
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="66"/>
-    </row>
-    <row r="19" ht="15" spans="2:9">
+    <row r="18" spans="2:9">
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="70"/>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
@@ -6456,161 +6479,149 @@
         <v>123</v>
       </c>
       <c r="D19" s="11"/>
-      <c r="E19" s="29">
+      <c r="E19" s="33">
         <v>2</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="33">
         <v>2</v>
       </c>
-      <c r="G19" s="29">
+      <c r="G19" s="33">
         <f>PRODUCT(E19:F19)</f>
         <v>4</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="42">
+      <c r="H19" s="33"/>
+      <c r="I19" s="46">
         <f>PRODUCT(H19,E19)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="2:9">
-      <c r="B20" s="53" t="s">
+    <row r="20" spans="2:9">
+      <c r="B20" s="57"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="70"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54">
-        <v>1</v>
-      </c>
-      <c r="F20" s="54">
-        <v>2</v>
-      </c>
-      <c r="G20" s="54">
-        <f>PRODUCT(E20:F20)</f>
-        <v>2</v>
-      </c>
-      <c r="H20" s="54"/>
-      <c r="I20" s="66">
-        <f>PRODUCT(H20,E20)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="2:9">
-      <c r="B21" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
-      <c r="E21" s="29">
+      <c r="E21" s="33">
         <v>1</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="33">
         <v>2</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="33">
         <f>PRODUCT(E21:F21)</f>
         <v>2</v>
       </c>
-      <c r="H21" s="29"/>
-      <c r="I21" s="42"/>
-    </row>
-    <row r="22" ht="14.25" spans="2:9">
-      <c r="B22" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54">
+      <c r="H21" s="33"/>
+      <c r="I21" s="46"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58">
         <v>2</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="58">
         <v>1</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="58">
         <f>PRODUCT(E22:F22)</f>
         <v>2</v>
       </c>
-      <c r="H22" s="54"/>
-      <c r="I22" s="66"/>
-    </row>
-    <row r="23" ht="15" spans="2:9">
+      <c r="H22" s="58"/>
+      <c r="I22" s="70"/>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="42"/>
-    </row>
-    <row r="24" ht="14.25" spans="2:9">
-      <c r="B24" s="53"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="66"/>
-    </row>
-    <row r="25" ht="15" spans="2:9">
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="46"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="57"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="70"/>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="42"/>
-    </row>
-    <row r="26" ht="14.25" spans="2:9">
-      <c r="B26" s="53"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="66"/>
-    </row>
-    <row r="27" ht="15" spans="2:9">
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="46"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="57"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="70"/>
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="42"/>
-    </row>
-    <row r="28" ht="14.25" spans="2:9">
-      <c r="B28" s="53"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="66"/>
-    </row>
-    <row r="29" ht="15.75" spans="2:9">
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="46"/>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="57"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="70"/>
+    </row>
+    <row r="29" ht="18.75" spans="2:9">
       <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="46"/>
-    </row>
-    <row r="30" ht="14.25"/>
-    <row r="31" ht="14.25"/>
-    <row r="32" ht="15.75" spans="2:4">
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="50"/>
+    </row>
+    <row r="30" ht="18.75"/>
+    <row r="31" ht="18.75"/>
+    <row r="32" ht="18.75" spans="2:4">
       <c r="B32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="56">
+        <v>126</v>
+      </c>
+      <c r="C32" s="60">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2">
         <f>Clebina!C3*3</f>
@@ -6618,26 +6629,26 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:4">
-      <c r="B33" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" s="58">
+      <c r="B33" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="62">
         <f>Clebina!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="63"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="2:4">
       <c r="B34" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="60" t="str">
+        <v>128</v>
+      </c>
+      <c r="C34" s="64" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D34" s="61"/>
-    </row>
-    <row r="35" ht="14.25"/>
+      <c r="D34" s="65"/>
+    </row>
+    <row r="35" ht="18.75"/>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="B2:F2"/>
@@ -6669,7 +6680,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -6686,1235 +6697,1235 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="D2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="25" t="s">
+      <c r="J2" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="O2" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F3" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F3" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-5</v>
-      </c>
-      <c r="K3" s="27" t="s">
+        <v>-4</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="M3" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="O3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="O3" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O4" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="46">
         <v>4</v>
       </c>
-      <c r="K4" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="42">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="26" t="s">
+    </row>
+    <row r="5" ht="18.75" spans="2:16">
+      <c r="B5" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F5" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="19.5" spans="2:13">
+      <c r="B6" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="33">
+        <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="2:16">
+      <c r="B7" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="31">
+        <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E7" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>6</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K7" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="M7" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O7" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="40"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="33">
+        <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E8" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F8" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="L8" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="O5" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="29">
-        <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
+      <c r="M8" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O8" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="43">
+        <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="31">
+        <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F9" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>16</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="46">
+        <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="33">
+        <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E10" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F6" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F10" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="27">
-        <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E7" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F7" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K10" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O7" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="29">
-        <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F8" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="39">
-        <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="27">
-        <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E9" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F9" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="42">
-        <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="29">
-        <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E10" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F10" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K10" s="29" t="s">
+      <c r="M10" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="38" t="s">
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="27">
+    <row r="11" spans="2:16">
+      <c r="B11" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F11" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F11" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M11" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="41" t="s">
+      <c r="M11" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="28" t="s">
+    <row r="12" spans="2:16">
+      <c r="B12" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F12" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F12" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>13</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="43">
+        <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+    </row>
+    <row r="13" ht="18.75" spans="2:16">
+      <c r="B13" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="31">
+        <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E13" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F13" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>-4</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="O13" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="P13" s="50">
+        <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" spans="2:13">
+      <c r="B14" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="33">
+        <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E14" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F14" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="31">
+        <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E15" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F15" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>6</v>
       </c>
-      <c r="K12" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L12" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M12" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O12" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="39">
-        <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="K15" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="27">
-        <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E13" s="27">
+      <c r="L15" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="33">
+        <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F13" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F16" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-5</v>
-      </c>
-      <c r="K13" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M13" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="P13" s="46">
-        <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="29">
-        <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="27">
-        <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E15" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>5</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K16" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="28" t="s">
+      <c r="M16" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C16" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="29">
-        <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="E16" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F16" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:17">
-      <c r="B17" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="27">
+      <c r="C17" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="31">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F17" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F17" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="37" t="s">
-        <v>142</v>
+      <c r="M17" s="41" t="s">
+        <v>141</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="29">
+    <row r="18" spans="2:13">
+      <c r="B18" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="33">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F18" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
+        <v>4</v>
+      </c>
+      <c r="F18" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="27">
+      <c r="L18" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="31">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F19" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K19" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="29">
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="33">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F20" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>-5</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="26" t="s">
+        <v>-4</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="27">
+      <c r="C21" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="31">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="31">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F21" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>15</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="33">
+        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F22" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G22" s="33">
         <v>2</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="31">
+        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F23" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="33">
+        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F24" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="31">
+        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F25" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="L25" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="33">
+        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E26" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F26" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="31">
+        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E27" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F27" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G27" s="31">
+        <v>2</v>
+      </c>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="33">
+        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E28" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="31">
+        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E29" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F29" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>6</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M29" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="33">
+        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E30" s="33">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F30" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
+        <v>14</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M30" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="31">
+        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="31">
+        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
+        <v>4</v>
+      </c>
+      <c r="F31" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K21" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" s="27" t="s">
+      <c r="K31" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="29">
-        <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E22" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G22" s="29">
-        <v>2</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="27">
-        <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E23" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F23" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K23" s="27" t="s">
+      <c r="M31" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="29">
-        <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E24" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="27">
-        <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="29">
-        <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E26" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="27">
-        <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E27" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G27" s="27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M27" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="29">
-        <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E28" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F28" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K28" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L28" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="27">
-        <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E29" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F29" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K29" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M29" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="29">
-        <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E30" s="29">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F30" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M30" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="26" t="s">
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="27">
-        <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31" s="27">
-        <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F31" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K31" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="29">
+      <c r="C32" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="33">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="33">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F32" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="F32" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K32" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L32" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="32">
+      <c r="M32" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="36">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="36">
         <f>ROUNDDOWN(Clebina!$G$2/2,0)</f>
-        <v>3</v>
-      </c>
-      <c r="F33" s="32">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
+        <v>4</v>
+      </c>
+      <c r="F33" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="M33" s="47" t="s">
-        <v>142</v>
+      <c r="L33" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="M33" s="51" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -7935,7 +7946,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:P33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -7952,1233 +7963,1233 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
+    <row r="1" ht="18.75"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="D2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="G2" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="25" t="s">
+      <c r="J2" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="M2" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="O2" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F3" s="27" t="str">
+      <c r="E3" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F3" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D16,0)</f>
-        <v>-5</v>
-      </c>
-      <c r="K3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="M3" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="O3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="O3" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E4" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="29" t="str">
+      <c r="E4" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F4" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D17,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O4" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="46">
         <v>4</v>
       </c>
-      <c r="K4" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O4" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="42">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="26" t="s">
+    </row>
+    <row r="5" ht="18.75" spans="2:16">
+      <c r="B5" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F5" s="27" t="str">
+      <c r="E5" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F5" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C1,0)</f>
+        <v>11</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O5" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="P5" s="48">
         <v>6</v>
       </c>
-      <c r="K5" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="L5" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M5" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O5" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="29">
+    </row>
+    <row r="6" ht="19.5" spans="2:13">
+      <c r="B6" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="33">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F6" s="29" t="str">
+      <c r="E6" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F6" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C2,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K6" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M6" s="40" t="s">
-        <v>142</v>
+      <c r="M6" s="44" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" s="27">
+      <c r="B7" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="31">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F7" s="27" t="str">
+      <c r="E7" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F7" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K7" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L7" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O7" s="35" t="s">
+      <c r="M7" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O7" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="40"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="B8" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="P7" s="36"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="C8" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F8" s="29">
+      <c r="E8" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F8" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
+        <v>4</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C4,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="O8" s="38" t="s">
+      <c r="L8" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="43">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="26" t="s">
+    <row r="9" spans="2:16">
+      <c r="B9" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F9" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
+        <v>4</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C5,0)</f>
+        <v>16</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M9" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="42">
+      <c r="P9" s="46">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="29">
+    <row r="10" spans="2:16">
+      <c r="B10" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="33">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E10" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F10" s="29" t="str">
+      <c r="E10" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C6,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K10" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L10" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L10" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M10" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O10" s="38" t="s">
+      <c r="M10" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="27">
+    <row r="11" spans="2:16">
+      <c r="B11" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E11" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F11" s="27" t="str">
+      <c r="E11" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F11" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C7,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K11" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L11" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M11" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="O11" s="41" t="s">
+      <c r="M11" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="28" t="s">
+    <row r="12" spans="2:16">
+      <c r="B12" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F12" s="29" t="str">
+      <c r="E12" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F12" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C8,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K12" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L12" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L12" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M12" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="O12" s="38" t="s">
+      <c r="M12" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="43">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="27">
+    <row r="13" ht="18.75" spans="2:16">
+      <c r="B13" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="31">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F13" s="27" t="str">
+      <c r="E13" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F13" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C9,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K13" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="M13" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="M13" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="46">
+      <c r="P13" s="50">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="29">
+    <row r="14" ht="18.75" spans="2:13">
+      <c r="B14" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="33">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="E14" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F14" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29">
+        <v>4</v>
+      </c>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33">
         <v>1</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C10,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M14" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="33" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="27">
+      <c r="L14" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="31">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F15" s="27" t="str">
+      <c r="E15" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F15" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C11,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K15" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="29">
+      <c r="M15" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="33">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E16" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F16" s="29" t="str">
+      <c r="E16" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F16" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C12,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K16" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:13">
-      <c r="B17" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="27">
+      <c r="M16" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="31">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F17" s="27" t="str">
+      <c r="E17" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F17" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C13,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L17" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="29">
+      <c r="M17" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="33">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="E18" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F18" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
+        <v>4</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C14,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M18" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="27">
+      <c r="L18" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="31">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E19" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F19" s="27" t="str">
+      <c r="E19" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F19" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C15,0)</f>
-        <v>4</v>
-      </c>
-      <c r="K19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M19" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="29">
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="33">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="29" t="str">
+      <c r="E20" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F20" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C16,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="27">
+      <c r="C21" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="31">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F21" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
+        <v>4</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C17,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M21" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="29">
+      <c r="L21" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="33">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="29">
+      <c r="E22" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F22" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="G22" s="33">
         <v>2</v>
       </c>
-      <c r="G22" s="29">
-        <v>2</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C18,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="27">
+      <c r="L22" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="31">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E23" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F23" s="27" t="str">
+      <c r="E23" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F23" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C19,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K23" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="29">
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="33">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="29">
+      <c r="E24" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F24" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
+        <v>4</v>
+      </c>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C20,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M24" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="33" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="27">
+      <c r="L24" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="31">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E25" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F25" s="27">
+      <c r="E25" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F25" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
+        <v>4</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C21,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M25" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="31" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="D26" s="29">
+      <c r="L25" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="33">
         <f>VLOOKUP(C26,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E26" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F26" s="29">
+      <c r="E26" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F26" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
+        <v>4</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C22,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M26" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="33" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="27">
+      <c r="L26" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="31">
         <f>VLOOKUP(C27,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E27" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F27" s="27">
+      <c r="E27" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F27" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
+      </c>
+      <c r="G27" s="31">
         <v>2</v>
       </c>
-      <c r="G27" s="27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!D40,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L27" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="M27" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="29">
+      <c r="L27" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="33">
         <f>VLOOKUP(C28,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E28" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F28" s="29" t="str">
+      <c r="E28" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F28" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K1,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K28" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="M28" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="L28" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="27">
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="31">
         <f>VLOOKUP(C29,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E29" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F29" s="27" t="str">
+      <c r="E29" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F29" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K2,0)</f>
-        <v>5</v>
-      </c>
-      <c r="K29" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L29" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="L29" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="M29" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" s="29">
+      <c r="M29" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="33">
         <f>VLOOKUP(C30,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E30" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F30" s="29">
+      <c r="E30" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F30" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
+        <v>4</v>
+      </c>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="M30" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="27">
+      <c r="L30" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="M30" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="31">
         <f>VLOOKUP(C31,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E31" s="27">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F31" s="27">
+      <c r="E31" s="31">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F31" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
+        <v>4</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K31" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="31" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="29">
+      <c r="L31" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="33">
         <f>VLOOKUP(C32,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E32" s="29">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F32" s="29" t="str">
+      <c r="E32" s="33">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F32" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K32" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="L32" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="M32" s="40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="32">
+      <c r="M32" s="44" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="36">
         <f>VLOOKUP(C33,Clebina!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E33" s="32">
-        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="F33" s="32">
+      <c r="E33" s="36">
+        <f>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="F33" s="36">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>2</v>
-      </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
+        <v>4</v>
+      </c>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="M33" s="47" t="s">
-        <v>142</v>
+      <c r="L33" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="M33" s="51" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -9198,20 +9209,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="B1:N23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
     <col min="8" max="8" width="20.25" customWidth="1"/>
-    <col min="9" max="9" width="19.875" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="9" max="10" width="19.875" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:13">
+    <row r="1" ht="18.75"/>
+    <row r="2" ht="18.75" spans="2:14">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9221,23 +9232,26 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="I2" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="J2" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <f>12+Clebina!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:13">
+    <row r="3" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9256,18 +9270,21 @@
       <c r="I3" s="12">
         <v>1</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="23">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4">
         <f>ROUNDDOWN(I3/2,0)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:13">
+    <row r="4" ht="18.75" spans="2:14">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9283,21 +9300,25 @@
       <c r="H4" s="16">
         <v>1000</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="24">
         <v>2</v>
       </c>
-      <c r="J4" s="6">
-        <f t="shared" ref="J4:J22" si="0">ROUNDDOWN(I4/2,0)</f>
+      <c r="J4" s="25">
+        <f>I4+K4</f>
+        <v>3</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:K22" si="0">ROUNDDOWN(I4/2,0)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="N4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:10">
+    <row r="5" ht="18.75" spans="2:11">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9310,12 +9331,15 @@
       <c r="I5" s="12">
         <v>3</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="23">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:10">
+    <row r="6" spans="2:11">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9325,15 +9349,18 @@
       <c r="H6" s="16">
         <v>6000</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="24">
         <v>4</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="25">
+        <v>4</v>
+      </c>
+      <c r="K6" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:10">
+    <row r="7" spans="2:11">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9346,12 +9373,15 @@
       <c r="I7" s="12">
         <v>5</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="23">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:10">
+    <row r="8" ht="18.75" spans="2:11">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9361,53 +9391,65 @@
       <c r="H8" s="16">
         <v>15000</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="24">
         <v>6</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="25">
+        <v>5</v>
+      </c>
+      <c r="K8" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:10">
+    <row r="9" ht="18.75" spans="8:11">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
       <c r="I9" s="12">
         <v>7</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="23">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:10">
+    <row r="10" spans="8:11">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="24">
         <v>8</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="25">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:10">
+    <row r="11" ht="18.75" spans="8:11">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
       <c r="I11" s="12">
         <v>9</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="23">
+        <v>8</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:10">
+    <row r="12" ht="18.75" spans="2:11">
       <c r="B12" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="2">
         <f>3+Clebina!D5</f>
@@ -9416,20 +9458,23 @@
       <c r="H12" s="16">
         <v>45000</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="24">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="25">
+        <v>9</v>
+      </c>
+      <c r="K12" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:10">
+    <row r="13" spans="2:11">
       <c r="B13" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4">
-        <f>SUM(M3:M4)</f>
+        <f>SUM(N3:N4)</f>
         <v>5</v>
       </c>
       <c r="H13" s="17">
@@ -9438,46 +9483,55 @@
       <c r="I13" s="12">
         <v>11</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="23">
+        <v>9</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:10">
+    <row r="14" ht="18.75" spans="2:11">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
         <v>66000</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="24">
         <v>12</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="25">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:10">
+    <row r="15" ht="19.5" spans="8:11">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
       <c r="I15" s="12">
         <v>13</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="23">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:10">
+    <row r="16" ht="18.75" spans="2:11">
       <c r="B16" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>78</v>
@@ -9485,15 +9539,18 @@
       <c r="H16" s="16">
         <v>91000</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="24">
         <v>14</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="25">
+        <v>11</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:10">
+    <row r="17" spans="2:11">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9511,12 +9568,15 @@
       <c r="I17" s="12">
         <v>15</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="23">
+        <v>13</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:10">
+    <row r="18" spans="2:11">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9531,15 +9591,18 @@
       <c r="H18" s="16">
         <v>120000</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="24">
         <v>16</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="25">
+        <v>14</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:10">
+    <row r="19" spans="2:11">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9557,12 +9620,15 @@
       <c r="I19" s="12">
         <v>17</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="23">
+        <v>14</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:10">
+    <row r="20" spans="2:11">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9577,15 +9643,18 @@
       <c r="H20" s="16">
         <v>153000</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="24">
         <v>18</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="25">
+        <v>15</v>
+      </c>
+      <c r="K20" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:10">
+    <row r="21" spans="2:11">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9605,12 +9674,15 @@
       <c r="I21" s="12">
         <v>19</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="23">
+        <v>15</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:10">
+    <row r="22" ht="18.75" spans="2:11">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9625,15 +9697,18 @@
       <c r="H22" s="20">
         <v>190000</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="26">
         <v>20</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="27">
+        <v>16</v>
+      </c>
+      <c r="K22" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="14.25"/>
+    <row r="23" ht="18.75"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>

--- a/Fichas/Tormenta/Ficha Cleber.xlsx
+++ b/Fichas/Tormenta/Ficha Cleber.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashzi\Documents\GitHub\RPG\Fichas\Tormenta\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158B9552-B822-40BB-A9C2-8BBAE3924989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19770" windowHeight="7005"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clebina" sheetId="1" r:id="rId1"/>
@@ -16,18 +22,31 @@
     <sheet name="Perícias (Cópia)" sheetId="8" state="hidden" r:id="rId7"/>
     <sheet name="uns dados aí" sheetId="4" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Luciano Segundo</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0">
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -53,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L4" authorId="1">
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -61,13 +80,12 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t>Seu deslocamento é 12m (em vez de 9m).</t>
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -91,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="1">
+    <comment ref="L5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +117,6 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t>Você
 recebe visão na penumbra e +2 em
@@ -107,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="1">
+    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -140,7 +157,6 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t xml:space="preserve">Você recebe
 +1 ponto de mana por nível.
@@ -148,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -163,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0">
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -188,32 +204,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Alquimista de Batalha. Quando usa um item
-alquímico ou poção que cause dano, você soma seu
-modificador de Inteligência na rolagem de dano.
-Pré-requisito: Alquimista Iniciado.</t>
+          <t>**Catalisador Instável** - Você pode gastar uma ação completa e 3 PM para fabricar um item alquímico ou poção cuja fórmula conheça instantaneamente. O custo do item é reduzido à metade e você não precisa fazer o teste de Ofício (alquimia). Contudo, ele só dura até o fim da cena.
+*Pré-requisito: Alquimista Iniciado.*</t>
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -249,7 +254,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>**Ferreiro** - Quando usa uma arma corpo a corpo feita por você mesmo, o dano dela aumenta em um passo.
+*Pré-requisitos: Armeiro, 5° nível de inventor.*</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -258,117 +277,19 @@
             <rFont val="Segoe UI"/>
             <charset val="134"/>
           </rPr>
-          <t>Luciano Segundo:</t>
+          <t xml:space="preserve">Luciano Segundo:
+</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="Segoe UI"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-Invenção Potente - Quando usa um item fabricado por você mesmo, você pode pagar 1 PM para
-aumentar em +2 a CD para resistir a ele.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Armeiro. Você recebe proficiência com armas
-marciais corpo a corpo. Quando usa uma arma corpo a corpo, pode usar seu modificador de Inteligência em
-vez de Força nos testes de ataque e rolagens de dano.
-Pré-requisitos: treinado em Luta e Ofício (armeiro).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Granadeiro. Você pode arremessar itens alquímicos e poções em alcance médio. Você pode usar
-seu modificador de Inteligência em vez de Destreza
-para calcular a CD do teste de resistência desses
-itens. Pré-requisito: Alquimista de Batalha.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Mestre Alquimista. Você pode fabricar poções
-com fórmulas que conheça de qualquer círculo.
-Pré-requisitos: Int 17, Sab 17, Alquimista Iniciado, 10º
-nível de inventor.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Você soma seu modificador do atributo-chave
-no limite de PM que pode gastar numa magia. Por
-exemplo, um mago de 5º nível com Int 18 (+4) e
-este poder pode gastar até 9 PM em cada magia.</t>
+          <t>Alquimista de Batalha. Quando usa um item
+alquímico ou poção que cause dano, você soma seu
+modificador de Inteligência na rolagem de dano.</t>
         </r>
       </text>
     </comment>
@@ -377,12 +298,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Luciano Segundo</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -418,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -455,7 +376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -489,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -528,7 +449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -569,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -629,7 +550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -665,80 +586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Execução: padrão; Alcance: curto;
-Alvo: 1 animal ou humanoide; Duração: cena; Resistência: Vontade parcial.
-Você emana ondas de serenidade. Se
-falhar na resistência, o alvo tem sua
-atitude mudada para indiferente (veja
-Diplomacia no Capítulo 2) e não
-pode atacar ou realizar qualquer ação
-agressiva. Se passar, sofre –2 em testes
-de ataque. Qualquer ação hostil contra
-o alvo ou seus aliados dissipa a magia e
-faz ele retornar à atitude que tinha antes (ou pior, de acordo com o mestre).
-+1 PM: muda o alvo para 1 criatura.
-+1 PM: aumenta o número de alvos
-em +1.
-+2 PM: aumenta a penalidade em –1.
-+5 PM: muda o alcance para médio e o
-alvo para criaturas escolhidas. Requer
-3º círculo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Execução: padrão; Alcance: médio;
-Alvo: 1 criatura; Duração: instantânea; Resistência: Fortitude reduz à
-metade.
-Esta magia cria um crânio humano envolto em energia negativa, que causa
-4d8+4 pontos de dano de trevas quando atinge o alvo e se desfaz emitindo um som horrendo, podendo deixar
-abalados todos os inimigos num raio
-de 3m. Passar no teste de resistência
-diminui o dano pela metade e evita a
-condição abalado. Alvos que já estiverem abalados e falharem no teste ficam
-apavorados por 1d4 rodadas.
-+1 PM: aumenta o dano em +1d8+1.
-+2 PM: aumenta o número de alvos
-em +1.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -778,7 +626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -797,102 +645,22 @@
           </rPr>
           <t xml:space="preserve">
 Execução: padrão; Alcance: médio;
-Alvo: 1 objeto de madeira Grande ou
-menor; Duração: cena.
-Você molda, retorce, altera ou repele madeira. Ao lançar a magia, escolha.
-Fortalecer: deixa o alvo mais resistente.
-Armas têm seu dano aumentado em
-um passo. Escudos têm seu bônus de
-Defesa aumentado em +2. Além disso, esses e outros itens de madeira recebem +5 na RD e dobram seus PV.
-Modelar: muda a forma do alvo. Pode
-transformar um galho em espada,
-criar uma porta onde antes havia apenas uma parede, transformar um tronco em uma caixa... Mas não pode criar
-mecanismos complexos (como uma
-besta) ou itens consumíveis.
-Repelir: o alvo é repelido por você. Se
-for uma arma, ataques feitos com ela
-contra você falham automaticamente.
-Se for uma porta ou outro objeto que
-possa ser aberto, ele vai se abrir quando você se aproximar, mesmo que esteja trancado. Uma carroça ou outro objeto que vá atingi-lo, como um tronco
-caindo ou barril, vai desviar ou simplesmente parar adjacente a você, sem lhe
-causar dano. Os efeitos de regras em
-outros objetos de madeira ficam a cargo do mestre.
-Retorcer: torna o alvo imprestável. Uma
-porta retorcida emperra (exigindo um
-teste de Força contra CD 25 para ser
-aberta). Armas e itens retorcidos impõem uma penalidade de –5 em testes
-de perícia. Escudos retorcidos deixam
-de oferecer qualquer bônus (mas ainda impõem penalidades). Um barco retorcido começa a afundar e naufraga ao
-final da cena. Os efeitos de regras em
-outros objetos de madeira ficam a cargo do mestre.
-+1 PM: muda o alcance para pessoal,
-o alvo para você e a duração para 1
-dia. Você e seu equipamento se transformam em uma árvore de tamanho
-Grande. Nessa forma, você não pode
-falar ou fazer ações físicas, mas consegue perceber seus arredores normalmente. Se for atacado nessa forma, a
-magia é dissipada. Um teste de Sobrevivência (CD 30) revela que você não é
-uma árvore verdadeira.
-+3 PM: muda o alvo para área de quadrado com 9m de lado e a duração para
-cena. Em vez do normal, qualquer
-vegetação na área fica rígida e afiada. A área é considerada terreno difícil e criaturas que andem nela sofrem
-1d6 pontos de dano de corte para cada
-1,5m que avancem.
-+7 PM: muda o alvo para objeto de
-madeira Enorme ou menor. Requer 3º
-círculo.
-+12 PM: muda o alvo para objeto de
-madeira Colossal ou menor. Requer 4º
-círculo.</t>
+Alvo: 1 criatura; Duração: instantânea; Resistência: Fortitude reduz à
+metade.
+Esta magia cria um crânio humano envolto em energia negativa, que causa
+4d8+4 pontos de dano de trevas quando atinge o alvo e se desfaz emitindo um som horrendo, podendo deixar
+abalados todos os inimigos num raio
+de 3m. Passar no teste de resistência
+diminui o dano pela metade e evita a
+condição abalado. Alvos que já estiverem abalados e falharem no teste ficam
+apavorados por 1d4 rodadas.
++1 PM: aumenta o dano em +1d8+1.
++2 PM: aumenta o número de alvos
+em +1.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Execução: completa; Alcance: médio;
-Efeito: 1 enxame Médio (quadrado de
-1,5m); Duração: sustentada. Resistência: Fortitude reduz à metade.
-Você conjura um enxame de criaturas a sua escolha, como besouros, gafanhotos, mosquitos, ratos, morcegos
-ou serpentes, que surge em um ponto
-a sua escolha. O enxame pode passar
-pelo espaço de outras criaturas e não
-impede que outras criaturas entrem
-no espaço dele. No final de cada um
-de seus turnos, o enxame causa 2d12
-pontos de dano de veneno a qualquer
-criatura em seu espaço (Fortitude reduz à metade). Você pode gastar uma
-ação de movimento para mover o enxame com deslocamento de 12m.
-+2 PM: aumenta o dano em +1d12.
-+3 PM: muda a resistência para Reflexos reduz à metade e o enxame para
-criaturas maiores, como gatos, guaxinins, compsognatos ou kobolds. Ele
-causa 3d12 pontos de dano (a sua escolha entre corte, impacto ou perfuração). O resto da magia segue normal.
-+5 PM: aumenta o número de enxames em +1. Eles não podem ocupar o
-mesmo espaço. Requer 3º círculo.
-+7 PM: muda a resistência para Reflexos reduz à metade e o enxame para
-criaturas elementais. Ele causa 5d12
-pontos do dano (a sua escolha entre
-ácido, eletricidade, fogo ou frio). O
-resto da magia segue normal. Requer
-4º círculo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -921,45 +689,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Luciano Segundo:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Segoe UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Execução: padrão; Alcance: pessoal;
-Alvo: você; Duração: sustentada.
-Você se torna uma máquina de combate, ficando mais forte, rápido e resistente. Você recebe +6 na Defesa, testes de ataque e rolagens de dano corpo
-a corpo, e 30 PV temporários. Durante
-a Transformação de Guerra você não pode
-lançar magias, mas se torna proficiente
-em todas as armas.
-+2 PM: aumenta os bônus na Defesa, testes de ataque e rolagens de dano
-corpo a corpo em +1, e os PV temporários em +10.
-+2 PM: adiciona componente material (uma barra de adamante no valor de T$ 100). Sua forma de combate
-ganha um aspecto metálico e sem expressões. Além do normal, você recebe resistência a dano 10 e imunidade a
-atordoamento, doenças, encantamento, fadiga, paralisia, necromancia, sangramento, sono e veneno, e não precisa respirar.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="183">
   <si>
     <t>Atributos</t>
   </si>
@@ -1051,9 +786,6 @@
     <t>Armadura de Gelo Eterno</t>
   </si>
   <si>
-    <t>Martelo de Guerra</t>
-  </si>
-  <si>
     <t>Status Anteriores</t>
   </si>
   <si>
@@ -1135,33 +867,18 @@
     <t>Nível 7</t>
   </si>
   <si>
-    <t>Invenção Potente</t>
-  </si>
-  <si>
     <t>Nível 8</t>
   </si>
   <si>
     <t>Nível 9</t>
   </si>
   <si>
-    <t>Granadeiro</t>
-  </si>
-  <si>
     <t>Nível 10</t>
   </si>
   <si>
-    <t>Mestre Alquimista</t>
-  </si>
-  <si>
     <t>Nível 11</t>
   </si>
   <si>
-    <t>Magia Ilimitada</t>
-  </si>
-  <si>
-    <t>PNA</t>
-  </si>
-  <si>
     <t>Nível 12</t>
   </si>
   <si>
@@ -1240,30 +957,18 @@
     <t>Toque Chocante</t>
   </si>
   <si>
-    <t>Tranquilidade</t>
-  </si>
-  <si>
     <t>Crânio voador de Vladislav</t>
   </si>
   <si>
     <t>Concentração</t>
   </si>
   <si>
-    <t>Controlar Madeira</t>
-  </si>
-  <si>
-    <t>Enxame de Pesteste</t>
-  </si>
-  <si>
     <t>Velocidade</t>
   </si>
   <si>
     <t>Aracana</t>
   </si>
   <si>
-    <t>Transformação de Guerra</t>
-  </si>
-  <si>
     <t>Armaduras</t>
   </si>
   <si>
@@ -1291,24 +996,6 @@
     <t>x2</t>
   </si>
   <si>
-    <t>Bordão</t>
-  </si>
-  <si>
-    <t>1d6/1d6</t>
-  </si>
-  <si>
-    <t>Equilibrada</t>
-  </si>
-  <si>
-    <t>1d10</t>
-  </si>
-  <si>
-    <t>Material Especial (adamante)</t>
-  </si>
-  <si>
-    <t>x4</t>
-  </si>
-  <si>
     <t>Itens</t>
   </si>
   <si>
@@ -1526,24 +1213,55 @@
   </si>
   <si>
     <t>Aumento ATR</t>
+  </si>
+  <si>
+    <t>Espada Bastarda</t>
+  </si>
+  <si>
+    <t>Maciça, Material Especial (adamante), Cruel, Certeira</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>Corte</t>
+  </si>
+  <si>
+    <t>Catalisador Instável</t>
+  </si>
+  <si>
+    <t>Ferreiro</t>
+  </si>
+  <si>
+    <t>Fazedor de poção 8000</t>
+  </si>
+  <si>
+    <t>Qnt.</t>
+  </si>
+  <si>
+    <t>Total T$</t>
+  </si>
+  <si>
+    <t>1d10/1d12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1581,154 +1299,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1742,8 +1315,27 @@
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF231F20"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF231F20"/>
+      <name val="Palatino Linotype"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1762,200 +1354,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="46">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -2474,58 +1874,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2533,545 +1904,807 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
-    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
-    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
-    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
-    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
-    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
-    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
-    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
-    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
-    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
-    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
-    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
-    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
-    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
-    <cellStyle name="Saída" xfId="25" builtinId="21"/>
-    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
-    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bom" xfId="29" builtinId="26"/>
-    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
-    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
-    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
-    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
-    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
-    <cellStyle name="Título" xfId="36" builtinId="15"/>
-    <cellStyle name="Observação" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
-    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
-    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
-    <cellStyle name="Comma" xfId="43" builtinId="3"/>
-    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
-    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
-    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
-    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
         <name val="Palatino Linotype"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <family val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3094,15 +2727,379 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3125,48 +3122,15 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <name val="Palatino Linotype"/>
+        <family val="1"/>
         <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3190,15 +3154,48 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3221,379 +3218,15 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <name val="Palatino Linotype"/>
+        <family val="1"/>
         <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3614,436 +3247,94 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela2" displayName="Tabela2" ref="B2:E35" totalsRowShown="0">
-  <autoFilter ref="B2:E35"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Magia" dataDxfId="0"/>
-    <tableColumn id="4" name="Tipo" dataDxfId="1"/>
-    <tableColumn id="2" name="Círculo" dataDxfId="2"/>
-    <tableColumn id="3" name="Custo" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela2" displayName="Tabela2" ref="B2:F35" totalsRowShown="0">
+  <autoFilter ref="B2:F35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Magia" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tipo" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{BC96C631-9C03-4DC1-8F50-5784511D8845}" name="Nível" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Círculo" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Custo" dataDxfId="25">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(E3,$H$3:$I$7,2,FALSE)^2*10,"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B2:M33" totalsRowShown="0">
-  <autoFilter ref="B2:M33"/>
-  <sortState ref="B2:M33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela1" displayName="Tabela1" ref="B2:M33" totalsRowShown="0">
+  <autoFilter ref="B2:M33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:M33">
     <sortCondition ref="B2:B33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" name="Perícia" dataDxfId="4"/>
-    <tableColumn id="11" name="ATR" dataDxfId="5"/>
-    <tableColumn id="2" name="MOD" dataDxfId="6"/>
-    <tableColumn id="3" name="1/2 Nível" dataDxfId="7"/>
-    <tableColumn id="4" name="Treino" dataDxfId="8"/>
-    <tableColumn id="10" name="Raça" dataDxfId="9"/>
-    <tableColumn id="5" name="Bônus" dataDxfId="10"/>
-    <tableColumn id="9" name="Bônus Habilidade" dataDxfId="11"/>
-    <tableColumn id="6" name="Total" dataDxfId="12"/>
-    <tableColumn id="7" name="Treinada?" dataDxfId="13"/>
-    <tableColumn id="12" name="Somente Treinada?" dataDxfId="14"/>
-    <tableColumn id="8" name="Penalidade de Armadura?" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Perícia" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ATR" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="MOD" dataDxfId="22">
+      <calculatedColumnFormula>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="1/2 Nível" dataDxfId="21">
+      <calculatedColumnFormula>ROUNDDOWN(Clebina!$G$2/2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Treino" dataDxfId="20">
+      <calculatedColumnFormula>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Raça" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Bônus" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Bônus Habilidade" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Total" dataDxfId="16">
+      <calculatedColumnFormula>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Clebina!$D$16,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Treinada?" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Somente Treinada?" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Penalidade de Armadura?" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela14" displayName="Tabela14" ref="B2:M33" totalsRowShown="0">
-  <autoFilter ref="B2:M33"/>
-  <sortState ref="B2:M33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela14" displayName="Tabela14" ref="B2:M33" totalsRowShown="0">
+  <autoFilter ref="B2:M33" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:M33">
     <sortCondition ref="B2:B33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" name="Perícia" dataDxfId="16"/>
-    <tableColumn id="11" name="ATR" dataDxfId="17"/>
-    <tableColumn id="2" name="MOD" dataDxfId="18"/>
-    <tableColumn id="3" name="1/2 Nível" dataDxfId="19"/>
-    <tableColumn id="4" name="Treino" dataDxfId="20"/>
-    <tableColumn id="10" name="Raça" dataDxfId="21"/>
-    <tableColumn id="5" name="Bônus" dataDxfId="22"/>
-    <tableColumn id="9" name="Bônus Habilidade" dataDxfId="23"/>
-    <tableColumn id="6" name="Total" dataDxfId="24"/>
-    <tableColumn id="7" name="Treinada?" dataDxfId="25"/>
-    <tableColumn id="12" name="Somente Treinada?" dataDxfId="26"/>
-    <tableColumn id="8" name="Penalidade de Armadura?" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Perícia" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="ATR" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="MOD" dataDxfId="10">
+      <calculatedColumnFormula>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="1/2 Nível" dataDxfId="9">
+      <calculatedColumnFormula>VLOOKUP(Clebina!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Treino" dataDxfId="8">
+      <calculatedColumnFormula>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Clebina!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Raça" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Bônus" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Bônus Habilidade" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Total" dataDxfId="4">
+      <calculatedColumnFormula>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Treinada?" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Somente Treinada?" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Penalidade de Armadura?" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4321,14 +3612,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:N41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:N41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="6.125" customWidth="1"/>
@@ -4340,31 +3631,30 @@
     <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
+      <c r="C2" s="81"/>
       <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="81">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
         <v>8</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="K2" s="39" t="s">
+      <c r="H2" s="82"/>
+      <c r="K2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="40"/>
-    </row>
-    <row r="3" spans="2:14">
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="82"/>
+    </row>
+    <row r="3" spans="2:14" ht="14.25">
       <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
@@ -4400,7 +3690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
+    <row r="4" spans="2:14" ht="15">
       <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
@@ -4432,7 +3722,7 @@
       </c>
       <c r="N4" s="46"/>
     </row>
-    <row r="5" spans="2:14">
+    <row r="5" spans="2:14" ht="14.25">
       <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
@@ -4447,11 +3737,11 @@
       <c r="F5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="83">
         <f>10+D4+C16</f>
         <v>22</v>
       </c>
-      <c r="H5" s="94"/>
+      <c r="H5" s="84"/>
       <c r="K5" s="42">
         <v>2</v>
       </c>
@@ -4461,7 +3751,7 @@
       </c>
       <c r="N5" s="43"/>
     </row>
-    <row r="6" spans="2:14">
+    <row r="6" spans="2:14" ht="15">
       <c r="B6" s="45" t="s">
         <v>12</v>
       </c>
@@ -4476,11 +3766,11 @@
       <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="85">
         <f>G5+Perícias!J12</f>
         <v>35</v>
       </c>
-      <c r="H6" s="95"/>
+      <c r="H6" s="86"/>
       <c r="K6" s="45">
         <v>3</v>
       </c>
@@ -4490,7 +3780,7 @@
       </c>
       <c r="N6" s="46"/>
     </row>
-    <row r="7" spans="2:14">
+    <row r="7" spans="2:14" ht="14.25">
       <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
@@ -4505,11 +3795,11 @@
       <c r="F7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="83">
         <f>Perícias!J27+Perícias!J21</f>
         <v>33</v>
       </c>
-      <c r="H7" s="94"/>
+      <c r="H7" s="84"/>
       <c r="K7" s="42">
         <v>4</v>
       </c>
@@ -4519,11 +3809,11 @@
       <c r="M7" s="31"/>
       <c r="N7" s="43"/>
     </row>
-    <row r="8" ht="18.75" spans="2:14">
+    <row r="8" spans="2:14" ht="15">
       <c r="B8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="54">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>12</v>
       </c>
@@ -4534,10 +3824,10 @@
       <c r="F8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="87">
         <v>0.5</v>
       </c>
-      <c r="H8" s="97"/>
+      <c r="H8" s="88"/>
       <c r="K8" s="45">
         <v>5</v>
       </c>
@@ -4547,14 +3837,14 @@
       <c r="M8" s="33"/>
       <c r="N8" s="46"/>
     </row>
-    <row r="9" spans="6:14">
+    <row r="9" spans="2:14" ht="14.25">
       <c r="F9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="89">
         <v>706</v>
       </c>
-      <c r="H9" s="43"/>
+      <c r="H9" s="90"/>
       <c r="K9" s="42">
         <v>6</v>
       </c>
@@ -4564,14 +3854,14 @@
       <c r="M9" s="31"/>
       <c r="N9" s="43"/>
     </row>
-    <row r="10" spans="6:14">
+    <row r="10" spans="2:14" ht="15">
       <c r="F10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="91">
         <v>28850</v>
       </c>
-      <c r="H10" s="50"/>
+      <c r="H10" s="92"/>
       <c r="K10" s="45">
         <v>7</v>
       </c>
@@ -4581,7 +3871,7 @@
       <c r="M10" s="33"/>
       <c r="N10" s="46"/>
     </row>
-    <row r="11" spans="11:14">
+    <row r="11" spans="2:14" ht="14.25">
       <c r="K11" s="42">
         <v>8</v>
       </c>
@@ -4591,17 +3881,17 @@
       <c r="M11" s="31"/>
       <c r="N11" s="43"/>
     </row>
-    <row r="12" ht="19.5" spans="2:14">
-      <c r="B12" s="76" t="s">
+    <row r="12" spans="2:14" ht="15">
+      <c r="B12" s="93" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="95"/>
       <c r="K12" s="45">
         <v>9</v>
       </c>
@@ -4609,8 +3899,8 @@
       <c r="M12" s="33"/>
       <c r="N12" s="46"/>
     </row>
-    <row r="13" ht="19.5" spans="2:14">
-      <c r="B13" s="93"/>
+    <row r="13" spans="2:14" ht="14.25">
+      <c r="B13" s="79"/>
       <c r="K13" s="42">
         <v>10</v>
       </c>
@@ -4620,18 +3910,18 @@
       <c r="M13" s="31"/>
       <c r="N13" s="43"/>
     </row>
-    <row r="14" ht="18.75" spans="2:14">
-      <c r="B14" s="39" t="s">
+    <row r="14" spans="2:14" ht="15">
+      <c r="B14" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="40"/>
-      <c r="F14" s="39" t="s">
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="F14" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="82"/>
       <c r="K14" s="45">
         <v>11</v>
       </c>
@@ -4639,7 +3929,7 @@
       <c r="M14" s="33"/>
       <c r="N14" s="46"/>
     </row>
-    <row r="15" spans="2:14">
+    <row r="15" spans="2:14" ht="14.25">
       <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
@@ -4668,11 +3958,11 @@
       <c r="M15" s="31"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" ht="33.75" spans="2:14">
+    <row r="16" spans="2:14" ht="30">
       <c r="B16" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="54">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$F$5,2,FALSE),"")</f>
         <v>10</v>
       </c>
@@ -4681,19 +3971,19 @@
         <v>10</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="56" t="str">
+        <v>173</v>
+      </c>
+      <c r="G16" s="54" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,2,FALSE),"")</f>
-        <v>1d10</v>
-      </c>
-      <c r="H16" s="56">
+        <v>1d10/1d12</v>
+      </c>
+      <c r="H16" s="54">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,4,FALSE),"")</f>
         <v>0</v>
       </c>
       <c r="I16" s="50" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
-        <v>x4</v>
+        <v>x3</v>
       </c>
       <c r="K16" s="45">
         <v>13</v>
@@ -4702,7 +3992,7 @@
       <c r="M16" s="33"/>
       <c r="N16" s="46"/>
     </row>
-    <row r="17" ht="18.75" spans="11:14">
+    <row r="17" spans="11:14" ht="14.25">
       <c r="K17" s="42">
         <v>14</v>
       </c>
@@ -4710,7 +4000,7 @@
       <c r="M17" s="31"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="11:14">
+    <row r="18" spans="11:14" ht="15.75" customHeight="1">
       <c r="K18" s="45">
         <v>15</v>
       </c>
@@ -4718,7 +4008,7 @@
       <c r="M18" s="33"/>
       <c r="N18" s="46"/>
     </row>
-    <row r="19" spans="11:14">
+    <row r="19" spans="11:14" ht="14.25">
       <c r="K19" s="42">
         <v>16</v>
       </c>
@@ -4726,7 +4016,7 @@
       <c r="M19" s="31"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" spans="11:14">
+    <row r="20" spans="11:14" ht="15">
       <c r="K20" s="45">
         <v>17</v>
       </c>
@@ -4734,7 +4024,7 @@
       <c r="M20" s="33"/>
       <c r="N20" s="46"/>
     </row>
-    <row r="21" spans="11:14">
+    <row r="21" spans="11:14" ht="14.25">
       <c r="K21" s="42">
         <v>18</v>
       </c>
@@ -4742,487 +4032,477 @@
       <c r="M21" s="31"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="11:14">
+    <row r="22" spans="11:14" ht="15.75" customHeight="1">
       <c r="K22" s="49">
         <v>20</v>
       </c>
-      <c r="L22" s="56"/>
-      <c r="M22" s="56"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
       <c r="N22" s="50"/>
     </row>
-    <row r="23" ht="19.5"/>
-    <row r="24" ht="18.75" spans="11:12">
-      <c r="K24" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" spans="11:12">
+    <row r="24" spans="11:14" ht="15">
+      <c r="K24" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="11:14" ht="14.25">
       <c r="K25" s="42" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" ht="18.75" spans="11:12">
+    <row r="26" spans="11:14" ht="15">
       <c r="K26" s="49" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" ht="18.75"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="B12:I12"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="K24:L24"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16">
-      <formula1>Inventário!$B$9:$B$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
-      <formula1>Inventário!$B$4:$B$5</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Inventário!$B$9:$B$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>Inventário!$B$4:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B16</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="12" max="12" width="19.75" customWidth="1"/>
     <col min="13" max="13" width="12.25" customWidth="1"/>
     <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" spans="1:15">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:15" ht="15">
+      <c r="A1" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="95"/>
+      <c r="I1" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="78"/>
-      <c r="I1" s="76" t="s">
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="95"/>
+    </row>
+    <row r="3" spans="1:15" ht="15">
+      <c r="B3" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="78"/>
-    </row>
-    <row r="2" ht="19.5"/>
-    <row r="3" ht="18.75" spans="2:13">
-      <c r="B3" s="39" t="s">
+      <c r="C3" s="81"/>
+      <c r="D3" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="40"/>
+      <c r="K3" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="40"/>
-      <c r="K3" s="80" t="s">
+      <c r="L3" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="81" t="s">
+      <c r="M3" s="75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1">
+      <c r="B4" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="89" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31" t="s">
+      <c r="E4" s="89"/>
+      <c r="F4" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="43" t="s">
+      <c r="K4" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="L4" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="83" t="s">
+      <c r="M4" s="76"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1">
+      <c r="B5" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="90"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="45" t="s">
+      <c r="C5" s="85"/>
+      <c r="D5" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="33" t="s">
+      <c r="E5" s="98"/>
+      <c r="F5" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="46" t="s">
+      <c r="M5" s="77"/>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1">
+      <c r="B6" s="96" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="83"/>
+      <c r="D6" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="89"/>
+      <c r="F6" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="85" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="91"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="31" t="s">
+      <c r="L6" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="83" t="s">
+      <c r="M6" s="76"/>
+    </row>
+    <row r="7" spans="1:15" ht="15">
+      <c r="B7" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="90"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="45" t="s">
+      <c r="C7" s="98"/>
+      <c r="D7" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33" t="s">
+      <c r="E7" s="98"/>
+      <c r="F7" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="84" t="s">
+      <c r="L7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="85" t="s">
+      <c r="M7" s="77"/>
+    </row>
+    <row r="8" spans="1:15" ht="14.25">
+      <c r="B8" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="91"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="42" t="s">
+      <c r="C8" s="89"/>
+      <c r="D8" s="89" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="89"/>
+      <c r="F8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="76"/>
+    </row>
+    <row r="9" spans="1:15" ht="15">
+      <c r="B9" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="98"/>
+      <c r="F9" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="77"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1">
+      <c r="B10" s="96" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="82" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="86" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="90"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33" t="s">
+      <c r="E10" s="89"/>
+      <c r="F10" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="68"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="76"/>
+    </row>
+    <row r="11" spans="1:15" ht="15">
+      <c r="B11" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="84"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="91"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="42" t="s">
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="46"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="77"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.25">
+      <c r="B12" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="82"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="90"/>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="45" t="s">
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="43"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="76"/>
+    </row>
+    <row r="13" spans="1:15" ht="15">
+      <c r="B13" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33" t="s">
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="65"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="77"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.25">
+      <c r="B14" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="84"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="91"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="42" t="s">
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="43"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="76"/>
+    </row>
+    <row r="15" spans="1:15" ht="15">
+      <c r="B15" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31" t="s">
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="46"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="77"/>
+    </row>
+    <row r="16" spans="1:15" ht="14.25">
+      <c r="B16" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="82"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="90"/>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="45" t="s">
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="43"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="76"/>
+    </row>
+    <row r="17" spans="2:13" ht="15">
+      <c r="B17" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33" t="s">
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="46"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="77"/>
+    </row>
+    <row r="18" spans="2:13" ht="14.25">
+      <c r="B18" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="46" t="s">
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="43"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="76"/>
+    </row>
+    <row r="19" spans="2:13" ht="15">
+      <c r="B19" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="79"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="91"/>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="42" t="s">
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="46"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="77"/>
+    </row>
+    <row r="20" spans="2:13" ht="14.25">
+      <c r="B20" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="43"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="90"/>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="45" t="s">
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="43"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="76"/>
+    </row>
+    <row r="21" spans="2:13" ht="15">
+      <c r="B21" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="46"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="91"/>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="42" t="s">
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="46"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="77"/>
+    </row>
+    <row r="22" spans="2:13" ht="14.25">
+      <c r="B22" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="43"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="90"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="46"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="91"/>
-    </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="43"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="90"/>
-    </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="46"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="91"/>
-    </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="43"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="90"/>
-    </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="46"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="85"/>
-      <c r="M21" s="91"/>
-    </row>
-    <row r="22" ht="18.75" spans="2:13">
-      <c r="B22" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="C22" s="100"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="100"/>
       <c r="F22" s="48"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="92"/>
-    </row>
-    <row r="23" ht="18.75"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="78"/>
+    </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:H31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
+    <row r="2" spans="2:8" ht="15">
       <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E2" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="68"/>
-    </row>
-    <row r="3" ht="18.75" spans="2:8">
+        <v>72</v>
+      </c>
+      <c r="G2" s="101" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="102"/>
+    </row>
+    <row r="3" spans="2:8" ht="14.25">
       <c r="B3" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5233,21 +4513,21 @@
       </c>
       <c r="D3" s="31">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" s="43">
         <f ca="1">SUM(C3:D3)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H3" s="48">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" spans="2:5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15">
       <c r="B4" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5257,15 +4537,15 @@
         <v>5</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>17</v>
+        <f t="shared" ref="D4:D31" ca="1" si="0">RANDBETWEEN(1,20)</f>
+        <v>2</v>
       </c>
       <c r="E4" s="46">
-        <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5">
+        <f t="shared" ref="E4:E31" ca="1" si="1">SUM(C4:D4)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="14.25">
       <c r="B5" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5275,15 +4555,15 @@
         <v>7</v>
       </c>
       <c r="D5" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>14</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="E5" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15">
       <c r="B6" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5293,15 +4573,15 @@
         <v>5</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="E6" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="14.25">
       <c r="B7" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5311,15 +4591,15 @@
         <v>6</v>
       </c>
       <c r="D7" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
       </c>
       <c r="E7" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15">
       <c r="B8" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
@@ -5329,15 +4609,15 @@
         <v>18</v>
       </c>
       <c r="D8" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
       </c>
       <c r="E8" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="14.25">
       <c r="B9" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
@@ -5347,15 +4627,15 @@
         <v>16</v>
       </c>
       <c r="D9" s="31">
-        <f ca="1" t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E9" s="43">
+        <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
-      <c r="E9" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
+    </row>
+    <row r="10" spans="2:8" ht="15">
       <c r="B10" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5365,15 +4645,15 @@
         <v>5</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
       <c r="E10" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="14.25">
       <c r="B11" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5383,15 +4663,15 @@
         <v>5</v>
       </c>
       <c r="D11" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="E11" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="15">
       <c r="B12" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5401,15 +4681,15 @@
         <v>13</v>
       </c>
       <c r="D12" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="E12" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="14.25">
       <c r="B13" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
@@ -5419,15 +4699,15 @@
         <v>-4</v>
       </c>
       <c r="D13" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
       </c>
       <c r="E13" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15">
       <c r="B14" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
@@ -5437,15 +4717,15 @@
         <v>18</v>
       </c>
       <c r="D14" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
       </c>
       <c r="E14" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="14.25">
       <c r="B15" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5455,15 +4735,15 @@
         <v>6</v>
       </c>
       <c r="D15" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
       </c>
       <c r="E15" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="15">
       <c r="B16" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5473,15 +4753,15 @@
         <v>5</v>
       </c>
       <c r="D16" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="E16" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="14.25">
       <c r="B17" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5491,15 +4771,15 @@
         <v>8</v>
       </c>
       <c r="D17" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
       </c>
       <c r="E17" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15">
       <c r="B18" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
@@ -5509,15 +4789,15 @@
         <v>18</v>
       </c>
       <c r="D18" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
       <c r="E18" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="14.25">
       <c r="B19" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5527,15 +4807,15 @@
         <v>5</v>
       </c>
       <c r="D19" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
       </c>
       <c r="E19" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="15">
       <c r="B20" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
@@ -5545,15 +4825,15 @@
         <v>-4</v>
       </c>
       <c r="D20" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="E20" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="14.25">
       <c r="B21" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
@@ -5563,15 +4843,15 @@
         <v>15</v>
       </c>
       <c r="D21" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="E21" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="15">
       <c r="B22" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
@@ -5581,15 +4861,15 @@
         <v>20</v>
       </c>
       <c r="D22" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
       </c>
       <c r="E22" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="14.25">
       <c r="B23" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
@@ -5599,15 +4879,15 @@
         <v>10</v>
       </c>
       <c r="D23" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="E23" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" ht="33" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="30">
       <c r="B24" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Alquimista)</v>
@@ -5617,15 +4897,15 @@
         <v>18</v>
       </c>
       <c r="D24" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
       </c>
       <c r="E24" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25">
       <c r="B25" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
@@ -5635,15 +4915,15 @@
         <v>18</v>
       </c>
       <c r="D25" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="E25" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" ht="49.5" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="30">
       <c r="B26" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Engenhoqueiro)</v>
@@ -5653,15 +4933,15 @@
         <v>18</v>
       </c>
       <c r="D26" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
       </c>
       <c r="E26" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="14.25">
       <c r="B27" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
@@ -5671,15 +4951,15 @@
         <v>18</v>
       </c>
       <c r="D27" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
       </c>
       <c r="E27" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="15">
       <c r="B28" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5689,15 +4969,15 @@
         <v>6</v>
       </c>
       <c r="D28" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
       <c r="E28" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="14.25">
       <c r="B29" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
@@ -5707,15 +4987,15 @@
         <v>6</v>
       </c>
       <c r="D29" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
       <c r="E29" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="15">
       <c r="B30" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
@@ -5725,15 +5005,15 @@
         <v>14</v>
       </c>
       <c r="D30" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="E30" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="14.25">
       <c r="B31" s="47" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
@@ -5743,509 +5023,673 @@
         <v>8</v>
       </c>
       <c r="D31" s="53">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
       </c>
       <c r="E31" s="48">
-        <f ca="1" t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75"/>
+        <f t="shared" ca="1" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$B$2:$B$31</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:K35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
-    <col min="3" max="3" width="15.375" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
-    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="3" max="4" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="22.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:8">
+    <row r="1" spans="2:11" ht="14.25" thickBot="1"/>
+    <row r="2" spans="2:11" ht="15.75" thickTop="1">
       <c r="B2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="82"/>
+    </row>
+    <row r="3" spans="2:11" ht="14.25">
+      <c r="B3" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="62">
+        <v>1</v>
+      </c>
+      <c r="E3" s="31">
+        <v>1</v>
+      </c>
+      <c r="F3" s="41">
+        <f t="shared" ref="F3:F35" si="0">IFERROR(VLOOKUP(E3,$H$3:$I$7,2,FALSE)^2*10,"")</f>
+        <v>10</v>
+      </c>
+      <c r="H3" s="42">
+        <v>1</v>
+      </c>
+      <c r="I3" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="15">
+      <c r="B4" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="40"/>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" s="71" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="31">
+      <c r="C4" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="28">
         <v>1</v>
       </c>
-      <c r="E3" s="41">
-        <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
-        <v>10</v>
-      </c>
-      <c r="G3" s="42">
+      <c r="E4" s="29">
         <v>1</v>
       </c>
-      <c r="H3" s="43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="33">
-        <v>1</v>
-      </c>
-      <c r="E4" s="44">
+      <c r="F4" s="63">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="45">
+      <c r="H4" s="45">
         <v>2</v>
       </c>
-      <c r="H4" s="46">
+      <c r="I4" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
-      <c r="B5" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="31">
+    <row r="5" spans="2:11" ht="14.25">
+      <c r="B5" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="62">
         <v>1</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="31">
+        <v>1</v>
+      </c>
+      <c r="F5" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G5" s="42">
+      <c r="H5" s="42">
         <v>3</v>
       </c>
-      <c r="H5" s="43">
+      <c r="I5" s="43">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="33">
+    <row r="6" spans="2:11" ht="15">
+      <c r="B6" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="28">
+        <v>2</v>
+      </c>
+      <c r="E6" s="29">
         <v>1</v>
       </c>
-      <c r="E6" s="44">
+      <c r="F6" s="63">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="45">
+      <c r="H6" s="45">
         <v>4</v>
       </c>
-      <c r="H6" s="46">
+      <c r="I6" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" spans="2:8">
-      <c r="B7" s="71" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="31">
+    <row r="7" spans="2:11" ht="15" thickBot="1">
+      <c r="B7" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="62">
+        <v>3</v>
+      </c>
+      <c r="E7" s="31">
         <v>1</v>
       </c>
-      <c r="E7" s="41">
+      <c r="F7" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G7" s="47">
+      <c r="H7" s="47">
         <v>5</v>
       </c>
-      <c r="H7" s="48">
+      <c r="I7" s="48">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="18.75" spans="2:5">
-      <c r="B8" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="33">
+    <row r="8" spans="2:11" ht="15.75" thickTop="1">
+      <c r="B8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="28">
+        <v>4</v>
+      </c>
+      <c r="E8" s="29">
         <v>1</v>
       </c>
-      <c r="E8" s="44">
+      <c r="F8" s="63">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="71" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="31">
+    <row r="9" spans="2:11" ht="15" customHeight="1">
+      <c r="B9" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="62">
+        <v>5</v>
+      </c>
+      <c r="E9" s="31">
         <v>1</v>
       </c>
-      <c r="E9" s="41">
+      <c r="F9" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F9" s="75"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="72"/>
-      <c r="B10" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="G9" s="64"/>
+    </row>
+    <row r="10" spans="2:11" ht="15">
+      <c r="B10" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="28">
+        <v>6</v>
+      </c>
+      <c r="E10" s="29">
         <v>1</v>
       </c>
-      <c r="E10" s="44">
-        <f t="shared" si="0"/>
+      <c r="F10" s="63">
+        <f>IFERROR(VLOOKUP(E10,$H$3:$I$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="F10" s="72"/>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="71" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="H10" s="120" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="121"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="122"/>
+    </row>
+    <row r="11" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B11" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="62">
+        <v>7</v>
+      </c>
+      <c r="E11" s="31">
         <v>2</v>
       </c>
-      <c r="E11" s="41">
+      <c r="F11" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="33">
-        <v>1</v>
-      </c>
-      <c r="E12" s="44">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="H11" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="116" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="116" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="116" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="15">
+      <c r="B12" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="28">
+        <v>8</v>
+      </c>
+      <c r="E12" s="29">
         <v>2</v>
       </c>
-      <c r="E13" s="41">
-        <f t="shared" si="0"/>
+      <c r="F12" s="63">
+        <f>IFERROR(VLOOKUP(E12,$H$3:$I$7,2,FALSE)^2*10,"")</f>
         <v>90</v>
       </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="B14" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="33">
-        <v>2</v>
-      </c>
-      <c r="E14" s="44">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="31">
-        <v>2</v>
-      </c>
-      <c r="E15" s="41">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
-      <c r="B16" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="33">
-        <v>3</v>
-      </c>
-      <c r="E16" s="44">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="71"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="41" t="str">
+      <c r="H12" s="124"/>
+      <c r="I12" s="119" t="str">
+        <f>IFERROR(VLOOKUP(H12,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="119"/>
+      <c r="K12" s="119" t="str">
+        <f>IFERROR((J12*I12),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18" s="34"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="44" t="str">
+      <c r="H13" s="123"/>
+      <c r="I13" s="116" t="str">
+        <f>IFERROR(VLOOKUP(H13,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116" t="str">
+        <f t="shared" ref="K13:K21" si="1">IFERROR((J13*I13),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="15">
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19" s="71"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="41" t="str">
+      <c r="H14" s="118"/>
+      <c r="I14" s="119" t="str">
+        <f>IFERROR(VLOOKUP(H14,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="115"/>
+      <c r="K14" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="41"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="116" t="str">
+        <f>IFERROR(VLOOKUP(H15,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="15">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20" s="34"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="44" t="str">
+      <c r="H16" s="118"/>
+      <c r="I16" s="119" t="str">
+        <f>IFERROR(VLOOKUP(H16,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="115"/>
+      <c r="K16" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="71"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="41" t="str">
+      <c r="H17" s="123"/>
+      <c r="I17" s="116" t="str">
+        <f>IFERROR(VLOOKUP(H17,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="116"/>
+      <c r="K17" s="116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="15">
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="34"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="44" t="str">
+      <c r="H18" s="118"/>
+      <c r="I18" s="119" t="str">
+        <f>IFERROR(VLOOKUP(H18,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="115"/>
+      <c r="K18" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23" s="71"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="41" t="str">
+      <c r="H19" s="123"/>
+      <c r="I19" s="116" t="str">
+        <f>IFERROR(VLOOKUP(H19,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="116"/>
+      <c r="K19" s="116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="15">
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="34"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="44" t="str">
+      <c r="H20" s="118"/>
+      <c r="I20" s="119" t="str">
+        <f>IFERROR(VLOOKUP(H20,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="115"/>
+      <c r="K20" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25" s="71"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="41" t="str">
+      <c r="H21" s="123"/>
+      <c r="I21" s="116" t="str">
+        <f>IFERROR(VLOOKUP(H21,Tabela2[#All],5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="116"/>
+      <c r="K21" s="116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="15">
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="44" t="str">
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+    </row>
+    <row r="23" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="71"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="41" t="str">
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+    </row>
+    <row r="24" spans="2:11" ht="15">
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="34"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="44" t="str">
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+    </row>
+    <row r="25" spans="2:11" ht="14.25" customHeight="1">
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="71"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="41" t="str">
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+    </row>
+    <row r="26" spans="2:11" ht="15">
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="34"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="44" t="str">
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+    </row>
+    <row r="27" spans="2:11" ht="15">
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="71"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="41" t="str">
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+    </row>
+    <row r="28" spans="2:11" ht="15">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="34"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="44" t="str">
+    <row r="29" spans="2:11" ht="14.25">
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="71"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="41" t="str">
+    <row r="30" spans="2:11" ht="15">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="34"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="44" t="str">
+    <row r="31" spans="2:11" ht="14.25">
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="73"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="51" t="str">
+    <row r="32" spans="2:11" ht="15">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
+    <row r="33" spans="2:6" ht="14.25">
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="15">
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="14.25">
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G2:H2"/>
+  <mergeCells count="2">
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H12:H21" xr:uid="{9B54DE80-3106-4728-9D91-99ABA5F1D256}">
+      <formula1>$B$3:$B$35</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B2:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="18.75" spans="2:6">
-      <c r="B2" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="40"/>
-    </row>
-    <row r="3" spans="2:6">
+    <row r="2" spans="2:9" ht="15">
+      <c r="B2" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="82"/>
+    </row>
+    <row r="3" spans="2:9" ht="14.25">
       <c r="B3" s="42" t="s">
         <v>23</v>
       </c>
@@ -6256,13 +5700,13 @@
         <v>25</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="15">
       <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
@@ -6279,26 +5723,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:6">
+    <row r="5" spans="2:9" ht="14.25">
       <c r="B5" s="47"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
-      <c r="E5" s="67"/>
+      <c r="E5" s="59"/>
       <c r="F5" s="48"/>
     </row>
-    <row r="6" ht="19.5"/>
-    <row r="7" ht="18.75" spans="2:8">
-      <c r="B7" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="68"/>
-    </row>
-    <row r="8" spans="2:8">
+    <row r="7" spans="2:9" ht="15">
+      <c r="B7" s="101" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="102"/>
+    </row>
+    <row r="8" spans="2:9" ht="14.25">
       <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
@@ -6306,81 +5749,69 @@
         <v>26</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E8" s="31" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="43" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:9" ht="15">
       <c r="B9" s="45" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
       <c r="F9" s="44"/>
       <c r="G9" s="44" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>112</v>
-      </c>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="14.25">
+      <c r="B10" s="42"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
       <c r="E10" s="31"/>
-      <c r="F10" s="41">
-        <v>2</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" ht="33" spans="2:8">
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="43"/>
+    </row>
+    <row r="11" spans="2:9" ht="45">
       <c r="B11" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>113</v>
+        <v>173</v>
+      </c>
+      <c r="C11" s="125" t="s">
+        <v>182</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="E11" s="33"/>
       <c r="F11" s="44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="14.25">
       <c r="B12" s="42"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -6389,60 +5820,59 @@
       <c r="G12" s="41"/>
       <c r="H12" s="43"/>
     </row>
-    <row r="13" ht="18.75" spans="2:8">
+    <row r="13" spans="2:9" ht="15">
       <c r="B13" s="49"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
       <c r="H13" s="50"/>
     </row>
-    <row r="14" ht="19.5"/>
-    <row r="15" ht="18.75" spans="2:9">
-      <c r="B15" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="57" t="s">
+    <row r="15" spans="2:9" ht="15">
+      <c r="B15" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="82"/>
+    </row>
+    <row r="16" spans="2:9" ht="14.25">
+      <c r="B16" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="58" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="I16" s="70" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
+      <c r="I16" s="61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15">
       <c r="B17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="98" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="11"/>
+        <v>104</v>
+      </c>
+      <c r="C17" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="107"/>
       <c r="E17" s="33">
         <v>1</v>
       </c>
@@ -6461,24 +5891,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="57"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="70"/>
-    </row>
-    <row r="19" spans="2:9">
+    <row r="18" spans="2:9" ht="14.25">
+      <c r="B18" s="55"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="61"/>
+    </row>
+    <row r="19" spans="2:9" ht="15">
       <c r="B19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="11"/>
+        <v>106</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="107"/>
       <c r="E19" s="33">
         <v>2</v>
       </c>
@@ -6495,22 +5925,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="57"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="70"/>
-    </row>
-    <row r="21" spans="2:9">
+    <row r="20" spans="2:9" ht="14.25">
+      <c r="B20" s="55"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="61"/>
+    </row>
+    <row r="21" spans="2:9" ht="15">
       <c r="B21" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+        <v>108</v>
+      </c>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
       <c r="E21" s="33">
         <v>1</v>
       </c>
@@ -6524,163 +5954,158 @@
       <c r="H21" s="33"/>
       <c r="I21" s="46"/>
     </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58">
+    <row r="22" spans="2:9" ht="14.25">
+      <c r="B22" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="56">
         <v>2</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="56">
         <v>1</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="56">
         <f>PRODUCT(E22:F22)</f>
         <v>2</v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="70"/>
-    </row>
-    <row r="23" spans="2:9">
+      <c r="H22" s="56"/>
+      <c r="I22" s="61"/>
+    </row>
+    <row r="23" spans="2:9" ht="15">
       <c r="B23" s="5"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="33"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33"/>
       <c r="H23" s="33"/>
       <c r="I23" s="46"/>
     </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="57"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="70"/>
-    </row>
-    <row r="25" spans="2:9">
+    <row r="24" spans="2:9" ht="14.25">
+      <c r="B24" s="55"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="61"/>
+    </row>
+    <row r="25" spans="2:9" ht="15">
       <c r="B25" s="5"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="46"/>
     </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="57"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="70"/>
-    </row>
-    <row r="27" spans="2:9">
+    <row r="26" spans="2:9" ht="14.25">
+      <c r="B26" s="55"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="61"/>
+    </row>
+    <row r="27" spans="2:9" ht="15">
       <c r="B27" s="5"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="33"/>
       <c r="F27" s="33"/>
       <c r="G27" s="33"/>
       <c r="H27" s="33"/>
       <c r="I27" s="46"/>
     </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="57"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="70"/>
-    </row>
-    <row r="29" ht="18.75" spans="2:9">
+    <row r="28" spans="2:9" ht="14.25">
+      <c r="B28" s="55"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="61"/>
+    </row>
+    <row r="29" spans="2:9" ht="15">
       <c r="B29" s="7"/>
-      <c r="C29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
       <c r="I29" s="50"/>
     </row>
-    <row r="30" ht="18.75"/>
-    <row r="31" ht="18.75"/>
-    <row r="32" ht="18.75" spans="2:4">
+    <row r="32" spans="2:9" ht="15">
       <c r="B32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="60">
+        <v>110</v>
+      </c>
+      <c r="C32" s="57">
         <f>SUM(G17:G29,F9:F13,F4:F5)</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D32" s="2">
         <f>Clebina!C3*3</f>
         <v>48</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="2:4">
-      <c r="B33" s="61" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="62">
+    <row r="33" spans="2:4" ht="15" customHeight="1">
+      <c r="B33" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="109">
         <f>Clebina!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D33" s="63"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="2:4">
+      <c r="D33" s="110"/>
+    </row>
+    <row r="34" spans="2:4" ht="15.75" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="64" t="str">
+        <v>112</v>
+      </c>
+      <c r="C34" s="111" t="str">
         <f>IF(C32&gt;D32,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D34" s="65"/>
-    </row>
-    <row r="35" ht="18.75"/>
+      <c r="D34" s="112"/>
+    </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:Q33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B2:Q33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="9.625" customWidth="1"/>
@@ -6697,55 +6122,54 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75"/>
-    <row r="2" ht="15" customHeight="1" spans="2:16">
+    <row r="2" spans="2:16" ht="15" customHeight="1">
       <c r="B2" s="28" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D2" s="29" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G2" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" s="29" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="29" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K2" s="37" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="L2" s="37" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="M2" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="O2" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="P2" s="40"/>
-    </row>
-    <row r="3" spans="2:16">
+        <v>120</v>
+      </c>
+      <c r="O2" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="2:16" ht="14.25">
       <c r="B3" s="30" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D3" s="31">
         <f>VLOOKUP(C3,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6767,27 +6191,27 @@
         <v>-4</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M3" s="41" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P3" s="43">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:16" ht="15">
       <c r="B4" s="32" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D4" s="33">
         <f>VLOOKUP(C4,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6809,27 +6233,27 @@
         <v>5</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L4" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O4" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" s="46">
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="2:16">
+    <row r="5" spans="2:16" ht="14.25">
       <c r="B5" s="30" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D5" s="31">
         <f>VLOOKUP(C5,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6851,27 +6275,27 @@
         <v>7</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L5" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M5" s="41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="P5" s="48">
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="19.5" spans="2:13">
+    <row r="6" spans="2:16" ht="15">
       <c r="B6" s="32" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D6" s="33">
         <f>VLOOKUP(C6,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6893,21 +6317,21 @@
         <v>5</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L6" s="33" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:16">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="15.75" customHeight="1">
       <c r="B7" s="30" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D7" s="31">
         <f>VLOOKUP(C7,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6929,25 +6353,25 @@
         <v>6</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L7" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M7" s="41" t="s">
-        <v>141</v>
-      </c>
-      <c r="O7" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
+        <v>125</v>
+      </c>
+      <c r="O7" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="82"/>
+    </row>
+    <row r="8" spans="2:16" ht="15" customHeight="1">
       <c r="B8" s="32" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D8" s="33">
         <f>VLOOKUP(C8,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -6969,13 +6393,13 @@
         <v>18</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O8" s="42" t="s">
         <v>4</v>
@@ -6985,12 +6409,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:16" ht="15">
       <c r="B9" s="30" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D9" s="31">
         <f>VLOOKUP(C9,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7012,13 +6436,13 @@
         <v>16</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L9" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M9" s="41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O9" s="45" t="s">
         <v>9</v>
@@ -7028,12 +6452,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:16" ht="15">
       <c r="B10" s="32" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D10" s="33">
         <f>VLOOKUP(C10,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7055,13 +6479,13 @@
         <v>5</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L10" s="33" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O10" s="42" t="s">
         <v>10</v>
@@ -7071,12 +6495,12 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:16" ht="15">
       <c r="B11" s="30" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D11" s="31">
         <f>VLOOKUP(C11,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7098,13 +6522,13 @@
         <v>5</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M11" s="41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O11" s="45" t="s">
         <v>12</v>
@@ -7114,12 +6538,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:16" ht="15">
       <c r="B12" s="32" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D12" s="33">
         <f>VLOOKUP(C12,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7141,13 +6565,13 @@
         <v>13</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L12" s="33" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O12" s="42" t="s">
         <v>14</v>
@@ -7157,12 +6581,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="18.75" spans="2:16">
+    <row r="13" spans="2:16" ht="15">
       <c r="B13" s="30" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D13" s="31">
         <f>VLOOKUP(C13,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7184,13 +6608,13 @@
         <v>-4</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L13" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M13" s="41" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="O13" s="49" t="s">
         <v>16</v>
@@ -7200,12 +6624,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.75" spans="2:13">
+    <row r="14" spans="2:16" ht="15">
       <c r="B14" s="32" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D14" s="33">
         <f>VLOOKUP(C14,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7227,21 +6651,21 @@
         <v>18</v>
       </c>
       <c r="K14" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L14" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="14.25">
       <c r="B15" s="30" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D15" s="31">
         <f>VLOOKUP(C15,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7263,21 +6687,21 @@
         <v>6</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L15" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M15" s="41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="15">
       <c r="B16" s="32" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D16" s="33">
         <f>VLOOKUP(C16,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7299,21 +6723,21 @@
         <v>5</v>
       </c>
       <c r="K16" s="33" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L16" s="33" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="14.25">
       <c r="B17" s="30" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="D17" s="31">
         <f>VLOOKUP(C17,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7335,25 +6759,25 @@
         <v>8</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L17" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M17" s="41" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="Q17" t="str">
         <f>IF(P17&gt;P18,"passou demais","")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:17" ht="15">
       <c r="B18" s="32" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D18" s="33">
         <f>VLOOKUP(C18,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7375,21 +6799,21 @@
         <v>18</v>
       </c>
       <c r="K18" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L18" s="33" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M18" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="14.25">
       <c r="B19" s="30" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D19" s="31">
         <f>VLOOKUP(C19,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7411,21 +6835,21 @@
         <v>5</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L19" s="31" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M19" s="41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" ht="15">
       <c r="B20" s="32" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D20" s="33">
         <f>VLOOKUP(C20,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7447,21 +6871,21 @@
         <v>-4</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M20" s="44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="14.25">
       <c r="B21" s="30" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="D21" s="31">
         <f>VLOOKUP(C21,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7483,21 +6907,21 @@
         <v>15</v>
       </c>
       <c r="K21" s="31" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L21" s="31" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="M21" s="41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="15">
       <c r="B22" s="32" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D22" s="33">
         <f>VLOOKUP(C22,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7521,21 +6945,21 @@
         <v>20</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L22" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M22" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="14.25">
       <c r="B23" s="30" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D23" s="31">
         <f>VLOOKUP(C23,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7557,21 +6981,21 @@
         <v>10</v>
       </c>
       <c r="K23" s="31" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="L23" s="31" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M23" s="41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" ht="15">
       <c r="B24" s="32" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D24" s="33">
         <f>VLOOKUP(C24,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7593,21 +7017,21 @@
         <v>18</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="L24" s="33" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="M24" s="44" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="14.25">
       <c r="B25" s="30" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D25" s="31">
         <f>VLOOKUP(C25,Clebina!$B$3:$D$8,3,FALSE)</f>
@@ -7629,21 +7053,21 @@
         <v>18</v>
       </c>
       <c r="K25" s="31" t=